--- a/indicadores/GSF-EPRIV-INF_out.xlsx
+++ b/indicadores/GSF-EPRIV-INF_out.xlsx
@@ -8,13 +8,14 @@
   <sheets>
     <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Correlograma" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Referencias" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Correlograma" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -55,7 +56,7 @@
     <t xml:space="preserve">Modelo</t>
   </si>
   <si>
-    <t xml:space="preserve">log</t>
+    <t xml:space="preserve">niv</t>
   </si>
   <si>
     <t xml:space="preserve">(1 0 1)</t>
@@ -106,13 +107,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">07/11/2025</t>
+    <t xml:space="preserve">07/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">pcohan</t>
+    <t xml:space="preserve">vcorvalan</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -458,6 +459,63 @@
   </si>
   <si>
     <t xml:space="preserve">2030T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referencias de las series incluidas en la hoja Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original | serie de datos brutos transformados, se importa directo desde base de datos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_normal | serie original con 4 forecasts obtenidos del mejor modelo ARIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_optimista | serie original con 4 forecasts, intervalo y límite optimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a_original_fct_pesimista | serie original con 4 forecasts, intervalo y límite pesimista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b_d16 | salida D16 del X13-ARIMA-SEATS con los factores estacionales de la serie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_c17 | salida C17 del X13-ARIMA-SEATS con pesos del irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_d12 | salida D12 del X13-ARIMA-SEATS con el componente tendencia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_1600 | tendencia HP de largo plazo con un lambda de 1.600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_hp_200 | suavizado con filtro HP usando lambda de 200, sirve para determinar PG automáticos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e_ajustada | serie ajustada por estacionalidad usando el mejor modelo (LOG o NIV según el caso)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f_filtrada | serie ajustada por estacionalidad y corregida por irregularidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final | serie f_filtrada con o sin suavizado 2x2 según el caso (es la vieja española)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_final_fct_normal | a_original_fct ajustada por D16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_tctl | tasas de cambio trimestral logarítmicas de la serie g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_var_interanual | variaciones interanuales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gg_final_var_trimestral | variaciones trimestrales de g_final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h_irregular | g_final/d_d12 componente irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i_dt | g_final/d_hp_1600 desvíos respecto de la tendencia</t>
   </si>
   <si>
     <t xml:space="preserve">Coeficientes de correlación de TCTL del ICA-SFE y serie específica</t>
@@ -1024,7 +1082,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.281779190215536</v>
+        <v>0.339098178992349</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1082,7 +1140,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.0793995120385231</v>
+        <v>0.114987574995927</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1152,7 +1210,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.406893700717286</v>
+        <v>0.226307929213274</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1182,7 +1240,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.440106039099237</v>
+        <v>0.170596365458058</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1442,40 +1500,40 @@
         <v>59.301</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>0.966981640440219</v>
+        <v>-2.57735274521391</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>63.5386784410758</v>
+        <v>63.6997944821128</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>69.6218001911328</v>
+        <v>69.545568549301</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>67.6748589781637</v>
+        <v>67.7415658238297</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>61.325879954663</v>
+        <v>61.8783527452139</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>61.325879954663</v>
+        <v>61.8783527452139</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>61.325879954663</v>
+        <v>61.8783527452139</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>61.325879954663</v>
+        <v>61.8783527452139</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>0.965173992586817</v>
+        <v>0.971405845941774</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.880843066199165</v>
+        <v>0.889752633215562</v>
       </c>
     </row>
     <row r="3">
@@ -1495,44 +1553,44 @@
         <v>69.648</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>0.970746978894638</v>
+        <v>-1.31967933240247</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.723335343691273</v>
+        <v>0.773514998731786</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>68.1297835231168</v>
+        <v>67.9776428065299</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>69.9746500231204</v>
+        <v>69.9019579190921</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>68.4931639155394</v>
+        <v>68.5340368687882</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>71.746810975715</v>
+        <v>70.9676793324025</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>70.7461073186827</v>
+        <v>70.2904809060482</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>70.7461073186827</v>
+        <v>70.2904809060482</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>70.7461073186827</v>
+        <v>70.2904809060482</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>0.142895575700944</v>
+        <v>0.12746597770436</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>0.153609330530338</v>
+        <v>0.135946220085585</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>1.03840205649088</v>
+        <v>1.03402351131976</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>1.01102481106097</v>
+        <v>1.0055581130847</v>
       </c>
     </row>
     <row r="4">
@@ -1540,56 +1598,56 @@
         <v>54</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>68.7385</v>
+        <v>68.504</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>68.7385</v>
+        <v>68.504</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>68.7385</v>
+        <v>68.504</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>68.7385</v>
+        <v>68.504</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>1.00223918031701</v>
+        <v>-0.331139537117107</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>70.2001086748881</v>
+        <v>70.0855216849906</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>70.3223149049602</v>
+        <v>70.2535552790058</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>69.2797239577976</v>
+        <v>69.2971918483537</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>68.5849259836937</v>
+        <v>68.8351395371171</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>68.5849259836937</v>
+        <v>68.8351395371171</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>68.5849259836937</v>
+        <v>68.8351395371171</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>68.5849259836937</v>
+        <v>68.8351395371171</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>-0.0310247420401339</v>
+        <v>-0.0209220192690694</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>-0.0305484134307732</v>
+        <v>-0.0207046722425522</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>0.976991735174163</v>
+        <v>0.982159194683697</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.975293917391449</v>
+        <v>0.979810050377443</v>
       </c>
     </row>
     <row r="5">
@@ -1609,44 +1667,44 @@
         <v>67.829</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>1.05941367533509</v>
+        <v>4.19091832615672</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>71.5277846556615</v>
+        <v>71.7857196496394</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>70.6600920473141</v>
+        <v>70.5958114460311</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>70.0140589268365</v>
+        <v>70.0104969173192</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>64.025037224997</v>
+        <v>63.6380816738433</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>71.5277846556615</v>
+        <v>71.7857196496394</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>71.5277846556615</v>
+        <v>71.7857196496394</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>71.5277846556615</v>
+        <v>71.7857196496394</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>0.0420131980596317</v>
+        <v>0.0419712019618764</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>0.042908243025114</v>
+        <v>0.0428644458682514</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>1.01227981146368</v>
+        <v>1.01685522383319</v>
       </c>
     </row>
     <row r="6">
@@ -1666,46 +1724,46 @@
         <v>81.778</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.969835569014098</v>
+        <v>-2.36012891173764</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>75.0235308045743</v>
+        <v>74.8396928507245</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>70.9821927927684</v>
+        <v>70.9232907273188</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>70.6722146546838</v>
+        <v>70.651107968922</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>84.3215103804996</v>
+        <v>84.1381289117377</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>75.0235308045743</v>
+        <v>74.8396928507245</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>75.0235308045743</v>
+        <v>74.8396928507245</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>75.0235308045743</v>
+        <v>74.8396928507245</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>0.0477158375913825</v>
+        <v>0.0416628317191655</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>0.223358406924412</v>
+        <v>0.209464853708684</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>0.0488725628193507</v>
+        <v>0.0425429070850087</v>
       </c>
       <c r="R6" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>1.05693453319489</v>
+        <v>1.05522025392848</v>
       </c>
     </row>
     <row r="7">
@@ -1725,46 +1783,46 @@
         <v>73.335</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.965599470417886</v>
+        <v>-1.72735857020546</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>76.2194365426861</v>
+        <v>75.9930279679327</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>71.2833707917893</v>
+        <v>71.2313011226468</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>71.2378056020113</v>
+        <v>71.2050570100606</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>75.9476390021864</v>
+        <v>75.0623585702054</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>75.9476390021864</v>
+        <v>75.0623585702054</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>75.9476390021864</v>
+        <v>75.0623585702054</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>75.9476390021864</v>
+        <v>75.0623585702054</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>0.0122423339565099</v>
+        <v>0.00297081835954165</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>0.0735239277558117</v>
+        <v>0.0678879643821959</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>0.0123175780678637</v>
+        <v>0.00297523561360769</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>0.996434012729188</v>
+        <v>0.987753226544414</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>1.06543276725817</v>
+        <v>1.05378334225515</v>
       </c>
     </row>
     <row r="8">
@@ -1784,46 +1842,46 @@
         <v>74.334</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>1.00541691993994</v>
+        <v>-0.171804110764795</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>72.7004379915661</v>
+        <v>72.6259775964041</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>71.5609055311005</v>
+        <v>71.5175983831199</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>71.7162028102403</v>
+        <v>71.6793189720426</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>73.9335081057124</v>
+        <v>74.5058041107648</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>73.9335081057124</v>
+        <v>74.5058041107648</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>73.9335081057124</v>
+        <v>74.5058041107648</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>73.9335081057124</v>
+        <v>74.5058041107648</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>-0.026877992182509</v>
+        <v>-0.0074421858000426</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0.0779848056304728</v>
+        <v>0.0823803744973883</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>-0.0265199935499771</v>
+        <v>-0.00741456130665152</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>1.01696097228863</v>
+        <v>1.02588366555019</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>1.03315501050473</v>
+        <v>1.04178280304712</v>
       </c>
     </row>
     <row r="9">
@@ -1843,46 +1901,46 @@
         <v>70.162</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1.05921024738883</v>
+        <v>4.30986420225621</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>67.5549504270107</v>
+        <v>67.572945602647</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>71.8149916650573</v>
+        <v>71.782332670748</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>72.1363264877929</v>
+        <v>72.1001552939765</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>66.2399180643915</v>
+        <v>65.8521357977438</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>66.2399180643915</v>
+        <v>65.8521357977438</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>66.2399180643915</v>
+        <v>65.8521357977438</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>66.2399180643915</v>
+        <v>65.8521357977438</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>-0.109882877038298</v>
+        <v>-0.123465167928452</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>-0.0739274481479614</v>
+        <v>-0.0826568833029093</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>-0.104060935811681</v>
+        <v>-0.116147572881113</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>0.980533886054139</v>
+        <v>0.974534041848313</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.922368944542001</v>
+        <v>0.917386400631408</v>
       </c>
     </row>
     <row r="10">
@@ -1902,46 +1960,46 @@
         <v>64.617</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.970554750415076</v>
+        <v>-1.997080290802</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>66.9203663564256</v>
+        <v>66.8049867535478</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>72.0473067246242</v>
+        <v>72.0275217761205</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>72.5381833695687</v>
+        <v>72.5079598406642</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>66.5773878004979</v>
+        <v>66.614080290802</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>66.5773878004979</v>
+        <v>66.614080290802</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>66.5773878004979</v>
+        <v>66.614080290802</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>66.5773878004979</v>
+        <v>66.614080290802</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>0.00508172425485033</v>
+        <v>0.0115041090295127</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>-0.11257991877345</v>
+        <v>-0.109909758399588</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>0.00509465811504084</v>
+        <v>0.0115705357742446</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>0.994874825488837</v>
+        <v>0.997142332151789</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.92407878694157</v>
+        <v>0.92484204159981</v>
       </c>
     </row>
     <row r="11">
@@ -1961,46 +2019,46 @@
         <v>68.225</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>0.96435255590293</v>
+        <v>-2.64357357329769</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>69.0315907433805</v>
+        <v>69.2084559792661</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>72.2560438197649</v>
+        <v>72.2514771167813</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>72.9322981483501</v>
+        <v>72.9118863794266</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>70.7469478692058</v>
+        <v>70.8685735732977</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>70.7469478692058</v>
+        <v>70.8685735732977</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>70.7469478692058</v>
+        <v>70.8685735732977</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>70.7469478692058</v>
+        <v>70.8685735732977</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>0.0607443985544584</v>
+        <v>0.0619111142707565</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>-0.0684773246582538</v>
+        <v>-0.0558706797493626</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>0.0626272704060149</v>
+        <v>0.0638677778620196</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>1.02484887147106</v>
+        <v>1.0239872074957</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.979114605910014</v>
+        <v>0.980859857837253</v>
       </c>
     </row>
     <row r="12">
@@ -2020,46 +2078,46 @@
         <v>70.05</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>1.00671303273077</v>
+        <v>0.35374009255429</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.887320193489519</v>
+        <v>0.854991730688768</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>72.3236112078467</v>
+        <v>72.4799542420324</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>72.435977361116</v>
+        <v>72.449126709346</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>73.2993915390743</v>
+        <v>73.2916192798351</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>69.5828877967191</v>
+        <v>69.6962599074457</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>69.8917119803837</v>
+        <v>70.0999186051956</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>69.8917119803837</v>
+        <v>70.0999186051956</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>69.8917119803837</v>
+        <v>70.0999186051956</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>-0.0121623233905801</v>
+        <v>-0.0109054523340425</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>-0.0546679878837839</v>
+        <v>-0.0591347957136218</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>-0.0120886612720488</v>
+        <v>-0.0108462034629084</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>0.966374753875687</v>
+        <v>0.967162842999471</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>0.964875667128113</v>
+        <v>0.967574376519747</v>
       </c>
     </row>
     <row r="13">
@@ -2079,46 +2137,46 @@
         <v>82.955</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>1.05723877790541</v>
+        <v>4.39156406923738</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>1</v>
+        <v>0.926876989087996</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>76.569329149417</v>
+        <v>76.3964494871093</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>72.5809385743447</v>
+        <v>72.6145342557155</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>73.6092575052827</v>
+        <v>73.6166263474307</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>78.46382646345</v>
+        <v>78.5634359307626</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>78.46382646345</v>
+        <v>78.4049793573972</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>78.46382646345</v>
+        <v>78.4049793573972</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>78.46382646345</v>
+        <v>78.4049793573972</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>0.115690636655931</v>
+        <v>0.111965804635547</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.184539908204228</v>
+        <v>0.190621661812273</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>0.122648512107876</v>
+        <v>0.118474613344074</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>1.0247422477783</v>
+        <v>1.02629087979575</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>1.08105279436528</v>
+        <v>1.07974223288812</v>
       </c>
     </row>
     <row r="14">
@@ -2138,46 +2196,46 @@
         <v>75.453</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>0.971139942791136</v>
+        <v>-1.82728377649303</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>77.536340479416</v>
+        <v>77.4895097886708</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>72.6831685192553</v>
+        <v>72.7402952027254</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>73.8146516127234</v>
+        <v>73.840416884381</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>77.6952905295419</v>
+        <v>77.280283776493</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>77.6952905295419</v>
+        <v>77.280283776493</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>77.6952905295419</v>
+        <v>77.280283776493</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>77.6952905295419</v>
+        <v>77.280283776493</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.00984306460901052</v>
+        <v>-0.014448575597656</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>0.166992174014986</v>
+        <v>0.160119353733145</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>-0.00979478020060709</v>
+        <v>-0.014344695835929</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>1.00205000712109</v>
+        <v>0.997299944047286</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.06895849633961</v>
+        <v>1.06241366715814</v>
       </c>
     </row>
     <row r="15">
@@ -2197,46 +2255,46 @@
         <v>72.058</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.966354290106425</v>
+        <v>-3.24042147067453</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>76.2470636183803</v>
+        <v>76.5217998296603</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>72.7385850605828</v>
+        <v>72.8226240254003</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>73.892602271935</v>
+        <v>73.9404419579035</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>74.5668547630334</v>
+        <v>75.2984214706745</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>74.5668547630334</v>
+        <v>75.2984214706745</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>74.5668547630334</v>
+        <v>75.2984214706745</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>74.5668547630334</v>
+        <v>75.2984214706745</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.0410985422403332</v>
+        <v>-0.0259796905723264</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>0.0539939461542513</v>
+        <v>0.0625079308643792</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>-0.0402654491049108</v>
+        <v>-0.0256451220022736</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>0.977963625409151</v>
+        <v>0.984012681853942</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.02513479882689</v>
+        <v>1.03399764123318</v>
       </c>
     </row>
     <row r="16">
@@ -2256,46 +2314,46 @@
         <v>78.697</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>1.00587773907846</v>
+        <v>0.637806506148738</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>76.5088683649958</v>
+        <v>76.5310525046534</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>72.7462386393186</v>
+        <v>72.8605726916228</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>73.8395410880406</v>
+        <v>73.9113519696762</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>78.2371424901983</v>
+        <v>78.0591934938513</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>78.2371424901983</v>
+        <v>78.0591934938513</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>78.2371424901983</v>
+        <v>78.0591934938513</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>78.2371424901983</v>
+        <v>78.0591934938513</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.048048400344119</v>
+        <v>0.0360082584430076</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.119405152246906</v>
+        <v>0.113541856353393</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0492214367741377</v>
+        <v>0.0366644076895015</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>1.02258919994683</v>
+        <v>1.01996759405739</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.07548024411412</v>
+        <v>1.0713502599579</v>
       </c>
     </row>
     <row r="17">
@@ -2315,46 +2373,46 @@
         <v>79.056</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>1.05433398728072</v>
+        <v>4.52218204850226</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>76.2417993586218</v>
+        <v>75.7705311370841</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>72.7063223650183</v>
+        <v>72.8547405426793</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>73.6552709286184</v>
+        <v>73.7545872189412</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>74.9819326263937</v>
+        <v>74.5338179514977</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>74.9819326263937</v>
+        <v>74.5338179514977</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>74.9819326263937</v>
+        <v>74.5338179514977</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>74.9819326263937</v>
+        <v>74.5338179514977</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.0424973164941631</v>
+        <v>-0.0462144751999576</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>-0.0443757842816674</v>
+        <v>-0.0493739229016739</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>-0.0416069626291941</v>
+        <v>-0.0451628486608848</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.98347538039728</v>
+        <v>0.983678177161661</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.03129865721926</v>
+        <v>1.023046920438</v>
       </c>
     </row>
     <row r="18">
@@ -2374,46 +2432,46 @@
         <v>72.726</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>0.974690537101999</v>
+        <v>-1.7793378495922</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>73.1520328588484</v>
+        <v>73.3372546991706</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>72.622461162144</v>
+        <v>72.8089760578575</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>73.3615826682578</v>
+        <v>73.4923272125611</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>74.6144516968768</v>
+        <v>74.5053378495922</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>74.6144516968768</v>
+        <v>74.5053378495922</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>74.6144516968768</v>
+        <v>74.5053378495922</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>74.6144516968768</v>
+        <v>74.5053378495922</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.00491297527472022</v>
+        <v>-0.000382182817651107</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>-0.0396528388228845</v>
+        <v>-0.0359075535349538</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>-0.00490092635179129</v>
+        <v>-0.000382109795101004</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>1.01999149963269</v>
+        <v>1.0159275548998</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.02742939997978</v>
+        <v>1.02329880027961</v>
       </c>
     </row>
     <row r="19">
@@ -2433,46 +2491,46 @@
         <v>67.312</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>0.964497056957299</v>
+        <v>-3.60194042850845</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>71.2624410426159</v>
+        <v>71.773604132509</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>72.4997022115714</v>
+        <v>72.7281771398254</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>72.9869004900367</v>
+        <v>73.1506476110616</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>69.7897412070383</v>
+        <v>70.9139404285085</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>69.7897412070383</v>
+        <v>70.9139404285085</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>69.7897412070383</v>
+        <v>70.9139404285085</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>69.7897412070383</v>
+        <v>70.9139404285085</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.0668471860708051</v>
+        <v>-0.0494037366014774</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>-0.0640648391457072</v>
+        <v>-0.0582280605161644</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>-0.0646618768900022</v>
+        <v>-0.0482032230809272</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>0.979334137113029</v>
+        <v>0.988022564640708</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>0.962621073992487</v>
+        <v>0.975054555432774</v>
       </c>
     </row>
     <row r="20">
@@ -2492,46 +2550,46 @@
         <v>73.631</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1.00754527372149</v>
+        <v>1.02300702278084</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>73.1133383085661</v>
+        <v>73.1003335987384</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>72.3443376882604</v>
+        <v>72.618301917371</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>72.5659129221763</v>
+        <v>72.7606891281534</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>73.0795944563712</v>
+        <v>72.6079929772192</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>73.0795944563712</v>
+        <v>72.6079929772192</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>73.0795944563712</v>
+        <v>72.6079929772192</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>73.0795944563712</v>
+        <v>72.6079929772192</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>0.0460621573282948</v>
+        <v>0.0236079766703811</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>-0.0659219888363545</v>
+        <v>-0.0698341895764206</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>0.0471394963275935</v>
+        <v>0.0238888508870629</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>0.999538472008315</v>
+        <v>0.993264864915367</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>1.01016329393019</v>
+        <v>0.999858039366391</v>
       </c>
     </row>
     <row r="21">
@@ -2551,46 +2609,46 @@
         <v>81.065</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>1.05280539445225</v>
+        <v>4.33693813645305</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>76.3377333963455</v>
+        <v>75.7512015352095</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>72.1609660415428</v>
+        <v>72.4841746213377</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>72.1173226964827</v>
+        <v>72.3424089416345</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>76.9990355550716</v>
+        <v>76.7280618635469</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>76.9990355550716</v>
+        <v>76.7280618635469</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>76.9990355550716</v>
+        <v>76.7280618635469</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>76.9990355550716</v>
+        <v>76.7280618635469</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>0.0522437143327623</v>
+        <v>0.0551924948205718</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>0.0269011861661175</v>
+        <v>0.0294395748447649</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>0.0536324965656498</v>
+        <v>0.0567440128474623</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>1.00866284770721</v>
+        <v>1.0128956413699</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.06704552029893</v>
+        <v>1.05854915592789</v>
       </c>
     </row>
     <row r="22">
@@ -2610,46 +2668,46 @@
         <v>71.81</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>0.975632561427039</v>
+        <v>-1.89950308605178</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>72.0695198888046</v>
+        <v>73.072992233864</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>71.9546452562309</v>
+        <v>72.3306130394813</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>71.6624009524331</v>
+        <v>71.9150007485481</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>73.6035294834409</v>
+        <v>73.7095030860518</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>73.6035294834409</v>
+        <v>73.7095030860518</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>73.6035294834409</v>
+        <v>73.7095030860518</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>73.6035294834409</v>
+        <v>73.7095030860518</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>-0.0450999169933474</v>
+        <v>-0.0401357729903033</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>-0.0135486114344553</v>
+        <v>-0.0106815804949036</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>-0.0440980337890362</v>
+        <v>-0.0393410012475404</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>1.02128513686511</v>
+        <v>1.00871061705193</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.02291560498059</v>
+        <v>1.01906371297887</v>
       </c>
     </row>
     <row r="23">
@@ -2669,46 +2727,46 @@
         <v>60.116</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>0.961648945592258</v>
+        <v>-3.35581464363786</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.677698236998949</v>
+        <v>0.180825615367491</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>67.5294802720037</v>
+        <v>69.4817640881192</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>71.7334571105826</v>
+        <v>72.165087389084</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>71.2468273937976</v>
+        <v>71.5195865105471</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>62.5134569902491</v>
+        <v>63.4718146436379</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>64.1301301372129</v>
+        <v>68.3950112814934</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>64.1301301372129</v>
+        <v>68.3950112814934</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>64.1301301372129</v>
+        <v>68.3950112814934</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>-0.137778677092379</v>
+        <v>-0.0748318462182698</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>-0.0810951720401942</v>
+        <v>-0.0355209304657742</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>-0.128708492822471</v>
+        <v>-0.0721004969787146</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.949661242451468</v>
+        <v>0.984359165014181</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.894005847764334</v>
+        <v>0.947757617374397</v>
       </c>
     </row>
     <row r="24">
@@ -2728,46 +2786,46 @@
         <v>70.882</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1.01250586835793</v>
+        <v>0.999772545036831</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>67.1057098732719</v>
+        <v>67.6823080963583</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>71.506513935498</v>
+        <v>71.995929693707</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>70.9259873670014</v>
+        <v>71.2062607009718</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>70.0065078288935</v>
+        <v>69.8822274549632</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>70.0065078288935</v>
+        <v>69.8822274549632</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>70.0065078288935</v>
+        <v>69.8822274549632</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>70.0065078288935</v>
+        <v>69.8822274549632</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>0.0876739042814974</v>
+        <v>0.0215114726990606</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>-0.0420512271631772</v>
+        <v>-0.0375408465444182</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>0.0916320874307823</v>
+        <v>0.0217445124374478</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>1.04322728961663</v>
+        <v>1.03250361018234</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>0.979022804720174</v>
+        <v>0.970641364758589</v>
       </c>
     </row>
     <row r="25">
@@ -2787,46 +2845,46 @@
         <v>68.268</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>1.04980968492316</v>
+        <v>4.20684130278836</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>65.3550341463041</v>
+        <v>64.6807546359221</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>71.2781759825188</v>
+        <v>71.8291156793445</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>70.7196827321865</v>
+        <v>71.0094949170175</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>65.0289295102063</v>
+        <v>64.0611586972116</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>65.0289295102063</v>
+        <v>64.0611586972116</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>65.0289295102063</v>
+        <v>64.0611586972116</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>65.0289295102063</v>
+        <v>64.0611586972116</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>-0.0737559664427799</v>
+        <v>-0.0869731284824681</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>-0.155457869810643</v>
+        <v>-0.165088272252492</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>-0.0711016514472221</v>
+        <v>-0.0832982715312419</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>0.995010259877337</v>
+        <v>0.990420706403349</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>0.912325948494457</v>
+        <v>0.891855038048775</v>
       </c>
     </row>
     <row r="26">
@@ -2846,46 +2904,46 @@
         <v>60.373</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>0.976930973658572</v>
+        <v>-1.99589336423896</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>63.6715498154739</v>
+        <v>63.784166851944</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>71.0518659993699</v>
+        <v>71.6693000080912</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>70.6431179518046</v>
+        <v>70.9571405896491</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>61.798634323063</v>
+        <v>62.368893364239</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>61.798634323063</v>
+        <v>62.368893364239</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>61.798634323063</v>
+        <v>62.368893364239</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>61.798634323063</v>
+        <v>62.368893364239</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>-0.0509509743822635</v>
+        <v>-0.0267715844013148</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>-0.160384906039508</v>
+        <v>-0.153855462959414</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>-0.049674740326707</v>
+        <v>-0.0264164021910883</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>0.970584735288543</v>
+        <v>0.977811523493124</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>0.869767928735483</v>
+        <v>0.870231652286234</v>
       </c>
     </row>
     <row r="27">
@@ -2905,46 +2963,46 @@
         <v>65.695</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>0.956942884521846</v>
+        <v>-3.2126445275933</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>66.5373601250488</v>
+        <v>66.9690334643461</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>70.8271009547312</v>
+        <v>71.5162823689281</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>70.6830437221976</v>
+        <v>71.0423074687327</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>68.6509101667292</v>
+        <v>68.9076445275933</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>68.6509101667292</v>
+        <v>68.9076445275933</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>68.6509101667292</v>
+        <v>68.9076445275933</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>68.6509101667292</v>
+        <v>68.9076445275933</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.105153124312192</v>
+        <v>0.099700475615761</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.0704938539785223</v>
+        <v>0.00749518475828737</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.110880700176071</v>
+        <v>0.104839942007108</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>1.03176486169136</v>
+        <v>1.02894787281467</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>0.969274603101532</v>
+        <v>0.963523861211385</v>
       </c>
     </row>
     <row r="28">
@@ -2964,46 +3022,46 @@
         <v>69.771</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1.01983930041831</v>
+        <v>1.26605176420736</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>69.2910760240662</v>
+        <v>69.3929226336838</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>70.5976145474849</v>
+        <v>71.3640496966837</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>70.7819883215634</v>
+        <v>71.2151640680073</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>68.4137196628742</v>
+        <v>68.5049482357926</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>68.4137196628742</v>
+        <v>68.5049482357926</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>68.4137196628742</v>
+        <v>68.5049482357926</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>68.4137196628742</v>
+        <v>68.5049482357926</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.00346100581771686</v>
+        <v>-0.0058611432405212</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>-0.022752001426957</v>
+        <v>-0.0197085764053263</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.00345502344075233</v>
+        <v>-0.00584400024933951</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>0.987338104536185</v>
+        <v>0.987203674896665</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>0.969065599473736</v>
+        <v>0.959936389918411</v>
       </c>
     </row>
     <row r="29">
@@ -3023,46 +3081,46 @@
         <v>64.776</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1.04733418464806</v>
+        <v>3.92168032399593</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>73.4769330155893</v>
+        <v>72.9258826855314</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>70.3557803572706</v>
+        <v>71.204958527536</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>70.8723193603227</v>
+        <v>71.4152055865061</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>61.8484538645771</v>
+        <v>60.8543196760041</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>73.4769330155893</v>
+        <v>72.9258826855314</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>73.4769330155893</v>
+        <v>72.9258826855314</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>73.4769330155893</v>
+        <v>72.9258826855314</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.0713981360575742</v>
+        <v>0.0625376400207069</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.12991146508197</v>
+        <v>0.138379076629247</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.0740087423643292</v>
+        <v>0.0645345272654174</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>1.04436241972542</v>
+        <v>1.02416859996246</v>
       </c>
     </row>
     <row r="30">
@@ -3082,46 +3140,46 @@
         <v>87.046</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.973786346281587</v>
+        <v>-2.24836873564253</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>80.9021230717373</v>
+        <v>79.6195208608723</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>70.0926070294252</v>
+        <v>71.0295784592495</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>70.8745631056029</v>
+        <v>71.5683761441014</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>89.3892180069951</v>
+        <v>89.2943687356425</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>80.9021230717373</v>
+        <v>79.6195208608723</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>80.9021230717373</v>
+        <v>79.6195208608723</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>80.9021230717373</v>
+        <v>79.6195208608723</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.0962685464420445</v>
+        <v>0.0878156800315157</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.309124772058999</v>
+        <v>0.276590245010255</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.101054708619542</v>
+        <v>0.0917868653603411</v>
       </c>
       <c r="R30" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.15421763436156</v>
+        <v>1.12093472308231</v>
       </c>
     </row>
     <row r="31">
@@ -3141,46 +3199,46 @@
         <v>79.367</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.957286471188581</v>
+        <v>-2.91035804233687</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>80.3823688189479</v>
+        <v>80.3621953853648</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>69.8010539296968</v>
+        <v>70.8295546671877</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>70.7222688928075</v>
+        <v>71.6081732461605</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>82.9083063311829</v>
+        <v>82.2773580423369</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>82.9083063311829</v>
+        <v>82.2773580423369</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>82.9083063311829</v>
+        <v>82.2773580423369</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>82.9083063311829</v>
+        <v>82.2773580423369</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>0.0244951872391999</v>
+        <v>0.0328366551847407</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>0.207679637893037</v>
+        <v>0.194023661763534</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>0.0247976589893288</v>
+        <v>0.0333817279070154</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>1.03142402431464</v>
+        <v>1.02383163685099</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>1.1877801503497</v>
+        <v>1.16162466965859</v>
       </c>
     </row>
     <row r="32">
@@ -3200,46 +3258,46 @@
         <v>72.42</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1.02486955691656</v>
+        <v>1.44776848718309</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>1</v>
+        <v>0.469214335666847</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>73.8346136294738</v>
+        <v>74.9258624684921</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>69.4808363713602</v>
+        <v>70.6019010407151</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>70.3991238571708</v>
+        <v>71.5083501216346</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>70.6626511747349</v>
+        <v>70.9722315128169</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>70.6626511747349</v>
+        <v>73.0707621461531</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>70.6626511747349</v>
+        <v>73.0707621461531</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>70.6626511747349</v>
+        <v>73.0707621461531</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>-0.159818092730073</v>
+        <v>-0.118667638809765</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>0.0328725221043802</v>
+        <v>0.0666494031153051</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>-0.14770118578387</v>
+        <v>-0.111897077339873</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.957039628179585</v>
+        <v>0.97524085460986</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>1.01700921959342</v>
+        <v>1.03496876244188</v>
       </c>
     </row>
     <row r="33">
@@ -3259,46 +3317,46 @@
         <v>74.787</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>1.04464521702317</v>
+        <v>3.70593289906636</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>70.1371432255077</v>
+        <v>70.6938261453214</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>69.1398617004409</v>
+        <v>70.3507863463055</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>69.9497453211189</v>
+        <v>71.2960059234558</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>71.5908126331289</v>
+        <v>71.0810671009337</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>71.5908126331289</v>
+        <v>71.0810671009337</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>71.5908126331289</v>
+        <v>71.0810671009337</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>71.5908126331289</v>
+        <v>71.0810671009337</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>0.0130495891633581</v>
+        <v>-0.0276073002565941</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>-0.0256695578469538</v>
+        <v>-0.0252971306847654</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>0.0131351066364438</v>
+        <v>-0.0272297015492973</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>1.02072609947838</v>
+        <v>1.00547771957931</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>1.03544917320354</v>
+        <v>1.0103805627848</v>
       </c>
     </row>
     <row r="34">
@@ -3318,46 +3376,46 @@
         <v>67.608</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.970692093772089</v>
+        <v>-2.37781945757</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>70.3109561793057</v>
+        <v>69.7386275447147</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>68.7867758972167</v>
+        <v>70.0819223886239</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>69.4200682436658</v>
+        <v>71.0060518646787</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>69.6492744030465</v>
+        <v>69.98581945757</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>69.6492744030465</v>
+        <v>69.98581945757</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>69.6492744030465</v>
+        <v>69.98581945757</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>69.6492744030465</v>
+        <v>69.98581945757</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>-0.0274944681417508</v>
+        <v>-0.0155283734988319</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>-0.139092130607162</v>
+        <v>-0.120996726671293</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>-0.0271199356268221</v>
+        <v>-0.0154084299523588</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>0.990589208109021</v>
+        <v>1.00354454800099</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>1.01253872557014</v>
+        <v>0.998628705837706</v>
       </c>
     </row>
     <row r="35">
@@ -3377,46 +3435,46 @@
         <v>65.8</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.959293963385697</v>
+        <v>-2.9057214023125</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>67.635381588617</v>
+        <v>69.0435753646102</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>68.4317567862982</v>
+        <v>69.8014773978066</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>68.8642329203854</v>
+        <v>70.6723244642455</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>68.5921130659135</v>
+        <v>68.7057214023125</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>68.5921130659135</v>
+        <v>68.7057214023125</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>68.5921130659135</v>
+        <v>68.7057214023125</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>68.5921130659135</v>
+        <v>68.7057214023125</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>-0.0152947241743353</v>
+        <v>-0.0184601656239705</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.172675017724792</v>
+        <v>-0.164949835081493</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>-0.015178353919604</v>
+        <v>-0.0182908204144639</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>1.01414542883953</v>
+        <v>0.995106656042745</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>1.00234330210338</v>
+        <v>0.984301822306006</v>
       </c>
     </row>
     <row r="36">
@@ -3424,58 +3482,58 @@
         <v>86</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>64.9615176352199</v>
+        <v>71.3555</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>64.9615176352199</v>
+        <v>71.3555</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>64.9615176352199</v>
+        <v>71.3555</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>64.9615176352199</v>
+        <v>71.3555</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>1.02849165729193</v>
+        <v>1.81983210157665</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>63.4671404803479</v>
+        <v>69.6424265348203</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>68.0855212538621</v>
+        <v>69.5155595396582</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>68.3375256776488</v>
+        <v>70.3235590790626</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>63.1619295836263</v>
+        <v>69.5356678984234</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>63.1619295836263</v>
+        <v>69.5356678984234</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>63.1619295836263</v>
+        <v>69.5356678984234</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>63.1619295836263</v>
+        <v>69.5356678984234</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>-0.0824758185944835</v>
+        <v>0.0120073513706603</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>-0.106148318332422</v>
+        <v>-0.0483790526320087</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>-0.0791662953591924</v>
+        <v>0.0120797290119559</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>0.99519104068008</v>
+        <v>0.998467045998985</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>0.92768518798765</v>
+        <v>1.00028926414314</v>
       </c>
     </row>
     <row r="37">
@@ -3483,58 +3541,58 @@
         <v>87</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>63.6977885083287</v>
+        <v>73.692</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>63.6977885083287</v>
+        <v>73.692</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>63.6977885083287</v>
+        <v>73.692</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>63.6977885083287</v>
+        <v>73.692</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1.04198668420303</v>
+        <v>3.52269529165224</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>62.540282225958</v>
+        <v>69.6052075423512</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>67.7588864087601</v>
+        <v>69.2295921324862</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>67.8938722425545</v>
+        <v>69.9786580507268</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>61.1310964660248</v>
+        <v>70.1693047083478</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>61.1310964660248</v>
+        <v>70.1693047083478</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>61.1310964660248</v>
+        <v>70.1693047083478</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>61.1310964660248</v>
+        <v>70.1693047083478</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>-0.0326810591361281</v>
+        <v>0.0090711324445952</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.146104168710942</v>
+        <v>-0.0128270780078641</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>-0.0321528036111158</v>
+        <v>0.0091123998528353</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>0.977467550356715</v>
+        <v>1.00810423797175</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>0.902185671961125</v>
+        <v>1.0135738568857</v>
       </c>
     </row>
     <row r="38">
@@ -3542,58 +3600,58 @@
         <v>88</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>71.5901850867734</v>
+        <v>64.2905</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>71.5901850867734</v>
+        <v>64.2905</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>71.5901850867734</v>
+        <v>64.2905</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>71.5901850867734</v>
+        <v>64.2905</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.965065670422907</v>
+        <v>-2.55582664169619</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>63.6501246146644</v>
+        <v>66.5456173208621</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>67.4595921150498</v>
+        <v>68.949011062322</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>67.5613203617309</v>
+        <v>69.6525842649319</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>74.1816720673542</v>
+        <v>66.8463266416962</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>63.6501246146644</v>
+        <v>66.8463266416962</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>63.6501246146644</v>
+        <v>66.8463266416962</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>63.6501246146644</v>
+        <v>66.8463266416962</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>0.0403806023053677</v>
+        <v>-0.0485146077670344</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>-0.086133701173486</v>
+        <v>-0.0448589848658869</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>0.0412069845670056</v>
+        <v>-0.0473565767889995</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1</v>
+        <v>1.00451884486072</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.943529639285567</v>
+        <v>0.96950377694721</v>
       </c>
     </row>
     <row r="39">
@@ -3613,46 +3671,46 @@
         <v>60.527</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.967836177588772</v>
+        <v>-2.96189467355596</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>64.8679299529621</v>
+        <v>64.9219803091866</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>67.1912358680745</v>
+        <v>68.6798395355573</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>67.3341039029239</v>
+        <v>69.3612538406596</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>62.5384764504201</v>
+        <v>63.488894673556</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>62.5384764504201</v>
+        <v>63.488894673556</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>62.5384764504201</v>
+        <v>63.488894673556</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>62.5384764504201</v>
+        <v>63.488894673556</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>-0.0176192922815618</v>
+        <v>-0.0515313492005937</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>-0.088255578446405</v>
+        <v>-0.0759300189602687</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>-0.0174649801704899</v>
+        <v>-0.0502261251562323</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>0.964089288740504</v>
+        <v>0.977926033235498</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.930753477629287</v>
+        <v>0.924418215052558</v>
       </c>
     </row>
     <row r="40">
@@ -3672,46 +3730,46 @@
         <v>70.291</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>1.02767719098542</v>
+        <v>2.17645566105495</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>67.5494329301342</v>
+        <v>67.1653364608063</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>66.9550342459901</v>
+        <v>68.4267865808206</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>67.1869007551437</v>
+        <v>69.1065516087754</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>68.3979372283229</v>
+        <v>68.1145443389451</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>68.3979372283229</v>
+        <v>68.1145443389451</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>68.3979372283229</v>
+        <v>68.1145443389451</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>68.3979372283229</v>
+        <v>68.1145443389451</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.0895606761622531</v>
+        <v>0.0703257600375388</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>0.0828981584193722</v>
+        <v>-0.0204373324141254</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0936936924350593</v>
+        <v>0.0728576184728531</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>1.01256123495613</v>
+        <v>1.01413240710396</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>1.02155032849407</v>
+        <v>0.995436841952138</v>
       </c>
     </row>
     <row r="41">
@@ -3731,46 +3789,46 @@
         <v>72.597</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>1.03760288885753</v>
+        <v>3.37345034094563</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>68.671105163549</v>
+        <v>68.9133199337248</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>66.7492958523161</v>
+        <v>68.1913168862019</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>67.0704106701385</v>
+        <v>68.8610006043095</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>69.9660735138605</v>
+        <v>69.2235496590544</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>69.9660735138605</v>
+        <v>69.2235496590544</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>69.9660735138605</v>
+        <v>69.2235496590544</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>69.9660735138605</v>
+        <v>69.2235496590544</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.0226677937809504</v>
+        <v>0.016150354111357</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>0.144525087207392</v>
+        <v>-0.0134781875525819</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0229266604971274</v>
+        <v>0.0162814760176739</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>1.01885754346355</v>
+        <v>1.00450173820718</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>1.04819193401922</v>
+        <v>1.0151373051583</v>
       </c>
     </row>
     <row r="42">
@@ -3790,46 +3848,46 @@
         <v>60.973</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0.961793666461227</v>
+        <v>-2.58139585949253</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>0.561611679840248</v>
+        <v>0</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>66.7025273869377</v>
+        <v>68.8985050295476</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>66.5732311049362</v>
+        <v>67.9746999883897</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>66.9413885820221</v>
+        <v>68.5921638259427</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>63.3950941103</v>
+        <v>63.5543958594925</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>64.8450342284857</v>
+        <v>68.8985050295476</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>64.8450342284857</v>
+        <v>68.8985050295476</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>64.8450342284857</v>
+        <v>68.8985050295476</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>-0.0760101258356764</v>
+        <v>-0.00470663762255227</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.0187730915069722</v>
+        <v>0.030699942554081</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>-0.0731931781817133</v>
+        <v>-0.00469557876051885</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>0.9721525820502</v>
+        <v>1</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>0.974040663976089</v>
+        <v>1.01359042469206</v>
       </c>
     </row>
     <row r="43">
@@ -3849,46 +3907,46 @@
         <v>67.704</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.978700616175723</v>
+        <v>-3.122985921293</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>69.8039581916106</v>
+        <v>70.9964685271024</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>66.4280609077725</v>
+        <v>67.7788505695559</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>66.7710677391269</v>
+        <v>68.2694170176297</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>69.1774367779124</v>
+        <v>70.826985921293</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>69.1774367779124</v>
+        <v>70.826985921293</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>69.1774367779124</v>
+        <v>70.826985921293</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>69.1774367779124</v>
+        <v>70.826985921293</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0646744166940896</v>
+        <v>0.0276056050583218</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.10615801190417</v>
+        <v>0.115580705656755</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0668116317767871</v>
+        <v>0.0279901703370538</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>0.991024557490301</v>
+        <v>0.997612802307981</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.04138877204254</v>
+        <v>1.04497177697944</v>
       </c>
     </row>
     <row r="44">
@@ -3908,46 +3966,46 @@
         <v>77.328</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>1.02379211032543</v>
+        <v>2.49284540569968</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>1</v>
+        <v>0.594629495901702</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>72.5985210695746</v>
+        <v>72.5567097031106</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>66.3139260416992</v>
+        <v>67.606260690023</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>66.5201996180176</v>
+        <v>67.8636676293431</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>75.5309590883836</v>
+        <v>74.8351545943003</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>75.5309590883836</v>
+        <v>73.9115402401985</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>75.5309590883836</v>
+        <v>73.9115402401985</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>75.5309590883836</v>
+        <v>73.9115402401985</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>0.0878678750240646</v>
+        <v>0.0426288908234374</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.104287090358435</v>
+        <v>0.0851065797696164</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>0.0918438526548564</v>
+        <v>0.0435505517957986</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.04039253108199</v>
+        <v>1.01867271190537</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.13899091181675</v>
+        <v>1.09326472852988</v>
       </c>
     </row>
     <row r="45">
@@ -3967,46 +4025,46 @@
         <v>70.704</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>1.03273630113406</v>
+        <v>3.21274894966836</v>
       </c>
       <c r="G45" s="7" t="n">
-        <v>0.887611202627428</v>
+        <v>0</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>72.4066522879672</v>
+        <v>72.9692876901181</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>66.2326856475096</v>
+        <v>67.4613274947081</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>66.161567540453</v>
+        <v>67.3586109555739</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>68.4627817598346</v>
+        <v>67.4912510503316</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>68.9060286254846</v>
+        <v>72.9692876901181</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>68.9060286254846</v>
+        <v>72.9692876901181</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>68.9060286254846</v>
+        <v>72.9692876901181</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>-0.0917989539718495</v>
+        <v>-0.0128303399329956</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>-0.0151508414741318</v>
+        <v>0.0541107477081506</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>-0.087711456902683</v>
+        <v>-0.0127483820120419</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>0.951653286654376</v>
+        <v>1</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>1.04036289562834</v>
+        <v>1.08164618752636</v>
       </c>
     </row>
     <row r="46">
@@ -4026,46 +4084,46 @@
         <v>70.836</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>0.960234750068097</v>
+        <v>-2.86174445446524</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>70.7206011915356</v>
+        <v>72.1620946686617</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>66.1919595116508</v>
+        <v>67.3523889282474</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>65.7130086255436</v>
+        <v>66.7681816538673</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>73.7694610562433</v>
+        <v>73.6977444544652</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>73.7694610562433</v>
+        <v>73.6977444544652</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>73.7694610562433</v>
+        <v>73.6977444544652</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>73.7694610562433</v>
+        <v>73.6977444544652</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.068201166754105</v>
+        <v>0.00993355826132262</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.137626989235781</v>
+        <v>0.0696566554362748</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.0705806520528454</v>
+        <v>0.00998305982430181</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>1.04311133974173</v>
+        <v>1.02128056000667</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.11447767373103</v>
+        <v>1.09421129119826</v>
       </c>
     </row>
     <row r="47">
@@ -4085,46 +4143,46 @@
         <v>65.703</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>0.988802056461974</v>
+        <v>-2.58345077390571</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>68.2136154442369</v>
+        <v>68.7703557166892</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>66.2010382599316</v>
+        <v>67.2912254103993</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>65.2060822978251</v>
+        <v>66.1343677654413</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>66.4470705442214</v>
+        <v>68.2864507739057</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>66.4470705442214</v>
+        <v>68.2864507739057</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>66.4470705442214</v>
+        <v>68.2864507739057</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>66.4470705442214</v>
+        <v>68.2864507739057</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>-0.104539140064604</v>
+        <v>-0.0762608255400355</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>-0.0394690286437841</v>
+        <v>-0.0358695928443216</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>-0.099260458286921</v>
+        <v>-0.0734254992553122</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.974102752236325</v>
+        <v>0.992963466049572</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.00371644147519</v>
+        <v>1.01478982374651</v>
       </c>
     </row>
     <row r="48">
@@ -4144,46 +4202,46 @@
         <v>65.884</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>1.02078202869318</v>
+        <v>2.49945320480183</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>64.1034922354005</v>
+        <v>63.6670962878137</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>66.2739484566259</v>
+        <v>67.2935832081259</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>64.7126302439866</v>
+        <v>65.5338051455169</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>64.5426723316688</v>
+        <v>63.3845467951982</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>64.5426723316688</v>
+        <v>63.3845467951982</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>64.5426723316688</v>
+        <v>63.3845467951982</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>64.5426723316688</v>
+        <v>63.3845467951982</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>-0.0290791074868498</v>
+        <v>-0.074491278437148</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>-0.145480567032874</v>
+        <v>-0.142426925630147</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>-0.0286603788091043</v>
+        <v>-0.0717844304858894</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>1.00685111030543</v>
+        <v>0.995562079801186</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.973876973301353</v>
+        <v>0.941910710849831</v>
       </c>
     </row>
     <row r="49">
@@ -4203,46 +4261,46 @@
         <v>63.259</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>1.02588987052044</v>
+        <v>2.54314280657209</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>60.939821014473</v>
+        <v>60.0926128193624</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>66.4248704361852</v>
+        <v>67.3758306042417</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>64.3106990919494</v>
+        <v>65.0538900643574</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>61.6625641969818</v>
+        <v>60.7158571934279</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>61.6625641969818</v>
+        <v>60.7158571934279</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>61.6625641969818</v>
+        <v>60.7158571934279</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>61.6625641969818</v>
+        <v>60.7158571934279</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>-0.0456495839255334</v>
+        <v>-0.0430151876127464</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>-0.10512090992607</v>
+        <v>-0.167925861476507</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>-0.0446233171116123</v>
+        <v>-0.04210315820973</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>1.01185994921674</v>
+        <v>1.01037139749505</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>0.928305374057469</v>
+        <v>0.901151891545</v>
       </c>
     </row>
     <row r="50">
@@ -4262,46 +4320,46 @@
         <v>55.23</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>0.962291375179988</v>
+        <v>-2.9261516490117</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>58.626697908553</v>
+        <v>59.1570278649809</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>66.666902485483</v>
+        <v>67.5518927338027</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>64.0774856800729</v>
+        <v>64.7712725004744</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>57.3942585629739</v>
+        <v>58.1561516490117</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>57.3942585629739</v>
+        <v>58.1561516490117</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>57.3942585629739</v>
+        <v>58.1561516490117</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>57.3942585629739</v>
+        <v>58.1561516490117</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>-0.0717327343744109</v>
+        <v>-0.0430732400297098</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>-0.221978068685964</v>
+        <v>-0.210882882786949</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>-0.0692203720294978</v>
+        <v>-0.0421587648225328</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>0.978978189296941</v>
+        <v>0.983081026006689</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.860910833160005</v>
+        <v>0.860910764975659</v>
       </c>
     </row>
     <row r="51">
@@ -4321,46 +4379,46 @@
         <v>60.865</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0.995040871419785</v>
+        <v>-1.20419465106803</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>61.0299908807346</v>
+        <v>61.7376322731934</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>67.0101664499933</v>
+        <v>67.8315322484837</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>64.0769461722419</v>
+        <v>64.7409122680251</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>61.1683416713869</v>
+        <v>62.069194651068</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>61.1683416713869</v>
+        <v>62.069194651068</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>61.1683416713869</v>
+        <v>62.069194651068</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>61.1683416713869</v>
+        <v>62.069194651068</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>0.0636854894375426</v>
+        <v>0.0651181428012072</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>-0.0794426124372394</v>
+        <v>-0.0910467018328837</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>0.0657571541632862</v>
+        <v>0.0672851089885145</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.0022669312031</v>
+        <v>1.00537050686375</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.912821813642772</v>
+        <v>0.915049278611211</v>
       </c>
     </row>
     <row r="52">
@@ -4380,46 +4438,46 @@
         <v>66.823</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>1.01816603311418</v>
+        <v>1.63523015734154</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>65.5837196849409</v>
+        <v>65.0294640210303</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>67.4589887727385</v>
+        <v>68.2186394617809</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>64.3396205967558</v>
+        <v>64.984693576909</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>65.6307496289323</v>
+        <v>65.1877698426585</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>65.6307496289323</v>
+        <v>65.1877698426585</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>65.6307496289323</v>
+        <v>65.1877698426585</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>65.6307496289323</v>
+        <v>65.1877698426585</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>0.0704145677422846</v>
+        <v>0.0490220667456083</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0.0168582622620927</v>
+        <v>0.0284489380871757</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>0.0729529007263052</v>
+        <v>0.0502435259410403</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.00071709784406</v>
+        <v>1.0024343706966</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.972898509493445</v>
+        <v>0.955571239135889</v>
       </c>
     </row>
     <row r="53">
@@ -4439,46 +4497,46 @@
         <v>66.726</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.0216557995829</v>
+        <v>1.96577532019653</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>63.7274026560931</v>
+        <v>64.5934452343711</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>68.0140447562545</v>
+        <v>68.7135032261929</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>64.8815059594093</v>
+        <v>65.5111420489413</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>65.3116245483474</v>
+        <v>64.7602246798035</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>65.3116245483474</v>
+        <v>64.7602246798035</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>65.3116245483474</v>
+        <v>64.7602246798035</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>65.3116245483474</v>
+        <v>64.7602246798035</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>-0.00487429244236058</v>
+        <v>-0.00658027401116443</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.0591778885436645</v>
+        <v>0.0666113874253815</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>-0.00486243235662054</v>
+        <v>-0.00655867141776645</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1.02485935133436</v>
+        <v>1.00258198714788</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.960266732884481</v>
+        <v>0.942467224624309</v>
       </c>
     </row>
     <row r="54">
@@ -4498,46 +4556,46 @@
         <v>61.185</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0.963799279956766</v>
+        <v>-2.9802906444212</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>0.106131922755929</v>
+        <v>0.521424122701073</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>56.2981789474902</v>
+        <v>58.9265629239773</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>68.6748670536122</v>
+        <v>69.3145181007057</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>65.7250549111585</v>
+        <v>66.3297986872655</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>63.4831352050238</v>
+        <v>64.1652906444212</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>57.0607321700195</v>
+        <v>61.6581619296796</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>57.0607321700195</v>
+        <v>61.6581619296796</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>57.0607321700195</v>
+        <v>61.6581619296796</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>-0.135053860740689</v>
+        <v>-0.0490859859806829</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>-0.00581114559722906</v>
+        <v>0.0602173662006291</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>-0.126331146030828</v>
+        <v>-0.047900741009803</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>1.01354490032867</v>
+        <v>1.04635598735372</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.830882309906389</v>
+        <v>0.889541810564096</v>
       </c>
     </row>
     <row r="55">
@@ -4557,46 +4615,46 @@
         <v>33.184</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.999101251983326</v>
+        <v>0.454780375040798</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>53.4514464478671</v>
+        <v>55.6162506443746</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>69.4392993052527</v>
+        <v>70.0176078452138</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>66.8948706959036</v>
+        <v>67.4464499081796</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>33.2138508826068</v>
+        <v>32.7292196249592</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>53.4514464478671</v>
+        <v>55.6162506443746</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>53.4514464478671</v>
+        <v>55.6162506443746</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>53.4514464478671</v>
+        <v>55.6162506443746</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>-0.0653424784792313</v>
+        <v>-0.10313017591704</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>-0.12615832001752</v>
+        <v>-0.103963714093113</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>-0.063253407113636</v>
+        <v>-0.0979904540812566</v>
       </c>
       <c r="R55" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.769757860212506</v>
+        <v>0.794318063069565</v>
       </c>
     </row>
     <row r="56">
@@ -4616,46 +4674,46 @@
         <v>75.79</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>1.01732292902141</v>
+        <v>0.707607099327488</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>61.5709560840207</v>
+        <v>62.15558365929</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>70.2979263173145</v>
+        <v>70.8139109970052</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>68.3722349438399</v>
+        <v>68.8435239441938</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>74.4994512931154</v>
+        <v>75.0823929006725</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>61.5709560840207</v>
+        <v>62.15558365929</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>61.5709560840207</v>
+        <v>62.15558365929</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>61.5709560840207</v>
+        <v>62.15558365929</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>0.14141656840465</v>
+        <v>0.111165219254917</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>-0.0618581010862315</v>
+        <v>-0.0465146482336662</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>0.151904395030223</v>
+        <v>0.117579537260246</v>
       </c>
       <c r="R56" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>0.875857358951081</v>
+        <v>0.877731264721683</v>
       </c>
     </row>
     <row r="57">
@@ -4675,46 +4733,46 @@
         <v>74.809</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.01526920815817</v>
+        <v>1.05862670455717</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>71.9614237675229</v>
+        <v>72.4931676914316</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>71.2313404879006</v>
+        <v>71.685565245117</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>70.0712121639217</v>
+        <v>70.4442980314991</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>73.6839051148938</v>
+        <v>73.7503732954428</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>73.6839051148938</v>
+        <v>73.7503732954428</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>73.6839051148938</v>
+        <v>73.7503732954428</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>73.6839051148938</v>
+        <v>73.7503732954428</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.179594124349439</v>
+        <v>0.171045401257096</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.128189746074205</v>
+        <v>0.138822072654777</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.196731540344178</v>
+        <v>0.186544618416109</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.02393617659561</v>
+        <v>1.0173424012779</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>1.03443097673291</v>
+        <v>1.02880367955899</v>
       </c>
     </row>
     <row r="58">
@@ -4734,46 +4792,46 @@
         <v>74.937</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0.968404240931413</v>
+        <v>-2.55479362292513</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>79.1350621001862</v>
+        <v>78.6101144601967</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>72.214679858718</v>
+        <v>72.6092968240007</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>71.8718604708048</v>
+        <v>72.138609704862</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>77.3819411694495</v>
+        <v>77.4917936229251</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>77.3819411694495</v>
+        <v>77.4917936229251</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>77.3819411694495</v>
+        <v>77.4917936229251</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>77.3819411694495</v>
+        <v>77.4917936229251</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.048969043589562</v>
+        <v>0.049485985176001</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.35613298719828</v>
+        <v>0.256797011096498</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0501878401910079</v>
+        <v>0.0507308663034725</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.977846470525072</v>
+        <v>0.985773830187745</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.07155416766841</v>
+        <v>1.06724341114003</v>
       </c>
     </row>
     <row r="59">
@@ -4793,46 +4851,46 @@
         <v>83.357</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1.00357153446596</v>
+        <v>1.73193788945066</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>81.2804529924151</v>
+        <v>80.8127307163717</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>73.2246153243658</v>
+        <v>73.5631224731387</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>73.6723014438994</v>
+        <v>73.8328268753688</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>83.0603471075508</v>
+        <v>81.6250621105493</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>83.0603471075508</v>
+        <v>81.6250621105493</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>83.0603471075508</v>
+        <v>81.6250621105493</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>83.0603471075508</v>
+        <v>81.6250621105493</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0708139820430139</v>
+        <v>0.0519643065056285</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.553940120003342</v>
+        <v>0.467647695859294</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.073381539055305</v>
+        <v>0.0533381445232342</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>1.02189818153821</v>
+        <v>1.01005202258328</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.13432275116251</v>
+        <v>1.10959213484113</v>
       </c>
     </row>
     <row r="60">
@@ -4852,46 +4910,46 @@
         <v>78.522</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>1.01164127361513</v>
+        <v>-0.25010944521655</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>77.5425162685282</v>
+        <v>77.8990034711661</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>74.241047317762</v>
+        <v>74.5281104925132</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>75.3982070661094</v>
+        <v>75.460083373696</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>77.6184227037311</v>
+        <v>78.7721094452166</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>77.6184227037311</v>
+        <v>78.7721094452166</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>77.6184227037311</v>
+        <v>78.7721094452166</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>77.6184227037311</v>
+        <v>78.7721094452166</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>-0.0677626122028479</v>
+        <v>-0.035577355360507</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.260633708494176</v>
+        <v>0.26733761969015</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>-0.0655177180607401</v>
+        <v>-0.0349519202995382</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>1.0009789008515</v>
+        <v>1.01120817899004</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.04549202237831</v>
+        <v>1.05694494231314</v>
       </c>
     </row>
     <row r="61">
@@ -4911,46 +4969,46 @@
         <v>73.12</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>1.01279946876369</v>
+        <v>0.501953746419341</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>73.6470718255975</v>
+        <v>74.3896881932484</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>75.2500236041892</v>
+        <v>75.4903678943794</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>77.0221895486565</v>
+        <v>76.992474206696</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>72.1959304434239</v>
+        <v>72.6180462535807</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>72.1959304434239</v>
+        <v>72.6180462535807</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>72.1959304434239</v>
+        <v>72.6180462535807</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>72.1959304434239</v>
+        <v>72.6180462535807</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.072421125728069</v>
+        <v>-0.0813455312333038</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>-0.0201940256715466</v>
+        <v>-0.0153535092944694</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0698608921879901</v>
+        <v>-0.0781249002340841</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>0.980296007075338</v>
+        <v>0.976184307493461</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>0.959414057106085</v>
+        <v>0.961951150578343</v>
       </c>
     </row>
     <row r="62">
@@ -4970,46 +5028,46 @@
         <v>76.726</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>0.971628363548291</v>
+        <v>-2.01285499936331</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>80.7034623721746</v>
+        <v>80.0404364531006</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>76.2397028085464</v>
+        <v>76.4386541903382</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>78.5279621809507</v>
+        <v>78.4186545115791</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>78.9664061676876</v>
+        <v>78.7388549993633</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>78.9664061676876</v>
+        <v>78.7388549993633</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>78.9664061676876</v>
+        <v>78.7388549993633</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>78.9664061676876</v>
+        <v>78.7388549993633</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>0.0896388443831587</v>
+        <v>0.0809232819446324</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>0.0204759014091995</v>
+        <v>0.0160928185829119</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>0.093779187866682</v>
+        <v>0.0842877089313161</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>0.978476063437324</v>
+        <v>0.983738451320166</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>1.0357648739265</v>
+        <v>1.03009211547992</v>
       </c>
     </row>
     <row r="63">
@@ -5029,46 +5087,46 @@
         <v>91.187</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>1.00937320994157</v>
+        <v>2.08498106143275</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>1</v>
+        <v>0.922037217446325</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>84.4461636995231</v>
+        <v>83.53986037445</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>77.196334747507</v>
+        <v>77.3599336909649</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>79.875106956876</v>
+        <v>79.7054072857895</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>90.3402221317907</v>
+        <v>89.1020189385672</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>90.3402221317907</v>
+        <v>88.6683775799039</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>90.3402221317907</v>
+        <v>88.6683775799039</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>90.3402221317907</v>
+        <v>88.6683775799039</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>0.134560265421644</v>
+        <v>0.118766572068684</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>0.0876456128315177</v>
+        <v>0.0862886384063686</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>0.144033602592353</v>
+        <v>0.126107022773202</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1.06979663935048</v>
+        <v>1.06139006197121</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>1.17026569237095</v>
+        <v>1.14617959645769</v>
       </c>
     </row>
     <row r="64">
@@ -5088,46 +5146,46 @@
         <v>75.475</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1.00538559754956</v>
+        <v>-0.39541459860768</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>80.7289856946933</v>
+        <v>80.9571281533998</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>78.1078734273437</v>
+        <v>78.2426083323405</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>81.0253980902498</v>
+        <v>80.8211165292109</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>75.0706994251322</v>
+        <v>75.8704145986077</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>75.0706994251322</v>
+        <v>75.8704145986077</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>75.0706994251322</v>
+        <v>75.8704145986077</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>75.0706994251322</v>
+        <v>75.8704145986077</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>-0.185152460551386</v>
+        <v>-0.155876502014158</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.032823693008082</v>
+        <v>-0.0368365766391836</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>-0.169022417106556</v>
+        <v>-0.144335143267545</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.929910103281119</v>
+        <v>0.937167811274707</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.961115648539111</v>
+        <v>0.969681561181386</v>
       </c>
     </row>
     <row r="65">
@@ -5147,46 +5205,46 @@
         <v>82.884</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>1.00853438830215</v>
+        <v>-0.1155409895062</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>79.693377689031</v>
+        <v>80.3983028914141</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>78.9704877839446</v>
+        <v>79.0821478279765</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>81.9929353707644</v>
+        <v>81.7789810931971</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>82.1826215956144</v>
+        <v>82.9995409895062</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>82.1826215956144</v>
+        <v>82.9995409895062</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>82.1826215956144</v>
+        <v>82.9995409895062</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>82.1826215956144</v>
+        <v>82.9995409895062</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>0.0905135350847531</v>
+        <v>0.0898082636071736</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.138327618895591</v>
+        <v>0.142960259488028</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>0.0947363248903097</v>
+        <v>0.0939645107861233</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>1.03123526670304</v>
+        <v>1.03235439063441</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>1.04067511676587</v>
+        <v>1.04953574566603</v>
       </c>
     </row>
     <row r="66">
@@ -5206,46 +5264,46 @@
         <v>81.745</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>0.97733984697003</v>
+        <v>-1.34539606404486</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>84.0721786674758</v>
+        <v>83.7320024159884</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>79.7784485194464</v>
+        <v>79.8725392703009</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>82.7620450947862</v>
+        <v>82.5674463194491</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>83.6403020437851</v>
+        <v>83.0903960640449</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>83.6403020437851</v>
+        <v>83.0903960640449</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>83.6403020437851</v>
+        <v>83.0903960640449</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>83.6403020437851</v>
+        <v>83.0903960640449</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>0.0175816221911343</v>
+        <v>0.00109404681840183</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0.0591884081209457</v>
+        <v>0.0552654856959343</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>0.0177370886918569</v>
+        <v>0.00109464550593308</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>0.994863025669896</v>
+        <v>0.992337381963518</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>1.04840722771636</v>
+        <v>1.04028739818643</v>
       </c>
     </row>
     <row r="67">
@@ -5265,46 +5323,46 @@
         <v>86.53</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>1.01431046989733</v>
+        <v>1.84005996607998</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>85.8237974912842</v>
+        <v>85.3617320123648</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>80.528033919618</v>
+        <v>80.6102181224675</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>83.3180019898059</v>
+        <v>83.1810603491494</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>85.3091854693748</v>
+        <v>84.68994003392</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>85.3091854693748</v>
+        <v>84.68994003392</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>85.3091854693748</v>
+        <v>84.68994003392</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>85.3091854693748</v>
+        <v>84.68994003392</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>0.0197566471935214</v>
+        <v>0.0190676985148114</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>-0.0556898858968542</v>
+        <v>-0.0448687305956251</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>0.0199531013734986</v>
+        <v>0.0192506480368952</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>0.994003853978127</v>
+        <v>0.992130056846229</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>1.05937251062815</v>
+        <v>1.05061048098461</v>
       </c>
     </row>
     <row r="68">
@@ -5324,46 +5382,46 @@
         <v>87.103</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>0.999197362784522</v>
+        <v>-0.504065651025295</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>85.348395120769</v>
+        <v>85.5808361003216</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>81.2179359286811</v>
+        <v>81.2936310081266</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>83.6504720680593</v>
+        <v>83.6169860722035</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>87.172968268516</v>
+        <v>87.6070656510253</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>87.172968268516</v>
+        <v>87.6070656510253</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>87.172968268516</v>
+        <v>87.6070656510253</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>87.172968268516</v>
+        <v>87.6070656510253</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.021612152951762</v>
+        <v>0.0338648299387758</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>0.161211616996499</v>
+        <v>0.154693382321823</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.0218473871117935</v>
+        <v>0.0344447713144784</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.02137794325441</v>
+        <v>1.02367620653213</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>1.07332164098659</v>
+        <v>1.07766210666943</v>
       </c>
     </row>
     <row r="69">
@@ -5383,46 +5441,46 @@
         <v>82.518</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>1.0037853159849</v>
+        <v>0.0165012772788441</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>85.0096526053711</v>
+        <v>85.1091076031188</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>81.8498347105759</v>
+        <v>81.9237743771225</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>83.75907725918</v>
+        <v>83.8799307769408</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>82.2068212056225</v>
+        <v>82.5014987227212</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>82.2068212056225</v>
+        <v>82.5014987227212</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>82.2068212056225</v>
+        <v>82.5014987227212</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>82.2068212056225</v>
+        <v>82.5014987227212</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>-0.0586560042792648</v>
+        <v>-0.0600451932947384</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>0.000294461402402746</v>
+        <v>-0.0060005424228553</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>-0.0569688879653195</v>
+        <v>-0.0582780268961604</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>0.967029257103781</v>
+        <v>0.969361576524131</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>1.00436148095239</v>
+        <v>1.00705197422837</v>
       </c>
     </row>
     <row r="70">
@@ -5442,46 +5500,46 @@
         <v>86.718</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>0.982808795000903</v>
+        <v>-0.910281794523327</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>85.9291613994837</v>
+        <v>85.9232702493223</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>82.4291323244551</v>
+        <v>82.5055905759519</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>83.661051973804</v>
+        <v>83.9945521495847</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>88.2348636287085</v>
+        <v>87.6282817945233</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>88.2348636287085</v>
+        <v>87.6282817945233</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>88.2348636287085</v>
+        <v>87.6282817945233</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>88.2348636287085</v>
+        <v>87.6282817945233</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0707638824915434</v>
+        <v>0.0602873378610145</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.0549323887247346</v>
+        <v>0.0546138416163131</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0733277644686943</v>
+        <v>0.0621416962258197</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.02683259316946</v>
+        <v>1.01984342006832</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.07043300275685</v>
+        <v>1.06208901945688</v>
       </c>
     </row>
     <row r="71">
@@ -5501,46 +5559,46 @@
         <v>86.566</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>1.01951116089668</v>
+        <v>0.836692102040065</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>85.7562566895842</v>
+        <v>85.89391562648</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>82.9614539460306</v>
+        <v>83.0443830288272</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>83.3658693422993</v>
+        <v>83.9786157160875</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>84.909320584449</v>
+        <v>85.7293078979599</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>84.909320584449</v>
+        <v>85.7293078979599</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>84.909320584449</v>
+        <v>85.7293078979599</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>84.909320584449</v>
+        <v>85.7293078979599</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>-0.038418293764695</v>
+        <v>-0.0219090477583231</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>-0.00468724302929002</v>
+        <v>0.0122726248669396</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>-0.037689671718124</v>
+        <v>-0.0216707877602375</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.99012391471096</v>
+        <v>0.998083592681513</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.02347917672327</v>
+        <v>1.03233120376366</v>
       </c>
     </row>
     <row r="72">
@@ -5560,46 +5618,46 @@
         <v>82.84</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.994670210550203</v>
+        <v>0.0728965103216065</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>83.495986381293</v>
+        <v>83.3853417810223</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>83.4560533330797</v>
+        <v>83.5486568419725</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>82.9058715533085</v>
+        <v>83.8680556506263</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>83.283885574674</v>
+        <v>82.7671034896784</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>83.283885574674</v>
+        <v>82.7671034896784</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>83.283885574674</v>
+        <v>82.7671034896784</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>83.283885574674</v>
+        <v>82.7671034896784</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>-0.0193287904081186</v>
+        <v>-0.0351640680173085</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>-0.0446134021943887</v>
+        <v>-0.0552462535456495</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>-0.019143187091674</v>
+        <v>-0.0345529957130569</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>0.997459748476407</v>
+        <v>0.992585767736403</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>0.997937024918749</v>
+        <v>0.990645530618495</v>
       </c>
     </row>
     <row r="73">
@@ -5619,46 +5677,46 @@
         <v>82.611</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>0.996780935417701</v>
+        <v>0.148605466851452</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>82.7979616904678</v>
+        <v>82.1582839301551</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>83.9234016600286</v>
+        <v>84.028595199655</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>82.3211180516851</v>
+        <v>83.7075595882876</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>82.8777889550846</v>
+        <v>82.4623945331486</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>82.8777889550846</v>
+        <v>82.4623945331486</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>82.8777889550846</v>
+        <v>82.4623945331486</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>82.8777889550846</v>
+        <v>82.4623945331486</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>-0.0048879794849007</v>
+        <v>-0.00368831601628178</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>0.00816194738613896</v>
+        <v>-0.0004739815661291</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>-0.00487605275363046</v>
+        <v>-0.00368152253350074</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>1.00096412113278</v>
+        <v>1.00370152087466</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>0.987540868407839</v>
+        <v>0.98136109900701</v>
       </c>
     </row>
     <row r="74">
@@ -5678,46 +5736,46 @@
         <v>79.522</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>0.990044401540023</v>
+        <v>-0.594090262109032</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>79.0405789526812</v>
+        <v>78.7433302753282</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>84.3738624964546</v>
+        <v>84.4938928152969</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>81.6535583523893</v>
+        <v>83.536310403353</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>80.3216500959985</v>
+        <v>80.116090262109</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>80.3216500959985</v>
+        <v>80.116090262109</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>80.3216500959985</v>
+        <v>80.116090262109</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>80.3216500959985</v>
+        <v>80.116090262109</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>-0.0313279007335527</v>
+        <v>-0.028865654499662</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>-0.0896835242587181</v>
+        <v>-0.0857279337055744</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>-0.0308422665627739</v>
+        <v>-0.0284530213356385</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>1.01620776517951</v>
+        <v>1.01743334936408</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>0.951973131482202</v>
+        <v>0.948187941076905</v>
       </c>
     </row>
     <row r="75">
@@ -5737,113 +5795,165 @@
         <v>74.938</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>1.02188284444229</v>
+        <v>-0.199404951921869</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>1</v>
+        <v>0.991350654950947</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>75.5726791735258</v>
+        <v>78.4233421635909</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>84.8171459039941</v>
+        <v>84.9532655269037</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>80.9479253248982</v>
+        <v>83.3872651448285</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>73.3332596858485</v>
+        <v>75.1374049519219</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>73.3332596858485</v>
+        <v>75.1658261566751</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>73.3332596858485</v>
+        <v>75.1658261566751</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>73.3332596858485</v>
+        <v>75.1658261566751</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>-0.0910249463564159</v>
+        <v>-0.0637800228200848</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>-0.136334395551867</v>
+        <v>-0.12321902509534</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>-0.0870050652818718</v>
+        <v>-0.0617886380780511</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>0.970367340258835</v>
+        <v>0.958462417986208</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>0.864604189450746</v>
+        <v>0.884790310183792</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
         <v>126</v>
       </c>
-      <c r="B76" s="2"/>
+      <c r="B76" s="2" t="n">
+        <v>86.256</v>
+      </c>
       <c r="C76" s="3" t="n">
-        <v>76.39839661286</v>
+        <v>86.256</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>99.1103100029956</v>
+        <v>86.256</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>58.8910982605083</v>
+        <v>86.256</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.991190921019052</v>
-      </c>
-      <c r="G76" s="7"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="9"/>
-      <c r="J76" s="10"/>
-      <c r="K76" s="11"/>
-      <c r="L76" s="12"/>
-      <c r="M76" s="13"/>
+        <v>0.491196524550069</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" s="8" t="n">
+        <v>83.3443013832209</v>
+      </c>
+      <c r="I76" s="9" t="n">
+        <v>85.4126930458852</v>
+      </c>
+      <c r="J76" s="10" t="n">
+        <v>83.2762797610138</v>
+      </c>
+      <c r="K76" s="11" t="n">
+        <v>85.7648034754499</v>
+      </c>
+      <c r="L76" s="12" t="n">
+        <v>85.7648034754499</v>
+      </c>
+      <c r="M76" s="13" t="n">
+        <v>85.7648034754499</v>
+      </c>
       <c r="N76" s="14" t="n">
-        <v>77.0773773172923</v>
-      </c>
-      <c r="O76" s="15"/>
-      <c r="P76" s="16"/>
-      <c r="Q76" s="17"/>
-      <c r="R76" s="18"/>
-      <c r="S76" s="19"/>
+        <v>85.7648034754499</v>
+      </c>
+      <c r="O76" s="15" t="n">
+        <v>0.131912018167511</v>
+      </c>
+      <c r="P76" s="16" t="n">
+        <v>0.0362184957474727</v>
+      </c>
+      <c r="Q76" s="17" t="n">
+        <v>0.141007926882655</v>
+      </c>
+      <c r="R76" s="18" t="n">
+        <v>1.02904220267082</v>
+      </c>
+      <c r="S76" s="19" t="n">
+        <v>1.00412246022234</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
         <v>127</v>
       </c>
-      <c r="B77" s="2"/>
+      <c r="B77" s="2" t="n">
+        <v>86.282</v>
+      </c>
       <c r="C77" s="3" t="n">
-        <v>75.7447104636289</v>
+        <v>86.282</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>99.3253778669863</v>
+        <v>86.282</v>
       </c>
       <c r="E77" s="5" t="n">
-        <v>57.7622888170851</v>
+        <v>86.282</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>0.993764215880996</v>
-      </c>
-      <c r="G77" s="7"/>
-      <c r="H77" s="8"/>
-      <c r="I77" s="9"/>
-      <c r="J77" s="10"/>
-      <c r="K77" s="11"/>
-      <c r="L77" s="12"/>
-      <c r="M77" s="13"/>
+        <v>0.542171380966198</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H77" s="8" t="n">
+        <v>85.6934026255793</v>
+      </c>
+      <c r="I77" s="9" t="n">
+        <v>85.8720379340448</v>
+      </c>
+      <c r="J77" s="10" t="n">
+        <v>83.1781030052679</v>
+      </c>
+      <c r="K77" s="11" t="n">
+        <v>85.7398286190338</v>
+      </c>
+      <c r="L77" s="12" t="n">
+        <v>85.7398286190338</v>
+      </c>
+      <c r="M77" s="13" t="n">
+        <v>85.7398286190338</v>
+      </c>
       <c r="N77" s="14" t="n">
-        <v>76.2200019412848</v>
-      </c>
-      <c r="O77" s="15"/>
-      <c r="P77" s="16"/>
-      <c r="Q77" s="17"/>
-      <c r="R77" s="18"/>
-      <c r="S77" s="19"/>
+        <v>85.7398286190338</v>
+      </c>
+      <c r="O77" s="15" t="n">
+        <v>-0.000291244105627546</v>
+      </c>
+      <c r="P77" s="16" t="n">
+        <v>0.0397445903001006</v>
+      </c>
+      <c r="Q77" s="17" t="n">
+        <v>-0.000291201698180088</v>
+      </c>
+      <c r="R77" s="18" t="n">
+        <v>1.00054176858465</v>
+      </c>
+      <c r="S77" s="19" t="n">
+        <v>0.998460391552457</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
@@ -5851,16 +5961,16 @@
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="3" t="n">
-        <v>75.1956221819782</v>
+        <v>81.4333459701193</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>99.3776339337483</v>
+        <v>97.0357288617872</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>56.8979293580726</v>
+        <v>65.8309630784515</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>0.995598078136688</v>
+        <v>-0.469177422976476</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="8"/>
@@ -5870,7 +5980,7 @@
       <c r="L78" s="12"/>
       <c r="M78" s="13"/>
       <c r="N78" s="14" t="n">
-        <v>75.528090936767</v>
+        <v>81.9025233930958</v>
       </c>
       <c r="O78" s="15"/>
       <c r="P78" s="16"/>
@@ -5884,16 +5994,16 @@
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="3" t="n">
-        <v>74.7338332785374</v>
+        <v>80.6787070653612</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>99.3364647130133</v>
+        <v>97.0989642566814</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>56.2245279479184</v>
+        <v>64.2584498740409</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>1.01800548858665</v>
+        <v>-1.0131098163127</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
@@ -5903,7 +6013,7 @@
       <c r="L79" s="12"/>
       <c r="M79" s="13"/>
       <c r="N79" s="14" t="n">
-        <v>73.4120140965981</v>
+        <v>81.6918168816739</v>
       </c>
       <c r="O79" s="15"/>
       <c r="P79" s="16"/>
@@ -5916,10 +6026,18 @@
         <v>130</v>
       </c>
       <c r="B80" s="2"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="6"/>
+      <c r="C80" s="3" t="n">
+        <v>80.0021189833975</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>97.0726693231899</v>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>62.9315686436052</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>0.974327735275761</v>
+      </c>
       <c r="G80" s="7"/>
       <c r="H80" s="8"/>
       <c r="I80" s="9"/>
@@ -5927,7 +6045,9 @@
       <c r="K80" s="11"/>
       <c r="L80" s="12"/>
       <c r="M80" s="13"/>
-      <c r="N80" s="14"/>
+      <c r="N80" s="14" t="n">
+        <v>79.0277912481217</v>
+      </c>
       <c r="O80" s="15"/>
       <c r="P80" s="16"/>
       <c r="Q80" s="17"/>
@@ -5939,10 +6059,18 @@
         <v>131</v>
       </c>
       <c r="B81" s="2"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="6"/>
+      <c r="C81" s="3" t="n">
+        <v>79.3955090806097</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>96.9898602033172</v>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>61.8011579579022</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>0.666056319693859</v>
+      </c>
       <c r="G81" s="7"/>
       <c r="H81" s="8"/>
       <c r="I81" s="9"/>
@@ -5950,7 +6078,9 @@
       <c r="K81" s="11"/>
       <c r="L81" s="12"/>
       <c r="M81" s="13"/>
-      <c r="N81" s="14"/>
+      <c r="N81" s="14" t="n">
+        <v>78.7294527609158</v>
+      </c>
       <c r="O81" s="15"/>
       <c r="P81" s="16"/>
       <c r="Q81" s="17"/>
@@ -6338,150 +6468,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B2" s="1"/>
+        <v>149</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3"/>
-      <c r="B3" s="1"/>
+      <c r="A3" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B4" s="1"/>
+        <v>151</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5" s="1" t="n">
-        <v>0.0214444114737955</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B6" s="1" t="n">
-        <v>-0.0591024708422404</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>0.02021438815392</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>153</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>0.165426667834434</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>0.281779190215536</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>155</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>0.11313295059703</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>-0.0303743900296572</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>-0.190752700777699</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>158</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>-0.243386415919159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="1"/>
+      <c r="A14" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="15">
-      <c r="B15" s="1"/>
+      <c r="A15" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="1"/>
+      <c r="A16" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="17">
-      <c r="B17" s="1"/>
+      <c r="A17" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="1"/>
+      <c r="A18" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="19">
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="1"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="1"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27">
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28">
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="1"/>
+      <c r="A19" t="s">
+        <v>166</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6489,235 +6567,160 @@
 </worksheet>
 </file>
 
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
-    <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
-    <xsd:import namespace="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b5dd4176-d247-4204-85b8-921214f3ccea" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="01529062-7a8b-4d76-943d-e0db5644ee6d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="18" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="359b39ce-e1f9-4933-8424-33b611e6fdcd" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{c9b73259-0823-4f05-8927-4a40ee49fbe1}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="359b39ce-e1f9-4933-8424-33b611e6fdcd">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EBCED2BB-6857-4458-BB65-916952781451}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C8B9BC3-A18E-4035-BF7A-16045A41CB5F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE2285F8-7184-4164-B9BD-1BBCDDC4D649}"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3"/>
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0.0226626019595318</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>-0.0561963431725149</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>-0.0156912361706693</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>0.149410474634527</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>173</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.339098178992349</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>0.127106810653067</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0.0289075947529167</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>-0.185065657609698</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>177</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>-0.231359469415676</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="1"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="1"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="1"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="1"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="1"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="1"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="1"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/indicadores/GSF-EPRIV-INF_out.xlsx
+++ b/indicadores/GSF-EPRIV-INF_out.xlsx
@@ -23,7 +23,7 @@
     <t xml:space="preserve">Título</t>
   </si>
   <si>
-    <t xml:space="preserve">Ocupados informales en el sector privado del Gran Santa Fe</t>
+    <t xml:space="preserve">Ocupados informales en el sector privado</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">(1 0 1)</t>
   </si>
   <si>
-    <t xml:space="preserve">Código</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSF-EPRIV-INF</t>
+    <t xml:space="preserve">Alcance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aglomerado Gran Santa Fe</t>
   </si>
   <si>
     <t xml:space="preserve">Regresores</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">07/05/2026</t>
+    <t xml:space="preserve">16/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">vcorvalan</t>
+    <t xml:space="preserve">fleiva</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1082,7 +1082,7 @@
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9" t="n">
-        <v>0.339098178992349</v>
+        <v>0.342637246779251</v>
       </c>
       <c r="E9"/>
       <c r="F9"/>
@@ -1140,7 +1140,7 @@
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13" t="n">
-        <v>0.114987574995927</v>
+        <v>0.117400282880465</v>
       </c>
       <c r="E13"/>
       <c r="F13"/>
@@ -1210,7 +1210,7 @@
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18" t="n">
-        <v>0.226307929213274</v>
+        <v>0.194703088502734</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
@@ -1240,7 +1240,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.170596365458058</v>
+        <v>0.181311789583426</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -6601,7 +6601,7 @@
         <v>169</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0226626019595318</v>
+        <v>0.0143909663492046</v>
       </c>
     </row>
     <row r="6">
@@ -6609,7 +6609,7 @@
         <v>170</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>-0.0561963431725149</v>
+        <v>-0.0549177632913489</v>
       </c>
     </row>
     <row r="7">
@@ -6617,7 +6617,7 @@
         <v>171</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>-0.0156912361706693</v>
+        <v>-0.00528574400128268</v>
       </c>
     </row>
     <row r="8">
@@ -6625,7 +6625,7 @@
         <v>172</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.149410474634527</v>
+        <v>0.137801449851668</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +6633,7 @@
         <v>173</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.339098178992349</v>
+        <v>0.342637246779251</v>
       </c>
     </row>
     <row r="10">
@@ -6641,7 +6641,7 @@
         <v>174</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.127106810653067</v>
+        <v>0.133161196420219</v>
       </c>
     </row>
     <row r="11">
@@ -6649,7 +6649,7 @@
         <v>175</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.0289075947529167</v>
+        <v>0.0283701131038142</v>
       </c>
     </row>
     <row r="12">
@@ -6657,7 +6657,7 @@
         <v>176</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.185065657609698</v>
+        <v>-0.179612555020879</v>
       </c>
     </row>
     <row r="13">
@@ -6665,7 +6665,7 @@
         <v>177</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.231359469415676</v>
+        <v>-0.238445213843736</v>
       </c>
     </row>
     <row r="14">

--- a/indicadores/GSF-EPRIV-INF_out.xlsx
+++ b/indicadores/GSF-EPRIV-INF_out.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -62,16 +62,22 @@
     <t xml:space="preserve">(1 0 1)</t>
   </si>
   <si>
+    <t xml:space="preserve">Código</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSF-EPRIV-INF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regresores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">const</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alcance</t>
   </si>
   <si>
     <t xml:space="preserve">Aglomerado Gran Santa Fe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regresores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">const</t>
   </si>
   <si>
     <t xml:space="preserve">Resumen del correlograma</t>
@@ -1050,9 +1056,13 @@
       <c r="J6" s="1"/>
     </row>
     <row r="7">
-      <c r="A7"/>
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
       <c r="B7"/>
-      <c r="C7"/>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
       <c r="D7"/>
       <c r="E7"/>
       <c r="F7"/>
@@ -1063,7 +1073,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8"/>
       <c r="C8"/>
@@ -1077,7 +1087,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B9"/>
       <c r="C9"/>
@@ -1093,7 +1103,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
@@ -1121,7 +1131,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
@@ -1135,7 +1145,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -1163,7 +1173,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -1177,7 +1187,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -1191,7 +1201,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1205,7 +1215,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
@@ -1221,7 +1231,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1235,7 +1245,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
@@ -1383,10 +1393,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32"/>
       <c r="D32"/>
@@ -1399,10 +1409,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C33"/>
       <c r="D33"/>
@@ -1426,66 +1436,66 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="L1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="P1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="Q1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="R1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="S1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>59.301</v>
@@ -1538,7 +1548,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>69.648</v>
@@ -1595,7 +1605,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>68.504</v>
@@ -1652,7 +1662,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>67.829</v>
@@ -1709,7 +1719,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>81.778</v>
@@ -1768,7 +1778,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>73.335</v>
@@ -1827,7 +1837,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>74.334</v>
@@ -1886,7 +1896,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>70.162</v>
@@ -1945,7 +1955,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>64.617</v>
@@ -2004,7 +2014,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>68.225</v>
@@ -2063,7 +2073,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>70.05</v>
@@ -2122,7 +2132,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>82.955</v>
@@ -2181,7 +2191,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B14" s="2" t="n">
         <v>75.453</v>
@@ -2240,7 +2250,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>72.058</v>
@@ -2299,7 +2309,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="n">
         <v>78.697</v>
@@ -2358,7 +2368,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B17" s="2" t="n">
         <v>79.056</v>
@@ -2417,7 +2427,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="n">
         <v>72.726</v>
@@ -2476,7 +2486,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B19" s="2" t="n">
         <v>67.312</v>
@@ -2535,7 +2545,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B20" s="2" t="n">
         <v>73.631</v>
@@ -2594,7 +2604,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>81.065</v>
@@ -2653,7 +2663,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B22" s="2" t="n">
         <v>71.81</v>
@@ -2712,7 +2722,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>60.116</v>
@@ -2771,7 +2781,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2" t="n">
         <v>70.882</v>
@@ -2830,7 +2840,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2" t="n">
         <v>68.268</v>
@@ -2889,7 +2899,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>60.373</v>
@@ -2948,7 +2958,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B27" s="2" t="n">
         <v>65.695</v>
@@ -3007,7 +3017,7 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B28" s="2" t="n">
         <v>69.771</v>
@@ -3066,7 +3076,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B29" s="2" t="n">
         <v>64.776</v>
@@ -3125,7 +3135,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B30" s="2" t="n">
         <v>87.046</v>
@@ -3184,7 +3194,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B31" s="2" t="n">
         <v>79.367</v>
@@ -3243,7 +3253,7 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B32" s="2" t="n">
         <v>72.42</v>
@@ -3302,7 +3312,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B33" s="2" t="n">
         <v>74.787</v>
@@ -3361,7 +3371,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B34" s="2" t="n">
         <v>67.608</v>
@@ -3420,7 +3430,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B35" s="2" t="n">
         <v>65.8</v>
@@ -3479,7 +3489,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B36" s="2" t="n">
         <v>71.3555</v>
@@ -3538,7 +3548,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B37" s="2" t="n">
         <v>73.692</v>
@@ -3597,7 +3607,7 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B38" s="2" t="n">
         <v>64.2905</v>
@@ -3656,7 +3666,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B39" s="2" t="n">
         <v>60.527</v>
@@ -3715,7 +3725,7 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B40" s="2" t="n">
         <v>70.291</v>
@@ -3774,7 +3784,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B41" s="2" t="n">
         <v>72.597</v>
@@ -3833,7 +3843,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B42" s="2" t="n">
         <v>60.973</v>
@@ -3892,7 +3902,7 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B43" s="2" t="n">
         <v>67.704</v>
@@ -3951,7 +3961,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B44" s="2" t="n">
         <v>77.328</v>
@@ -4010,7 +4020,7 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B45" s="2" t="n">
         <v>70.704</v>
@@ -4069,7 +4079,7 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B46" s="2" t="n">
         <v>70.836</v>
@@ -4128,7 +4138,7 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B47" s="2" t="n">
         <v>65.703</v>
@@ -4187,7 +4197,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B48" s="2" t="n">
         <v>65.884</v>
@@ -4246,7 +4256,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2" t="n">
         <v>63.259</v>
@@ -4305,7 +4315,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B50" s="2" t="n">
         <v>55.23</v>
@@ -4364,7 +4374,7 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B51" s="2" t="n">
         <v>60.865</v>
@@ -4423,7 +4433,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B52" s="2" t="n">
         <v>66.823</v>
@@ -4482,7 +4492,7 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>66.726</v>
@@ -4541,7 +4551,7 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>61.185</v>
@@ -4600,7 +4610,7 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B55" s="2" t="n">
         <v>33.184</v>
@@ -4659,7 +4669,7 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B56" s="2" t="n">
         <v>75.79</v>
@@ -4718,7 +4728,7 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B57" s="2" t="n">
         <v>74.809</v>
@@ -4777,7 +4787,7 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B58" s="2" t="n">
         <v>74.937</v>
@@ -4836,7 +4846,7 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B59" s="2" t="n">
         <v>83.357</v>
@@ -4895,7 +4905,7 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>78.522</v>
@@ -4954,7 +4964,7 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B61" s="2" t="n">
         <v>73.12</v>
@@ -5013,7 +5023,7 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B62" s="2" t="n">
         <v>76.726</v>
@@ -5072,7 +5082,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>91.187</v>
@@ -5131,7 +5141,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B64" s="2" t="n">
         <v>75.475</v>
@@ -5190,7 +5200,7 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>82.884</v>
@@ -5249,7 +5259,7 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B66" s="2" t="n">
         <v>81.745</v>
@@ -5308,7 +5318,7 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B67" s="2" t="n">
         <v>86.53</v>
@@ -5367,7 +5377,7 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B68" s="2" t="n">
         <v>87.103</v>
@@ -5426,7 +5436,7 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B69" s="2" t="n">
         <v>82.518</v>
@@ -5485,7 +5495,7 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B70" s="2" t="n">
         <v>86.718</v>
@@ -5544,7 +5554,7 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B71" s="2" t="n">
         <v>86.566</v>
@@ -5603,7 +5613,7 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B72" s="2" t="n">
         <v>82.84</v>
@@ -5662,7 +5672,7 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>82.611</v>
@@ -5721,7 +5731,7 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>79.522</v>
@@ -5780,7 +5790,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>74.938</v>
@@ -5839,7 +5849,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B76" s="2" t="n">
         <v>86.256</v>
@@ -5898,7 +5908,7 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>86.282</v>
@@ -5957,7 +5967,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="3" t="n">
@@ -5990,7 +6000,7 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="3" t="n">
@@ -6023,7 +6033,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="3" t="n">
@@ -6056,7 +6066,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" s="3" t="n">
@@ -6089,7 +6099,7 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="3"/>
@@ -6112,7 +6122,7 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -6135,7 +6145,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" s="3"/>
@@ -6158,7 +6168,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B85" s="2"/>
       <c r="C85" s="3"/>
@@ -6181,7 +6191,7 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B86" s="2"/>
       <c r="C86" s="3"/>
@@ -6204,7 +6214,7 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B87" s="2"/>
       <c r="C87" s="3"/>
@@ -6227,7 +6237,7 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B88" s="2"/>
       <c r="C88" s="3"/>
@@ -6250,7 +6260,7 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="3"/>
@@ -6273,7 +6283,7 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="3"/>
@@ -6296,7 +6306,7 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B91" s="2"/>
       <c r="C91" s="3"/>
@@ -6319,7 +6329,7 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B92" s="2"/>
       <c r="C92" s="3"/>
@@ -6342,7 +6352,7 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B93" s="2"/>
       <c r="C93" s="3"/>
@@ -6365,7 +6375,7 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="3"/>
@@ -6388,7 +6398,7 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B95" s="2"/>
       <c r="C95" s="3"/>
@@ -6411,7 +6421,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -6434,7 +6444,7 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="3"/>
@@ -6468,97 +6478,97 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -6582,7 +6592,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -6592,13 +6602,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>0.0143909663492046</v>
@@ -6606,7 +6616,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>-0.0549177632913489</v>
@@ -6614,7 +6624,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>-0.00528574400128268</v>
@@ -6622,7 +6632,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>0.137801449851668</v>
@@ -6630,7 +6640,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>0.342637246779251</v>
@@ -6638,7 +6648,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>0.133161196420219</v>
@@ -6646,7 +6656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>0.0283701131038142</v>
@@ -6654,7 +6664,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>-0.179612555020879</v>
@@ -6662,7 +6672,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>-0.238445213843736</v>

--- a/indicadores/GSF-EPRIV-INF_out.xlsx
+++ b/indicadores/GSF-EPRIV-INF_out.xlsx
@@ -113,13 +113,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">16/06/2026</t>
+    <t xml:space="preserve">17/06/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">fleiva</t>
+    <t xml:space="preserve">focampo</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>

--- a/indicadores/GSF-EPRIV-INF_out.xlsx
+++ b/indicadores/GSF-EPRIV-INF_out.xlsx
@@ -113,13 +113,13 @@
     <t xml:space="preserve">Fecha</t>
   </si>
   <si>
-    <t xml:space="preserve">17/06/2026</t>
+    <t xml:space="preserve">04/08/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Usuario</t>
   </si>
   <si>
-    <t xml:space="preserve">focampo</t>
+    <t xml:space="preserve">fleiva</t>
   </si>
   <si>
     <t xml:space="preserve">fecha</t>
@@ -1072,9 +1072,7 @@
       <c r="J7" s="1"/>
     </row>
     <row r="8">
-      <c r="A8" t="s">
-        <v>21</v>
-      </c>
+      <c r="A8"/>
       <c r="B8"/>
       <c r="C8"/>
       <c r="D8"/>
@@ -1086,14 +1084,10 @@
       <c r="J8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
+      <c r="A9"/>
       <c r="B9"/>
       <c r="C9"/>
-      <c r="D9" t="n">
-        <v>0.342637246779251</v>
-      </c>
+      <c r="D9"/>
       <c r="E9"/>
       <c r="F9"/>
       <c r="G9"/>
@@ -1103,13 +1097,11 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10"/>
       <c r="C10"/>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
+      <c r="D10"/>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
@@ -1118,10 +1110,14 @@
       <c r="J10" s="1"/>
     </row>
     <row r="11">
-      <c r="A11"/>
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
       <c r="B11"/>
       <c r="C11"/>
-      <c r="D11"/>
+      <c r="D11" t="n">
+        <v>0.350515836346144</v>
+      </c>
       <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
@@ -1131,11 +1127,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12"/>
       <c r="C12"/>
-      <c r="D12"/>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
       <c r="E12"/>
       <c r="F12"/>
       <c r="G12"/>
@@ -1144,14 +1142,10 @@
       <c r="J12" s="1"/>
     </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>25</v>
-      </c>
+      <c r="A13"/>
       <c r="B13"/>
       <c r="C13"/>
-      <c r="D13" t="n">
-        <v>0.117400282880465</v>
-      </c>
+      <c r="D13"/>
       <c r="E13"/>
       <c r="F13"/>
       <c r="G13"/>
@@ -1160,7 +1154,9 @@
       <c r="J13" s="1"/>
     </row>
     <row r="14">
-      <c r="A14"/>
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1173,11 +1169,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
-      <c r="D15"/>
+      <c r="D15" t="n">
+        <v>0.122861351529437</v>
+      </c>
       <c r="E15"/>
       <c r="F15"/>
       <c r="G15"/>
@@ -1186,9 +1184,7 @@
       <c r="J15" s="1"/>
     </row>
     <row r="16">
-      <c r="A16" t="s">
-        <v>27</v>
-      </c>
+      <c r="A16"/>
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1201,7 +1197,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -1215,13 +1211,11 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
-      <c r="D18" t="n">
-        <v>0.194703088502734</v>
-      </c>
+      <c r="D18"/>
       <c r="E18"/>
       <c r="F18"/>
       <c r="G18"/>
@@ -1231,7 +1225,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -1250,7 +1244,7 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20" t="n">
-        <v>0.181311789583426</v>
+        <v>0.237947137575376</v>
       </c>
       <c r="E20"/>
       <c r="F20"/>
@@ -1260,7 +1254,9 @@
       <c r="J20" s="1"/>
     </row>
     <row r="21">
-      <c r="A21"/>
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
@@ -1272,10 +1268,14 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22">
-      <c r="A22"/>
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
       <c r="B22"/>
       <c r="C22"/>
-      <c r="D22"/>
+      <c r="D22" t="n">
+        <v>0.240601720732893</v>
+      </c>
       <c r="E22"/>
       <c r="F22"/>
       <c r="G22"/>
@@ -1510,40 +1510,40 @@
         <v>59.301</v>
       </c>
       <c r="F2" s="6" t="n">
-        <v>-2.57735274521391</v>
+        <v>-2.57735293812007</v>
       </c>
       <c r="G2" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="8" t="n">
-        <v>63.6997944821128</v>
+        <v>63.699794823802</v>
       </c>
       <c r="I2" s="9" t="n">
-        <v>69.545568549301</v>
+        <v>69.5464894029269</v>
       </c>
       <c r="J2" s="10" t="n">
-        <v>67.7415658238297</v>
+        <v>67.7415684033198</v>
       </c>
       <c r="K2" s="11" t="n">
-        <v>61.8783527452139</v>
+        <v>61.8783529381201</v>
       </c>
       <c r="L2" s="12" t="n">
-        <v>61.8783527452139</v>
+        <v>61.8783529381201</v>
       </c>
       <c r="M2" s="13" t="n">
-        <v>61.8783527452139</v>
+        <v>61.8783529381201</v>
       </c>
       <c r="N2" s="14" t="n">
-        <v>61.8783527452139</v>
+        <v>61.8783529381201</v>
       </c>
       <c r="O2" s="15"/>
       <c r="P2" s="16"/>
       <c r="Q2" s="17"/>
       <c r="R2" s="18" t="n">
-        <v>0.971405845941774</v>
+        <v>0.971405843759463</v>
       </c>
       <c r="S2" s="19" t="n">
-        <v>0.889752633215562</v>
+        <v>0.889740854921081</v>
       </c>
     </row>
     <row r="3">
@@ -1563,44 +1563,44 @@
         <v>69.648</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>-1.31967933240247</v>
+        <v>-1.3196801276388</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.773514998731786</v>
+        <v>0.773514953570622</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>67.9776428065299</v>
+        <v>67.9776433457381</v>
       </c>
       <c r="I3" s="9" t="n">
-        <v>69.9019579190921</v>
+        <v>69.9027559666016</v>
       </c>
       <c r="J3" s="10" t="n">
-        <v>68.5340368687882</v>
+        <v>68.5340388806205</v>
       </c>
       <c r="K3" s="11" t="n">
-        <v>70.9676793324025</v>
+        <v>70.9676801276388</v>
       </c>
       <c r="L3" s="12" t="n">
-        <v>70.2904809060482</v>
+        <v>70.2904815082645</v>
       </c>
       <c r="M3" s="13" t="n">
-        <v>70.2904809060482</v>
+        <v>70.2904815082645</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>70.2904809060482</v>
+        <v>70.2904815082645</v>
       </c>
       <c r="O3" s="15" t="n">
-        <v>0.12746597770436</v>
+        <v>0.12746598315439</v>
       </c>
       <c r="P3" s="16"/>
       <c r="Q3" s="17" t="n">
-        <v>0.135946220085585</v>
+        <v>0.135946226276526</v>
       </c>
       <c r="R3" s="18" t="n">
-        <v>1.03402351131976</v>
+        <v>1.03402351197677</v>
       </c>
       <c r="S3" s="19" t="n">
-        <v>1.0055581130847</v>
+        <v>1.00554664170677</v>
       </c>
     </row>
     <row r="4">
@@ -1620,44 +1620,44 @@
         <v>68.504</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>-0.331139537117107</v>
+        <v>-0.331139865097263</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>70.0855216849906</v>
+        <v>70.0855216215485</v>
       </c>
       <c r="I4" s="9" t="n">
-        <v>70.2535552790058</v>
+        <v>70.2542299449859</v>
       </c>
       <c r="J4" s="10" t="n">
-        <v>69.2971918483537</v>
+        <v>69.2971932805952</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>68.8351395371171</v>
+        <v>68.8351398650973</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>68.8351395371171</v>
+        <v>68.8351398650973</v>
       </c>
       <c r="M4" s="13" t="n">
-        <v>68.8351395371171</v>
+        <v>68.8351398650973</v>
       </c>
       <c r="N4" s="14" t="n">
-        <v>68.8351395371171</v>
+        <v>68.8351398650973</v>
       </c>
       <c r="O4" s="15" t="n">
-        <v>-0.0209220192690694</v>
+        <v>-0.020922023071886</v>
       </c>
       <c r="P4" s="16"/>
       <c r="Q4" s="17" t="n">
-        <v>-0.0207046722425522</v>
+        <v>-0.0207046759666328</v>
       </c>
       <c r="R4" s="18" t="n">
-        <v>0.982159194683697</v>
+        <v>0.98215920025247</v>
       </c>
       <c r="S4" s="19" t="n">
-        <v>0.979810050377443</v>
+        <v>0.979800645726245</v>
       </c>
     </row>
     <row r="5">
@@ -1677,44 +1677,44 @@
         <v>67.829</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>4.19091832615672</v>
+        <v>4.19091975339809</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>71.7857196496394</v>
+        <v>71.7857188408478</v>
       </c>
       <c r="I5" s="9" t="n">
-        <v>70.5958114460311</v>
+        <v>70.5963610812526</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>70.0104969173192</v>
+        <v>70.010497739056</v>
       </c>
       <c r="K5" s="11" t="n">
-        <v>63.6380816738433</v>
+        <v>63.6380802466019</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>71.7857196496394</v>
+        <v>71.7857188408478</v>
       </c>
       <c r="M5" s="13" t="n">
-        <v>71.7857196496394</v>
+        <v>71.7857188408478</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>71.7857196496394</v>
+        <v>71.7857188408478</v>
       </c>
       <c r="O5" s="15" t="n">
-        <v>0.0419712019618764</v>
+        <v>0.0419711859304089</v>
       </c>
       <c r="P5" s="16"/>
       <c r="Q5" s="17" t="n">
-        <v>0.0428644458682514</v>
+        <v>0.0428644291496041</v>
       </c>
       <c r="R5" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S5" s="19" t="n">
-        <v>1.01685522383319</v>
+        <v>1.01684729554582</v>
       </c>
     </row>
     <row r="6">
@@ -1734,46 +1734,46 @@
         <v>81.778</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>-2.36012891173764</v>
+        <v>-2.36012903442563</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>74.8396928507245</v>
+        <v>74.8396928242136</v>
       </c>
       <c r="I6" s="9" t="n">
-        <v>70.9232907273188</v>
+        <v>70.923712187275</v>
       </c>
       <c r="J6" s="10" t="n">
-        <v>70.651107968922</v>
+        <v>70.6511081247379</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>84.1381289117377</v>
+        <v>84.1381290344256</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>74.8396928507245</v>
+        <v>74.8396928242136</v>
       </c>
       <c r="M6" s="13" t="n">
-        <v>74.8396928507245</v>
+        <v>74.8396928242136</v>
       </c>
       <c r="N6" s="14" t="n">
-        <v>74.8396928507245</v>
+        <v>74.8396928242136</v>
       </c>
       <c r="O6" s="15" t="n">
-        <v>0.0416628317191655</v>
+        <v>0.0416628426316774</v>
       </c>
       <c r="P6" s="16" t="n">
-        <v>0.209464853708684</v>
+        <v>0.209464849509734</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>0.0425429070850087</v>
+        <v>0.0425429184617707</v>
       </c>
       <c r="R6" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S6" s="19" t="n">
-        <v>1.05522025392848</v>
+        <v>1.05521398297086</v>
       </c>
     </row>
     <row r="7">
@@ -1793,46 +1793,46 @@
         <v>73.335</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-1.72735857020546</v>
+        <v>-1.72735984815484</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>75.9930279679327</v>
+        <v>75.9930290830579</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>71.2313011226468</v>
+        <v>71.2315894235259</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>71.2050570100606</v>
+        <v>71.2050564118844</v>
       </c>
       <c r="K7" s="11" t="n">
-        <v>75.0623585702054</v>
+        <v>75.0623598481548</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>75.0623585702054</v>
+        <v>75.0623598481548</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>75.0623585702054</v>
+        <v>75.0623598481548</v>
       </c>
       <c r="N7" s="14" t="n">
-        <v>75.0623585702054</v>
+        <v>75.0623598481548</v>
       </c>
       <c r="O7" s="15" t="n">
-        <v>0.00297081835954165</v>
+        <v>0.00297083573894711</v>
       </c>
       <c r="P7" s="16" t="n">
-        <v>0.0678879643821959</v>
+        <v>0.0678879734140005</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>0.00297523561360769</v>
+        <v>0.00297525304472113</v>
       </c>
       <c r="R7" s="18" t="n">
-        <v>0.987753226544414</v>
+        <v>0.987753228866744</v>
       </c>
       <c r="S7" s="19" t="n">
-        <v>1.05378334225515</v>
+        <v>1.05377909514067</v>
       </c>
     </row>
     <row r="8">
@@ -1852,46 +1852,46 @@
         <v>74.334</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.171804110764795</v>
+        <v>-0.171804483822041</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>72.6259775964041</v>
+        <v>72.6259776617322</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>71.5175983831199</v>
+        <v>71.5177464383762</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>71.6793189720426</v>
+        <v>71.6793174982366</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>74.5058041107648</v>
+        <v>74.505804483822</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>74.5058041107648</v>
+        <v>74.505804483822</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>74.5058041107648</v>
+        <v>74.505804483822</v>
       </c>
       <c r="N8" s="14" t="n">
-        <v>74.5058041107648</v>
+        <v>74.505804483822</v>
       </c>
       <c r="O8" s="15" t="n">
-        <v>-0.0074421858000426</v>
+        <v>-0.00744219781812227</v>
       </c>
       <c r="P8" s="16" t="n">
-        <v>0.0823803744973883</v>
+        <v>0.0823803747597247</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>-0.00741456130665152</v>
+        <v>-0.00741457323562233</v>
       </c>
       <c r="R8" s="18" t="n">
-        <v>1.02588366555019</v>
+        <v>1.02588366976408</v>
       </c>
       <c r="S8" s="19" t="n">
-        <v>1.04178280304712</v>
+        <v>1.04178065157605</v>
       </c>
     </row>
     <row r="9">
@@ -1911,46 +1911,46 @@
         <v>70.162</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>4.30986420225621</v>
+        <v>4.30986624038932</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>67.572945602647</v>
+        <v>67.5729437234423</v>
       </c>
       <c r="I9" s="9" t="n">
-        <v>71.782332670748</v>
+        <v>71.7823311117122</v>
       </c>
       <c r="J9" s="10" t="n">
-        <v>72.1001552939765</v>
+        <v>72.100152798717</v>
       </c>
       <c r="K9" s="11" t="n">
-        <v>65.8521357977438</v>
+        <v>65.8521337596107</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>65.8521357977438</v>
+        <v>65.8521337596107</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>65.8521357977438</v>
+        <v>65.8521337596107</v>
       </c>
       <c r="N9" s="14" t="n">
-        <v>65.8521357977438</v>
+        <v>65.8521337596107</v>
       </c>
       <c r="O9" s="15" t="n">
-        <v>-0.123465167928452</v>
+        <v>-0.123465203885687</v>
       </c>
       <c r="P9" s="16" t="n">
-        <v>-0.0826568833029093</v>
+        <v>-0.082656901359338</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>-0.116147572881113</v>
+        <v>-0.116147604662002</v>
       </c>
       <c r="R9" s="18" t="n">
-        <v>0.974534041848313</v>
+        <v>0.974534038788151</v>
       </c>
       <c r="S9" s="19" t="n">
-        <v>0.917386400631408</v>
+        <v>0.917386392162821</v>
       </c>
     </row>
     <row r="10">
@@ -1970,46 +1970,46 @@
         <v>64.617</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>-1.997080290802</v>
+        <v>-1.99707907960203</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>66.8049867535478</v>
+        <v>66.8049872283691</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>72.0275217761205</v>
+        <v>72.0273588596988</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>72.5079598406642</v>
+        <v>72.5079561631758</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>66.614080290802</v>
+        <v>66.614079079602</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>66.614080290802</v>
+        <v>66.614079079602</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>66.614080290802</v>
+        <v>66.614079079602</v>
       </c>
       <c r="N10" s="14" t="n">
-        <v>66.614080290802</v>
+        <v>66.614079079602</v>
       </c>
       <c r="O10" s="15" t="n">
-        <v>0.0115041090295127</v>
+        <v>0.0115041217973159</v>
       </c>
       <c r="P10" s="16" t="n">
-        <v>-0.109909758399588</v>
+        <v>-0.109909774268211</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>0.0115705357742446</v>
+        <v>0.0115705486897781</v>
       </c>
       <c r="R10" s="18" t="n">
-        <v>0.997142332151789</v>
+        <v>0.997142306934145</v>
       </c>
       <c r="S10" s="19" t="n">
-        <v>0.92484204159981</v>
+        <v>0.924844116655156</v>
       </c>
     </row>
     <row r="11">
@@ -2029,46 +2029,46 @@
         <v>68.225</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>-2.64357357329769</v>
+        <v>-2.64357900712359</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>69.2084559792661</v>
+        <v>69.2084583256273</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>72.2514771167813</v>
+        <v>72.2511387251555</v>
       </c>
       <c r="J11" s="10" t="n">
-        <v>72.9118863794266</v>
+        <v>72.9118813462679</v>
       </c>
       <c r="K11" s="11" t="n">
-        <v>70.8685735732977</v>
+        <v>70.8685790071236</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>70.8685735732977</v>
+        <v>70.8685790071236</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>70.8685735732977</v>
+        <v>70.8685790071236</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>70.8685735732977</v>
+        <v>70.8685790071236</v>
       </c>
       <c r="O11" s="15" t="n">
-        <v>0.0619111142707565</v>
+        <v>0.0619112091277853</v>
       </c>
       <c r="P11" s="16" t="n">
-        <v>-0.0558706797493626</v>
+        <v>-0.0558706234325024</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>0.0638677778620196</v>
+        <v>0.0638678787773608</v>
       </c>
       <c r="R11" s="18" t="n">
-        <v>1.0239872074957</v>
+        <v>1.02398725129355</v>
       </c>
       <c r="S11" s="19" t="n">
-        <v>0.980859857837253</v>
+        <v>0.980864526948271</v>
       </c>
     </row>
     <row r="12">
@@ -2088,46 +2088,46 @@
         <v>70.05</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>0.35374009255429</v>
+        <v>0.353742639652225</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.854991730688768</v>
+        <v>0.854991706351659</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>72.4799542420324</v>
+        <v>72.479953608179</v>
       </c>
       <c r="I12" s="9" t="n">
-        <v>72.449126709346</v>
+        <v>72.4485964510395</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>73.2916192798351</v>
+        <v>73.2916127172303</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>69.6962599074457</v>
+        <v>69.6962573603478</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>70.0999186051956</v>
+        <v>70.0999164032811</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>70.0999186051956</v>
+        <v>70.0999164032811</v>
       </c>
       <c r="N12" s="14" t="n">
-        <v>70.0999186051956</v>
+        <v>70.0999164032811</v>
       </c>
       <c r="O12" s="15" t="n">
-        <v>-0.0109054523340425</v>
+        <v>-0.0109055604198153</v>
       </c>
       <c r="P12" s="16" t="n">
-        <v>-0.0591347957136218</v>
+        <v>-0.0591348299782154</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>-0.0108462034629084</v>
+        <v>-0.0108463103763552</v>
       </c>
       <c r="R12" s="18" t="n">
-        <v>0.967162842999471</v>
+        <v>0.967162821077891</v>
       </c>
       <c r="S12" s="19" t="n">
-        <v>0.967574376519747</v>
+        <v>0.9675814278977</v>
       </c>
     </row>
     <row r="13">
@@ -2147,46 +2147,46 @@
         <v>82.955</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>4.39156406923738</v>
+        <v>4.39156723105071</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0.926876989087996</v>
+        <v>0.926876936133055</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>76.3964494871093</v>
+        <v>76.3964456167829</v>
       </c>
       <c r="I13" s="9" t="n">
-        <v>72.6145342557155</v>
+        <v>72.6137936804842</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>73.6166263474307</v>
+        <v>73.6166181336041</v>
       </c>
       <c r="K13" s="11" t="n">
-        <v>78.5634359307626</v>
+        <v>78.5634327689493</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>78.4049793573972</v>
+        <v>78.4049760290226</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>78.4049793573972</v>
+        <v>78.4049760290226</v>
       </c>
       <c r="N13" s="14" t="n">
-        <v>78.4049793573972</v>
+        <v>78.4049760290226</v>
       </c>
       <c r="O13" s="15" t="n">
-        <v>0.111965804635547</v>
+        <v>0.11196579359557</v>
       </c>
       <c r="P13" s="16" t="n">
-        <v>0.190621661812273</v>
+        <v>0.190621648119031</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>0.118474613344074</v>
+        <v>0.11847460099614</v>
       </c>
       <c r="R13" s="18" t="n">
-        <v>1.02629087979575</v>
+        <v>1.02629088822162</v>
       </c>
       <c r="S13" s="19" t="n">
-        <v>1.07974223288812</v>
+        <v>1.0797531991514</v>
       </c>
     </row>
     <row r="14">
@@ -2206,46 +2206,46 @@
         <v>75.453</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-1.82728377649303</v>
+        <v>-1.82728321484319</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>77.4895097886708</v>
+        <v>77.4895121081624</v>
       </c>
       <c r="I14" s="9" t="n">
-        <v>72.7402952027254</v>
+        <v>72.7393241315929</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>73.840416884381</v>
+        <v>73.8404069713609</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>77.280283776493</v>
+        <v>77.2802832148432</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>77.280283776493</v>
+        <v>77.2802832148432</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>77.280283776493</v>
+        <v>77.2802832148432</v>
       </c>
       <c r="N14" s="14" t="n">
-        <v>77.280283776493</v>
+        <v>77.2802832148432</v>
       </c>
       <c r="O14" s="15" t="n">
-        <v>-0.014448575597656</v>
+        <v>-0.0144485404142923</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>0.160119353733145</v>
+        <v>0.160119366395433</v>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>-0.014344695835929</v>
+        <v>-0.0143446611572593</v>
       </c>
       <c r="R14" s="18" t="n">
-        <v>0.997299944047286</v>
+        <v>0.997299906947057</v>
       </c>
       <c r="S14" s="19" t="n">
-        <v>1.06241366715814</v>
+        <v>1.06242784267606</v>
       </c>
     </row>
     <row r="15">
@@ -2265,46 +2265,46 @@
         <v>72.058</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-3.24042147067453</v>
+        <v>-3.2404314045924</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>76.5217998296603</v>
+        <v>76.5218039338918</v>
       </c>
       <c r="I15" s="9" t="n">
-        <v>72.8226240254003</v>
+        <v>72.8214010114371</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>73.9404419579035</v>
+        <v>73.9404303959493</v>
       </c>
       <c r="K15" s="11" t="n">
-        <v>75.2984214706745</v>
+        <v>75.2984314045924</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>75.2984214706745</v>
+        <v>75.2984314045924</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>75.2984214706745</v>
+        <v>75.2984314045924</v>
       </c>
       <c r="N15" s="14" t="n">
-        <v>75.2984214706745</v>
+        <v>75.2984314045924</v>
       </c>
       <c r="O15" s="15" t="n">
-        <v>-0.0259796905723264</v>
+        <v>-0.0259795513773304</v>
       </c>
       <c r="P15" s="16" t="n">
-        <v>0.0625079308643792</v>
+        <v>0.062507989570717</v>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>-0.0256451220022736</v>
+        <v>-0.0256449863769409</v>
       </c>
       <c r="R15" s="18" t="n">
-        <v>0.984012681853942</v>
+        <v>0.984012758894755</v>
       </c>
       <c r="S15" s="19" t="n">
-        <v>1.03399764123318</v>
+        <v>1.03401514333357</v>
       </c>
     </row>
     <row r="16">
@@ -2324,46 +2324,46 @@
         <v>78.697</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0.637806506148738</v>
+        <v>0.637813360503729</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>76.5310525046534</v>
+        <v>76.5310494593479</v>
       </c>
       <c r="I16" s="9" t="n">
-        <v>72.8605726916228</v>
+        <v>72.8590756265151</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>73.9113519696762</v>
+        <v>73.9113389540351</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>78.0591934938513</v>
+        <v>78.0591866394963</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>78.0591934938513</v>
+        <v>78.0591866394963</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>78.0591934938513</v>
+        <v>78.0591866394963</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>78.0591934938513</v>
+        <v>78.0591866394963</v>
       </c>
       <c r="O16" s="15" t="n">
-        <v>0.0360082584430076</v>
+        <v>0.0360080387059987</v>
       </c>
       <c r="P16" s="16" t="n">
-        <v>0.113541856353393</v>
+        <v>0.113541793551164</v>
       </c>
       <c r="Q16" s="17" t="n">
-        <v>0.0366644076895015</v>
+        <v>0.0366641798959904</v>
       </c>
       <c r="R16" s="18" t="n">
-        <v>1.01996759405739</v>
+        <v>1.01996754508064</v>
       </c>
       <c r="S16" s="19" t="n">
-        <v>1.0713502599579</v>
+        <v>1.07137217935124</v>
       </c>
     </row>
     <row r="17">
@@ -2383,46 +2383,46 @@
         <v>79.056</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>4.52218204850226</v>
+        <v>4.52218861959937</v>
       </c>
       <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>75.7705311370841</v>
+        <v>75.7705241845465</v>
       </c>
       <c r="I17" s="9" t="n">
-        <v>72.8547405426793</v>
+        <v>72.852947427321</v>
       </c>
       <c r="J17" s="10" t="n">
-        <v>73.7545872189412</v>
+        <v>73.7545731973277</v>
       </c>
       <c r="K17" s="11" t="n">
-        <v>74.5338179514977</v>
+        <v>74.5338113804006</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>74.5338179514977</v>
+        <v>74.5338113804006</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>74.5338179514977</v>
+        <v>74.5338113804006</v>
       </c>
       <c r="N17" s="14" t="n">
-        <v>74.5338179514977</v>
+        <v>74.5338113804006</v>
       </c>
       <c r="O17" s="15" t="n">
-        <v>-0.0462144751999576</v>
+        <v>-0.0462144755528756</v>
       </c>
       <c r="P17" s="16" t="n">
-        <v>-0.0493739229016739</v>
+        <v>-0.0493739663562806</v>
       </c>
       <c r="Q17" s="17" t="n">
-        <v>-0.0451628486608848</v>
+        <v>-0.045162848997864</v>
       </c>
       <c r="R17" s="18" t="n">
-        <v>0.983678177161661</v>
+        <v>0.98367818069816</v>
       </c>
       <c r="S17" s="19" t="n">
-        <v>1.023046920438</v>
+        <v>1.02307201029521</v>
       </c>
     </row>
     <row r="18">
@@ -2442,46 +2442,46 @@
         <v>72.726</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>-1.7793378495922</v>
+        <v>-1.77934111302888</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>73.3372546991706</v>
+        <v>73.3372629213682</v>
       </c>
       <c r="I18" s="9" t="n">
-        <v>72.8089760578575</v>
+        <v>72.8068659337319</v>
       </c>
       <c r="J18" s="10" t="n">
-        <v>73.4923272125611</v>
+        <v>73.4923129159635</v>
       </c>
       <c r="K18" s="11" t="n">
-        <v>74.5053378495922</v>
+        <v>74.5053411130289</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>74.5053378495922</v>
+        <v>74.5053411130289</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>74.5053378495922</v>
+        <v>74.5053411130289</v>
       </c>
       <c r="N18" s="14" t="n">
-        <v>74.5053378495922</v>
+        <v>74.5053411130289</v>
       </c>
       <c r="O18" s="15" t="n">
-        <v>-0.000382182817651107</v>
+        <v>-0.000382050853641244</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>-0.0359075535349538</v>
+        <v>-0.0359075042996392</v>
       </c>
       <c r="Q18" s="17" t="n">
-        <v>-0.000382109795101004</v>
+        <v>-0.000381977881507178</v>
       </c>
       <c r="R18" s="18" t="n">
-        <v>1.0159275548998</v>
+        <v>1.01592748549824</v>
       </c>
       <c r="S18" s="19" t="n">
-        <v>1.02329880027961</v>
+        <v>1.02332850284811</v>
       </c>
     </row>
     <row r="19">
@@ -2501,46 +2501,46 @@
         <v>67.312</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-3.60194042850845</v>
+        <v>-3.60196075235606</v>
       </c>
       <c r="G19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>71.773604132509</v>
+        <v>71.7736098947672</v>
       </c>
       <c r="I19" s="9" t="n">
-        <v>72.7281771398254</v>
+        <v>72.7257312055958</v>
       </c>
       <c r="J19" s="10" t="n">
-        <v>73.1506476110616</v>
+        <v>73.1506340909943</v>
       </c>
       <c r="K19" s="11" t="n">
-        <v>70.9139404285085</v>
+        <v>70.9139607523561</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>70.9139404285085</v>
+        <v>70.9139607523561</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>70.9139404285085</v>
+        <v>70.9139607523561</v>
       </c>
       <c r="N19" s="14" t="n">
-        <v>70.9139404285085</v>
+        <v>70.9139607523561</v>
       </c>
       <c r="O19" s="15" t="n">
-        <v>-0.0494037366014774</v>
+        <v>-0.0494034938041354</v>
       </c>
       <c r="P19" s="16" t="n">
-        <v>-0.0582280605161644</v>
+        <v>-0.0582279148509453</v>
       </c>
       <c r="Q19" s="17" t="n">
-        <v>-0.0482032230809272</v>
+        <v>-0.0482029919871716</v>
       </c>
       <c r="R19" s="18" t="n">
-        <v>0.988022564640708</v>
+        <v>0.988022768484523</v>
       </c>
       <c r="S19" s="19" t="n">
-        <v>0.975054555432774</v>
+        <v>0.975087628227238</v>
       </c>
     </row>
     <row r="20">
@@ -2560,46 +2560,46 @@
         <v>73.631</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>1.02300702278084</v>
+        <v>1.02303227164483</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>73.1003335987384</v>
+        <v>73.1003224591951</v>
       </c>
       <c r="I20" s="9" t="n">
-        <v>72.618301917371</v>
+        <v>72.6155048497476</v>
       </c>
       <c r="J20" s="10" t="n">
-        <v>72.7606891281534</v>
+        <v>72.7606778444575</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>72.6079929772192</v>
+        <v>72.6079677283552</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>72.6079929772192</v>
+        <v>72.6079677283552</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>72.6079929772192</v>
+        <v>72.6079677283552</v>
       </c>
       <c r="N20" s="14" t="n">
-        <v>72.6079929772192</v>
+        <v>72.6079677283552</v>
       </c>
       <c r="O20" s="15" t="n">
-        <v>0.0236079766703811</v>
+        <v>0.0236073423293881</v>
       </c>
       <c r="P20" s="16" t="n">
-        <v>-0.0698341895764206</v>
+        <v>-0.0698344313567688</v>
       </c>
       <c r="Q20" s="17" t="n">
-        <v>0.0238888508870629</v>
+        <v>0.0238882013925985</v>
       </c>
       <c r="R20" s="18" t="n">
-        <v>0.993264864915367</v>
+        <v>0.993264670875908</v>
       </c>
       <c r="S20" s="19" t="n">
-        <v>0.999858039366391</v>
+        <v>0.999896205067939</v>
       </c>
     </row>
     <row r="21">
@@ -2619,46 +2619,46 @@
         <v>81.065</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>4.33693813645305</v>
+        <v>4.33694313517235</v>
       </c>
       <c r="G21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>75.7512015352095</v>
+        <v>75.7512000351344</v>
       </c>
       <c r="I21" s="9" t="n">
-        <v>72.4841746213377</v>
+        <v>72.4810161164889</v>
       </c>
       <c r="J21" s="10" t="n">
-        <v>72.3424089416345</v>
+        <v>72.3424019316969</v>
       </c>
       <c r="K21" s="11" t="n">
-        <v>76.7280618635469</v>
+        <v>76.7280568648276</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>76.7280618635469</v>
+        <v>76.7280568648276</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>76.7280618635469</v>
+        <v>76.7280568648276</v>
       </c>
       <c r="N21" s="14" t="n">
-        <v>76.7280618635469</v>
+        <v>76.7280568648276</v>
       </c>
       <c r="O21" s="15" t="n">
-        <v>0.0551924948205718</v>
+        <v>0.055192777414326</v>
       </c>
       <c r="P21" s="16" t="n">
-        <v>0.0294395748447649</v>
+        <v>0.0294395985364038</v>
       </c>
       <c r="Q21" s="17" t="n">
-        <v>0.0567440128474623</v>
+        <v>0.0567443114767623</v>
       </c>
       <c r="R21" s="18" t="n">
-        <v>1.0128956413699</v>
+        <v>1.01289559543928</v>
       </c>
       <c r="S21" s="19" t="n">
-        <v>1.05854915592789</v>
+        <v>1.05859521535285</v>
       </c>
     </row>
     <row r="22">
@@ -2678,46 +2678,46 @@
         <v>71.81</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>-1.89950308605178</v>
+        <v>-1.89952046080263</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>73.072992233864</v>
+        <v>73.0729858807242</v>
       </c>
       <c r="I22" s="9" t="n">
-        <v>72.3306130394813</v>
+        <v>72.3270895454206</v>
       </c>
       <c r="J22" s="10" t="n">
-        <v>71.9150007485481</v>
+        <v>71.9150005574761</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>73.7095030860518</v>
+        <v>73.7095204608026</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>73.7095030860518</v>
+        <v>73.7095204608026</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>73.7095030860518</v>
+        <v>73.7095204608026</v>
       </c>
       <c r="N22" s="14" t="n">
-        <v>73.7095030860518</v>
+        <v>73.7095204608026</v>
       </c>
       <c r="O22" s="15" t="n">
-        <v>-0.0401357729903033</v>
+        <v>-0.0401354721225359</v>
       </c>
       <c r="P22" s="16" t="n">
-        <v>-0.0106815804949036</v>
+        <v>-0.0106813906270012</v>
       </c>
       <c r="Q22" s="17" t="n">
-        <v>-0.0393410012475404</v>
+        <v>-0.0393407122161687</v>
       </c>
       <c r="R22" s="18" t="n">
-        <v>1.00871061705193</v>
+        <v>1.0087109425242</v>
       </c>
       <c r="S22" s="19" t="n">
-        <v>1.01906371297887</v>
+        <v>1.01911359801799</v>
       </c>
     </row>
     <row r="23">
@@ -2737,46 +2737,46 @@
         <v>60.116</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>-3.35581464363786</v>
+        <v>-3.35584099795607</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>0.180825615367491</v>
+        <v>0.180846375617293</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>69.4817640881192</v>
+        <v>69.4817153981094</v>
       </c>
       <c r="I23" s="9" t="n">
-        <v>72.165087389084</v>
+        <v>72.161204076611</v>
       </c>
       <c r="J23" s="10" t="n">
-        <v>71.5195865105471</v>
+        <v>71.5195962012243</v>
       </c>
       <c r="K23" s="11" t="n">
-        <v>63.4718146436379</v>
+        <v>63.4718409979561</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>68.3950112814934</v>
+        <v>68.3948513949265</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>68.3950112814934</v>
+        <v>68.3948513949265</v>
       </c>
       <c r="N23" s="14" t="n">
-        <v>68.3950112814934</v>
+        <v>68.3948513949265</v>
       </c>
       <c r="O23" s="15" t="n">
-        <v>-0.0748318462182698</v>
+        <v>-0.0748344196336579</v>
       </c>
       <c r="P23" s="16" t="n">
-        <v>-0.0355209304657742</v>
+        <v>-0.0355234615399176</v>
       </c>
       <c r="Q23" s="17" t="n">
-        <v>-0.0721004969787146</v>
+        <v>-0.0721028848465017</v>
       </c>
       <c r="R23" s="18" t="n">
-        <v>0.984359165014181</v>
+        <v>0.98435755368221</v>
       </c>
       <c r="S23" s="19" t="n">
-        <v>0.947757617374397</v>
+        <v>0.947806404703476</v>
       </c>
     </row>
     <row r="24">
@@ -2796,46 +2796,46 @@
         <v>70.882</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>0.999772545036831</v>
+        <v>0.999826293025698</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>67.6823080963583</v>
+        <v>67.6822503174048</v>
       </c>
       <c r="I24" s="9" t="n">
-        <v>71.995929693707</v>
+        <v>71.9917026694509</v>
       </c>
       <c r="J24" s="10" t="n">
-        <v>71.2062607009718</v>
+        <v>71.2062839418871</v>
       </c>
       <c r="K24" s="11" t="n">
-        <v>69.8822274549632</v>
+        <v>69.8821737069743</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>69.8822274549632</v>
+        <v>69.8821737069743</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>69.8822274549632</v>
+        <v>69.8821737069743</v>
       </c>
       <c r="N24" s="14" t="n">
-        <v>69.8822274549632</v>
+        <v>69.8821737069743</v>
       </c>
       <c r="O24" s="15" t="n">
-        <v>0.0215114726990606</v>
+        <v>0.021513041272469</v>
       </c>
       <c r="P24" s="16" t="n">
-        <v>-0.0375408465444182</v>
+        <v>-0.0375412521058121</v>
       </c>
       <c r="Q24" s="17" t="n">
-        <v>0.0217445124374478</v>
+        <v>0.0217461151199771</v>
       </c>
       <c r="R24" s="18" t="n">
-        <v>1.03250361018234</v>
+        <v>1.03250369748719</v>
       </c>
       <c r="S24" s="19" t="n">
-        <v>0.970641364758589</v>
+        <v>0.970697609804251</v>
       </c>
     </row>
     <row r="25">
@@ -2855,46 +2855,46 @@
         <v>68.268</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4.20684130278836</v>
+        <v>4.2068480278255</v>
       </c>
       <c r="G25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>64.6807546359221</v>
+        <v>64.6807543596501</v>
       </c>
       <c r="I25" s="9" t="n">
-        <v>71.8291156793445</v>
+        <v>71.8245743129048</v>
       </c>
       <c r="J25" s="10" t="n">
-        <v>71.0094949170175</v>
+        <v>71.009535134379</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>64.0611586972116</v>
+        <v>64.0611519721745</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>64.0611586972116</v>
+        <v>64.0611519721745</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>64.0611586972116</v>
+        <v>64.0611519721745</v>
       </c>
       <c r="N25" s="14" t="n">
-        <v>64.0611586972116</v>
+        <v>64.0611519721745</v>
       </c>
       <c r="O25" s="15" t="n">
-        <v>-0.0869731284824681</v>
+        <v>-0.0869724643381315</v>
       </c>
       <c r="P25" s="16" t="n">
-        <v>-0.165088272252492</v>
+        <v>-0.165088305506922</v>
       </c>
       <c r="Q25" s="17" t="n">
-        <v>-0.0832982715312419</v>
+        <v>-0.0832976627087785</v>
       </c>
       <c r="R25" s="18" t="n">
-        <v>0.990420706403349</v>
+        <v>0.99042060666098</v>
       </c>
       <c r="S25" s="19" t="n">
-        <v>0.891855038048775</v>
+        <v>0.891911335152384</v>
       </c>
     </row>
     <row r="26">
@@ -2914,46 +2914,46 @@
         <v>60.373</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-1.99589336423896</v>
+        <v>-1.99594857042959</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>63.784166851944</v>
+        <v>63.7842153805102</v>
       </c>
       <c r="I26" s="9" t="n">
-        <v>71.6693000080912</v>
+        <v>71.6644895403356</v>
       </c>
       <c r="J26" s="10" t="n">
-        <v>70.9571405896491</v>
+        <v>70.9572005824396</v>
       </c>
       <c r="K26" s="11" t="n">
-        <v>62.368893364239</v>
+        <v>62.3689485704296</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>62.368893364239</v>
+        <v>62.3689485704296</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>62.368893364239</v>
+        <v>62.3689485704296</v>
       </c>
       <c r="N26" s="14" t="n">
-        <v>62.368893364239</v>
+        <v>62.3689485704296</v>
       </c>
       <c r="O26" s="15" t="n">
-        <v>-0.0267715844013148</v>
+        <v>-0.0267705942674667</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>-0.153855462959414</v>
+        <v>-0.153854913442338</v>
       </c>
       <c r="Q26" s="17" t="n">
-        <v>-0.0264164021910883</v>
+        <v>-0.0264154382125369</v>
       </c>
       <c r="R26" s="18" t="n">
-        <v>0.977811523493124</v>
+        <v>0.977811645065512</v>
       </c>
       <c r="S26" s="19" t="n">
-        <v>0.870231652286234</v>
+        <v>0.870290836793386</v>
       </c>
     </row>
     <row r="27">
@@ -2973,46 +2973,46 @@
         <v>65.695</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-3.2126445275933</v>
+        <v>-3.21267236076944</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>66.9690334643461</v>
+        <v>66.9690356661877</v>
       </c>
       <c r="I27" s="9" t="n">
-        <v>71.5162823689281</v>
+        <v>71.5112667461435</v>
       </c>
       <c r="J27" s="10" t="n">
-        <v>71.0423074687327</v>
+        <v>71.0423891739976</v>
       </c>
       <c r="K27" s="11" t="n">
-        <v>68.9076445275933</v>
+        <v>68.9076723607694</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>68.9076445275933</v>
+        <v>68.9076723607694</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>68.9076445275933</v>
+        <v>68.9076723607694</v>
       </c>
       <c r="N27" s="14" t="n">
-        <v>68.9076445275933</v>
+        <v>68.9076723607694</v>
       </c>
       <c r="O27" s="15" t="n">
-        <v>0.099700475615761</v>
+        <v>0.0996999943802297</v>
       </c>
       <c r="P27" s="16" t="n">
-        <v>0.00749518475828737</v>
+        <v>0.00749794692705419</v>
       </c>
       <c r="Q27" s="17" t="n">
-        <v>0.104839942007108</v>
+        <v>0.104839410319</v>
       </c>
       <c r="R27" s="18" t="n">
-        <v>1.02894787281467</v>
+        <v>1.02894825459702</v>
       </c>
       <c r="S27" s="19" t="n">
-        <v>0.963523861211385</v>
+        <v>0.963591829597754</v>
       </c>
     </row>
     <row r="28">
@@ -3032,46 +3032,46 @@
         <v>69.771</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1.26605176420736</v>
+        <v>1.2661538779218</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>69.3929226336838</v>
+        <v>69.3928686603456</v>
       </c>
       <c r="I28" s="9" t="n">
-        <v>71.3640496966837</v>
+        <v>71.3589146116223</v>
       </c>
       <c r="J28" s="10" t="n">
-        <v>71.2151640680073</v>
+        <v>71.2152685369218</v>
       </c>
       <c r="K28" s="11" t="n">
-        <v>68.5049482357926</v>
+        <v>68.5048461220782</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>68.5049482357926</v>
+        <v>68.5048461220782</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>68.5049482357926</v>
+        <v>68.5048461220782</v>
       </c>
       <c r="N28" s="14" t="n">
-        <v>68.5049482357926</v>
+        <v>68.5048461220782</v>
       </c>
       <c r="O28" s="15" t="n">
-        <v>-0.0058611432405212</v>
+        <v>-0.0058630377650388</v>
       </c>
       <c r="P28" s="16" t="n">
-        <v>-0.0197085764053263</v>
+        <v>-0.019709283667555</v>
       </c>
       <c r="Q28" s="17" t="n">
-        <v>-0.00584400024933951</v>
+        <v>-0.00584588370047123</v>
       </c>
       <c r="R28" s="18" t="n">
-        <v>0.987203674896665</v>
+        <v>0.987202971207114</v>
       </c>
       <c r="S28" s="19" t="n">
-        <v>0.959936389918411</v>
+        <v>0.960004037266015</v>
       </c>
     </row>
     <row r="29">
@@ -3091,46 +3091,46 @@
         <v>64.776</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>3.92168032399593</v>
+        <v>3.9216855836301</v>
       </c>
       <c r="G29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>72.9258826855314</v>
+        <v>72.9258468096895</v>
       </c>
       <c r="I29" s="9" t="n">
-        <v>71.204958527536</v>
+        <v>71.1998145715749</v>
       </c>
       <c r="J29" s="10" t="n">
-        <v>71.4152055865061</v>
+        <v>71.4153327150145</v>
       </c>
       <c r="K29" s="11" t="n">
-        <v>60.8543196760041</v>
+        <v>60.8543144163699</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>72.9258826855314</v>
+        <v>72.9258468096895</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>72.9258826855314</v>
+        <v>72.9258468096895</v>
       </c>
       <c r="N29" s="14" t="n">
-        <v>72.9258826855314</v>
+        <v>72.9258468096895</v>
       </c>
       <c r="O29" s="15" t="n">
-        <v>0.0625376400207069</v>
+        <v>0.0625386386758116</v>
       </c>
       <c r="P29" s="16" t="n">
-        <v>0.138379076629247</v>
+        <v>0.138378636109533</v>
       </c>
       <c r="Q29" s="17" t="n">
-        <v>0.0645345272654174</v>
+        <v>0.0645355903687881</v>
       </c>
       <c r="R29" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S29" s="19" t="n">
-        <v>1.02416859996246</v>
+        <v>1.02424208895066</v>
       </c>
     </row>
     <row r="30">
@@ -3150,46 +3150,46 @@
         <v>87.046</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>-2.24836873564253</v>
+        <v>-2.24844356775335</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>79.6195208608723</v>
+        <v>79.6195741182023</v>
       </c>
       <c r="I30" s="9" t="n">
-        <v>71.0295784592495</v>
+        <v>71.0245642679986</v>
       </c>
       <c r="J30" s="10" t="n">
-        <v>71.5683761441014</v>
+        <v>71.5685236400042</v>
       </c>
       <c r="K30" s="11" t="n">
-        <v>89.2943687356425</v>
+        <v>89.2944435677534</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>79.6195208608723</v>
+        <v>79.6195741182023</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>79.6195208608723</v>
+        <v>79.6195741182023</v>
       </c>
       <c r="N30" s="14" t="n">
-        <v>79.6195208608723</v>
+        <v>79.6195741182023</v>
       </c>
       <c r="O30" s="15" t="n">
-        <v>0.0878156800315157</v>
+        <v>0.087816840878677</v>
       </c>
       <c r="P30" s="16" t="n">
-        <v>0.276590245010255</v>
+        <v>0.276589968937709</v>
       </c>
       <c r="Q30" s="17" t="n">
-        <v>0.0917868653603411</v>
+        <v>0.0917881327587602</v>
       </c>
       <c r="R30" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S30" s="19" t="n">
-        <v>1.12093472308231</v>
+        <v>1.12101460866091</v>
       </c>
     </row>
     <row r="31">
@@ -3209,46 +3209,46 @@
         <v>79.367</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-2.91035804233687</v>
+        <v>-2.91049072019295</v>
       </c>
       <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>80.3621953853648</v>
+        <v>80.362281365686</v>
       </c>
       <c r="I31" s="9" t="n">
-        <v>70.8295546671877</v>
+        <v>70.824840113039</v>
       </c>
       <c r="J31" s="10" t="n">
-        <v>71.6081732461605</v>
+        <v>71.6083358140924</v>
       </c>
       <c r="K31" s="11" t="n">
-        <v>82.2773580423369</v>
+        <v>82.277490720193</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>82.2773580423369</v>
+        <v>82.277490720193</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>82.2773580423369</v>
+        <v>82.277490720193</v>
       </c>
       <c r="N31" s="14" t="n">
-        <v>82.2773580423369</v>
+        <v>82.277490720193</v>
       </c>
       <c r="O31" s="15" t="n">
-        <v>0.0328366551847407</v>
+        <v>0.032837598854028</v>
       </c>
       <c r="P31" s="16" t="n">
-        <v>0.194023661763534</v>
+        <v>0.194025104917565</v>
       </c>
       <c r="Q31" s="17" t="n">
-        <v>0.0333817279070154</v>
+        <v>0.0333827030780742</v>
       </c>
       <c r="R31" s="18" t="n">
-        <v>1.02383163685099</v>
+        <v>1.02383219244103</v>
       </c>
       <c r="S31" s="19" t="n">
-        <v>1.16162466965859</v>
+        <v>1.16170386814676</v>
       </c>
     </row>
     <row r="32">
@@ -3268,46 +3268,46 @@
         <v>72.42</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>1.44776848718309</v>
+        <v>1.44806217873746</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>0.469214335666847</v>
+        <v>0.469147758237884</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>74.9258624684921</v>
+        <v>74.9259554361453</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>70.6019010407151</v>
+        <v>70.5976903999985</v>
       </c>
       <c r="J32" s="10" t="n">
-        <v>71.5083501216346</v>
+        <v>71.5085189918719</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>70.9722315128169</v>
+        <v>70.9719378212625</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>73.0707621461531</v>
+        <v>73.07093693609</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>73.0707621461531</v>
+        <v>73.07093693609</v>
       </c>
       <c r="N32" s="14" t="n">
-        <v>73.0707621461531</v>
+        <v>73.07093693609</v>
       </c>
       <c r="O32" s="15" t="n">
-        <v>-0.118667638809765</v>
+        <v>-0.118666859315623</v>
       </c>
       <c r="P32" s="16" t="n">
-        <v>0.0666494031153051</v>
+        <v>0.0666535445663916</v>
       </c>
       <c r="Q32" s="17" t="n">
-        <v>-0.111897077339873</v>
+        <v>-0.111896385068577</v>
       </c>
       <c r="R32" s="18" t="n">
-        <v>0.97524085460986</v>
+        <v>0.975241977372764</v>
       </c>
       <c r="S32" s="19" t="n">
-        <v>1.03496876244188</v>
+        <v>1.03503296668883</v>
       </c>
     </row>
     <row r="33">
@@ -3327,46 +3327,46 @@
         <v>74.787</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>3.70593289906636</v>
+        <v>3.70582951922358</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>70.6938261453214</v>
+        <v>70.6938810328214</v>
       </c>
       <c r="I33" s="9" t="n">
-        <v>70.3507863463055</v>
+        <v>70.3473213288087</v>
       </c>
       <c r="J33" s="10" t="n">
-        <v>71.2960059234558</v>
+        <v>71.2961687024657</v>
       </c>
       <c r="K33" s="11" t="n">
-        <v>71.0810671009337</v>
+        <v>71.0811704807764</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>71.0810671009337</v>
+        <v>71.0811704807764</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>71.0810671009337</v>
+        <v>71.0811704807764</v>
       </c>
       <c r="N33" s="14" t="n">
-        <v>71.0810671009337</v>
+        <v>71.0811704807764</v>
       </c>
       <c r="O33" s="15" t="n">
-        <v>-0.0276073002565941</v>
+        <v>-0.0276082379252422</v>
       </c>
       <c r="P33" s="16" t="n">
-        <v>-0.0252971306847654</v>
+        <v>-0.0252952335778428</v>
       </c>
       <c r="Q33" s="17" t="n">
-        <v>-0.0272297015492973</v>
+        <v>-0.0272306136850803</v>
       </c>
       <c r="R33" s="18" t="n">
-        <v>1.00547771957931</v>
+        <v>1.00547840127458</v>
       </c>
       <c r="S33" s="19" t="n">
-        <v>1.0103805627848</v>
+        <v>1.01043179950716</v>
       </c>
     </row>
     <row r="34">
@@ -3386,46 +3386,46 @@
         <v>67.608</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>-2.37781945757</v>
+        <v>-2.37784766780205</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>69.7386275447147</v>
+        <v>69.7387588396991</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>70.0819223886239</v>
+        <v>70.0794848784865</v>
       </c>
       <c r="J34" s="10" t="n">
-        <v>71.0060518646787</v>
+        <v>71.0061925647182</v>
       </c>
       <c r="K34" s="11" t="n">
-        <v>69.98581945757</v>
+        <v>69.985847667802</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>69.98581945757</v>
+        <v>69.985847667802</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>69.98581945757</v>
+        <v>69.985847667802</v>
       </c>
       <c r="N34" s="14" t="n">
-        <v>69.98581945757</v>
+        <v>69.985847667802</v>
       </c>
       <c r="O34" s="15" t="n">
-        <v>-0.0155283734988319</v>
+        <v>-0.0155294248063952</v>
       </c>
       <c r="P34" s="16" t="n">
-        <v>-0.120996726671293</v>
+        <v>-0.120996960321568</v>
       </c>
       <c r="Q34" s="17" t="n">
-        <v>-0.0154084299523588</v>
+        <v>-0.0154094650603791</v>
       </c>
       <c r="R34" s="18" t="n">
-        <v>1.00354454800099</v>
+        <v>1.00354306317196</v>
       </c>
       <c r="S34" s="19" t="n">
-        <v>0.998628705837706</v>
+        <v>0.99866384276587</v>
       </c>
     </row>
     <row r="35">
@@ -3445,46 +3445,46 @@
         <v>65.8</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>-2.9057214023125</v>
+        <v>-2.90593489223358</v>
       </c>
       <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>69.0435753646102</v>
+        <v>69.0435806211612</v>
       </c>
       <c r="I35" s="9" t="n">
-        <v>69.8014773978066</v>
+        <v>69.8003916837685</v>
       </c>
       <c r="J35" s="10" t="n">
-        <v>70.6723244642455</v>
+        <v>70.6724232063652</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>68.7057214023125</v>
+        <v>68.7059348922336</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>68.7057214023125</v>
+        <v>68.7059348922336</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>68.7057214023125</v>
+        <v>68.7059348922336</v>
       </c>
       <c r="N35" s="14" t="n">
-        <v>68.7057214023125</v>
+        <v>68.7059348922336</v>
       </c>
       <c r="O35" s="15" t="n">
-        <v>-0.0184601656239705</v>
+        <v>-0.0184574614044758</v>
       </c>
       <c r="P35" s="16" t="n">
-        <v>-0.164949835081493</v>
+        <v>-0.164948586899826</v>
       </c>
       <c r="Q35" s="17" t="n">
-        <v>-0.0182908204144639</v>
+        <v>-0.0182881656537729</v>
       </c>
       <c r="R35" s="18" t="n">
-        <v>0.995106656042745</v>
+        <v>0.995109672385326</v>
       </c>
       <c r="S35" s="19" t="n">
-        <v>0.984301822306006</v>
+        <v>0.984320191260625</v>
       </c>
     </row>
     <row r="36">
@@ -3504,46 +3504,46 @@
         <v>71.3555</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>1.81983210157665</v>
+        <v>1.8201860966587</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>69.6424265348203</v>
+        <v>69.6423387525888</v>
       </c>
       <c r="I36" s="9" t="n">
-        <v>69.5155595396582</v>
+        <v>69.5161938561349</v>
       </c>
       <c r="J36" s="10" t="n">
-        <v>70.3235590790626</v>
+        <v>70.3235915306579</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>69.5356678984234</v>
+        <v>69.5353139033413</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>69.5356678984234</v>
+        <v>69.5353139033413</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>69.5356678984234</v>
+        <v>69.5353139033413</v>
       </c>
       <c r="N36" s="14" t="n">
-        <v>69.5356678984234</v>
+        <v>69.5353139033413</v>
       </c>
       <c r="O36" s="15" t="n">
-        <v>0.0120073513706603</v>
+        <v>0.0119991532115553</v>
       </c>
       <c r="P36" s="16" t="n">
-        <v>-0.0483790526320087</v>
+        <v>-0.0483861735048096</v>
       </c>
       <c r="Q36" s="17" t="n">
-        <v>0.0120797290119559</v>
+        <v>0.0120714318553212</v>
       </c>
       <c r="R36" s="18" t="n">
-        <v>0.998467045998985</v>
+        <v>0.99846322149479</v>
       </c>
       <c r="S36" s="19" t="n">
-        <v>1.00028926414314</v>
+        <v>1.00027504450612</v>
       </c>
     </row>
     <row r="37">
@@ -3563,46 +3563,46 @@
         <v>73.692</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>3.52269529165224</v>
+        <v>3.52254681023757</v>
       </c>
       <c r="G37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>69.6052075423512</v>
+        <v>69.6051292162008</v>
       </c>
       <c r="I37" s="9" t="n">
-        <v>69.2295921324862</v>
+        <v>69.232359471571</v>
       </c>
       <c r="J37" s="10" t="n">
-        <v>69.9786580507268</v>
+        <v>69.9785959992769</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>70.1693047083478</v>
+        <v>70.1694531897624</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>70.1693047083478</v>
+        <v>70.1694531897624</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>70.1693047083478</v>
+        <v>70.1694531897624</v>
       </c>
       <c r="N37" s="14" t="n">
-        <v>70.1693047083478</v>
+        <v>70.1694531897624</v>
       </c>
       <c r="O37" s="15" t="n">
-        <v>0.0090711324445952</v>
+        <v>0.00907833934219432</v>
       </c>
       <c r="P37" s="16" t="n">
-        <v>-0.0128270780078641</v>
+        <v>-0.0128264248442641</v>
       </c>
       <c r="Q37" s="17" t="n">
-        <v>0.0091123998528353</v>
+        <v>0.00911967244877343</v>
       </c>
       <c r="R37" s="18" t="n">
-        <v>1.00810423797175</v>
+        <v>1.00810750558064</v>
       </c>
       <c r="S37" s="19" t="n">
-        <v>1.0135738568857</v>
+        <v>1.01353548723955</v>
       </c>
     </row>
     <row r="38">
@@ -3622,46 +3622,46 @@
         <v>64.2905</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-2.55582664169619</v>
+        <v>-2.55574472181175</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>66.5456173208621</v>
+        <v>66.545738153135</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>68.949011062322</v>
+        <v>68.9543685560916</v>
       </c>
       <c r="J38" s="10" t="n">
-        <v>69.6525842649319</v>
+        <v>69.6523936857661</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>66.8463266416962</v>
+        <v>66.8462447218117</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>66.8463266416962</v>
+        <v>66.8462447218117</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>66.8463266416962</v>
+        <v>66.8462447218117</v>
       </c>
       <c r="N38" s="14" t="n">
-        <v>66.8463266416962</v>
+        <v>66.8462447218117</v>
       </c>
       <c r="O38" s="15" t="n">
-        <v>-0.0485146077670344</v>
+        <v>-0.0485179493063433</v>
       </c>
       <c r="P38" s="16" t="n">
-        <v>-0.0448589848658869</v>
+        <v>-0.0448605403894353</v>
       </c>
       <c r="Q38" s="17" t="n">
-        <v>-0.0473565767889995</v>
+        <v>-0.047359760079127</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1.00451884486072</v>
+        <v>1.00451578984645</v>
       </c>
       <c r="S38" s="19" t="n">
-        <v>0.96950377694721</v>
+        <v>0.969427262138366</v>
       </c>
     </row>
     <row r="39">
@@ -3681,46 +3681,46 @@
         <v>60.527</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-2.96189467355596</v>
+        <v>-2.96213553830985</v>
       </c>
       <c r="G39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>64.9219803091866</v>
+        <v>64.9219115198975</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>68.6798395355573</v>
+        <v>68.6882868192855</v>
       </c>
       <c r="J39" s="10" t="n">
-        <v>69.3612538406596</v>
+        <v>69.360895949622</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>63.488894673556</v>
+        <v>63.4891355383099</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>63.488894673556</v>
+        <v>63.4891355383099</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>63.488894673556</v>
+        <v>63.4891355383099</v>
       </c>
       <c r="N39" s="14" t="n">
-        <v>63.488894673556</v>
+        <v>63.4891355383099</v>
       </c>
       <c r="O39" s="15" t="n">
-        <v>-0.0515313492005937</v>
+        <v>-0.051526329902142</v>
       </c>
       <c r="P39" s="16" t="n">
-        <v>-0.0759300189602687</v>
+        <v>-0.0759293845881925</v>
       </c>
       <c r="Q39" s="17" t="n">
-        <v>-0.0502261251562323</v>
+        <v>-0.0502213579457288</v>
       </c>
       <c r="R39" s="18" t="n">
-        <v>0.977926033235498</v>
+        <v>0.977930779485004</v>
       </c>
       <c r="S39" s="19" t="n">
-        <v>0.924418215052558</v>
+        <v>0.924308036759538</v>
       </c>
     </row>
     <row r="40">
@@ -3740,46 +3740,46 @@
         <v>70.291</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>2.17645566105495</v>
+        <v>2.1768140532779</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>67.1653364608063</v>
+        <v>67.1655651470777</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>68.4267865808206</v>
+        <v>68.438862393345</v>
       </c>
       <c r="J40" s="10" t="n">
-        <v>69.1065516087754</v>
+        <v>69.1059834055212</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>68.1145443389451</v>
+        <v>68.1141859467221</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>68.1145443389451</v>
+        <v>68.1141859467221</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>68.1145443389451</v>
+        <v>68.1141859467221</v>
       </c>
       <c r="N40" s="14" t="n">
-        <v>68.1145443389451</v>
+        <v>68.1141859467221</v>
       </c>
       <c r="O40" s="15" t="n">
-        <v>0.0703257600375388</v>
+        <v>0.0703167046108622</v>
       </c>
       <c r="P40" s="16" t="n">
-        <v>-0.0204373324141254</v>
+        <v>-0.0204374996939636</v>
       </c>
       <c r="Q40" s="17" t="n">
-        <v>0.0728576184728531</v>
+        <v>0.072847903333342</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>1.01413240710396</v>
+        <v>1.01412361821965</v>
       </c>
       <c r="S40" s="19" t="n">
-        <v>0.995436841952138</v>
+        <v>0.995255963713177</v>
       </c>
     </row>
     <row r="41">
@@ -3799,46 +3799,46 @@
         <v>72.597</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>3.37345034094563</v>
+        <v>3.37258806615638</v>
       </c>
       <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>68.9133199337248</v>
+        <v>68.9131356982571</v>
       </c>
       <c r="I41" s="9" t="n">
-        <v>68.1913168862019</v>
+        <v>68.2075939409119</v>
       </c>
       <c r="J41" s="10" t="n">
-        <v>68.8610006043095</v>
+        <v>68.8601778660838</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>69.2235496590544</v>
+        <v>69.2244119338436</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>69.2235496590544</v>
+        <v>69.2244119338436</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>69.2235496590544</v>
+        <v>69.2244119338436</v>
       </c>
       <c r="N41" s="14" t="n">
-        <v>69.2235496590544</v>
+        <v>69.2244119338436</v>
       </c>
       <c r="O41" s="15" t="n">
-        <v>0.016150354111357</v>
+        <v>0.0161680720377052</v>
       </c>
       <c r="P41" s="16" t="n">
-        <v>-0.0134781875525819</v>
+        <v>-0.0134679866089749</v>
       </c>
       <c r="Q41" s="17" t="n">
-        <v>0.0162814760176739</v>
+        <v>0.016299482577534</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>1.00450173820718</v>
+        <v>1.00451693617527</v>
       </c>
       <c r="S41" s="19" t="n">
-        <v>1.0151373051583</v>
+        <v>1.01490769479147</v>
       </c>
     </row>
     <row r="42">
@@ -3858,46 +3858,46 @@
         <v>60.973</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>-2.58139585949253</v>
+        <v>-2.57957838217503</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>68.8985050295476</v>
+        <v>68.8982812207338</v>
       </c>
       <c r="I42" s="9" t="n">
-        <v>67.9746999883897</v>
+        <v>67.9957772018486</v>
       </c>
       <c r="J42" s="10" t="n">
-        <v>68.5921638259427</v>
+        <v>68.5910421566359</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>63.5543958594925</v>
+        <v>63.552578382175</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>68.8985050295476</v>
+        <v>68.8982812207338</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>68.8985050295476</v>
+        <v>68.8982812207338</v>
       </c>
       <c r="N42" s="14" t="n">
-        <v>68.8985050295476</v>
+        <v>68.8982812207338</v>
       </c>
       <c r="O42" s="15" t="n">
-        <v>-0.00470663762255227</v>
+        <v>-0.0047223423137027</v>
       </c>
       <c r="P42" s="16" t="n">
-        <v>0.030699942554081</v>
+        <v>0.0306978575604633</v>
       </c>
       <c r="Q42" s="17" t="n">
-        <v>-0.00469557876051885</v>
+        <v>-0.0047112095863161</v>
       </c>
       <c r="R42" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S42" s="19" t="n">
-        <v>1.01359042469206</v>
+        <v>1.01327294217413</v>
       </c>
     </row>
     <row r="43">
@@ -3917,46 +3917,46 @@
         <v>67.704</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>-3.122985921293</v>
+        <v>-3.12498783763149</v>
       </c>
       <c r="G43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>70.9964685271024</v>
+        <v>70.9983790186469</v>
       </c>
       <c r="I43" s="9" t="n">
-        <v>67.7788505695559</v>
+        <v>67.8053434272632</v>
       </c>
       <c r="J43" s="10" t="n">
-        <v>68.2694170176297</v>
+        <v>68.2679602728423</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>70.826985921293</v>
+        <v>70.8289878376315</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>70.826985921293</v>
+        <v>70.8289878376315</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>70.826985921293</v>
+        <v>70.8289878376315</v>
       </c>
       <c r="N43" s="14" t="n">
-        <v>70.826985921293</v>
+        <v>70.8289878376315</v>
       </c>
       <c r="O43" s="15" t="n">
-        <v>0.0276056050583218</v>
+        <v>0.0276371179294732</v>
       </c>
       <c r="P43" s="16" t="n">
-        <v>0.115580705656755</v>
+        <v>0.115608005008868</v>
       </c>
       <c r="Q43" s="17" t="n">
-        <v>0.0279901703370538</v>
+        <v>0.0280225657692703</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>0.997612802307981</v>
+        <v>0.997614154247509</v>
       </c>
       <c r="S43" s="19" t="n">
-        <v>1.04497177697944</v>
+        <v>1.04459301077963</v>
       </c>
     </row>
     <row r="44">
@@ -3976,46 +3976,46 @@
         <v>77.328</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>2.49284540569968</v>
+        <v>2.4941018229355</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>0.594629495901702</v>
+        <v>0.596302260216955</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>72.5567097031106</v>
+        <v>72.5605764448438</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>67.606260690023</v>
+        <v>67.6387879332759</v>
       </c>
       <c r="J44" s="10" t="n">
-        <v>67.8636676293431</v>
+        <v>67.8618524056885</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>74.8351545943003</v>
+        <v>74.8338981770645</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>73.9115402401985</v>
+        <v>73.9161633319673</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>73.9115402401985</v>
+        <v>73.9161633319673</v>
       </c>
       <c r="N44" s="14" t="n">
-        <v>73.9115402401985</v>
+        <v>73.9161633319673</v>
       </c>
       <c r="O44" s="15" t="n">
-        <v>0.0426288908234374</v>
+        <v>0.0426631733699188</v>
       </c>
       <c r="P44" s="16" t="n">
-        <v>0.0851065797696164</v>
+        <v>0.0851801618796919</v>
       </c>
       <c r="Q44" s="17" t="n">
-        <v>0.0435505517957986</v>
+        <v>0.043586327979342</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>1.01867271190537</v>
+        <v>1.01868214054438</v>
       </c>
       <c r="S44" s="19" t="n">
-        <v>1.09326472852988</v>
+        <v>1.09280733127394</v>
       </c>
     </row>
     <row r="45">
@@ -4035,46 +4035,46 @@
         <v>70.704</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>3.21274894966836</v>
+        <v>3.21117539216124</v>
       </c>
       <c r="G45" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>72.9692876901181</v>
+        <v>72.9698911705172</v>
       </c>
       <c r="I45" s="9" t="n">
-        <v>67.4613274947081</v>
+        <v>67.5004958137628</v>
       </c>
       <c r="J45" s="10" t="n">
-        <v>67.3586109555739</v>
+        <v>67.3564438839837</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>67.4912510503316</v>
+        <v>67.4928246078388</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>72.9692876901181</v>
+        <v>72.9698911705172</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>72.9692876901181</v>
+        <v>72.9698911705172</v>
       </c>
       <c r="N45" s="14" t="n">
-        <v>72.9692876901181</v>
+        <v>72.9698911705172</v>
       </c>
       <c r="O45" s="15" t="n">
-        <v>-0.0128303399329956</v>
+        <v>-0.012884616661122</v>
       </c>
       <c r="P45" s="16" t="n">
-        <v>0.0541107477081506</v>
+        <v>0.0541063352080631</v>
       </c>
       <c r="Q45" s="17" t="n">
-        <v>-0.0127483820120419</v>
+        <v>-0.0128019653455266</v>
       </c>
       <c r="R45" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S45" s="19" t="n">
-        <v>1.08164618752636</v>
+        <v>1.08102748418093</v>
       </c>
     </row>
     <row r="46">
@@ -4094,46 +4094,46 @@
         <v>70.836</v>
       </c>
       <c r="F46" s="6" t="n">
-        <v>-2.86174445446524</v>
+        <v>-2.85832188555007</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>72.1620946686617</v>
+        <v>72.1615441453707</v>
       </c>
       <c r="I46" s="9" t="n">
-        <v>67.3523889282474</v>
+        <v>67.3987755222248</v>
       </c>
       <c r="J46" s="10" t="n">
-        <v>66.7681816538673</v>
+        <v>66.7657315911687</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>73.6977444544652</v>
+        <v>73.6943218855501</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>73.6977444544652</v>
+        <v>73.6943218855501</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>73.6977444544652</v>
+        <v>73.6943218855501</v>
       </c>
       <c r="N46" s="14" t="n">
-        <v>73.6977444544652</v>
+        <v>73.6943218855501</v>
       </c>
       <c r="O46" s="15" t="n">
-        <v>0.00993355826132262</v>
+        <v>0.00987884626327945</v>
       </c>
       <c r="P46" s="16" t="n">
-        <v>0.0696566554362748</v>
+        <v>0.0696104544241227</v>
       </c>
       <c r="Q46" s="17" t="n">
-        <v>0.00998305982430181</v>
+        <v>0.00992780314472452</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>1.02128056000667</v>
+        <v>1.02124092213287</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>1.09421129119826</v>
+        <v>1.09340742935677</v>
       </c>
     </row>
     <row r="47">
@@ -4153,46 +4153,46 @@
         <v>65.703</v>
       </c>
       <c r="F47" s="6" t="n">
-        <v>-2.58345077390571</v>
+        <v>-2.58743123562656</v>
       </c>
       <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>68.7703557166892</v>
+        <v>68.7706906044036</v>
       </c>
       <c r="I47" s="9" t="n">
-        <v>67.2912254103993</v>
+        <v>67.3453538842603</v>
       </c>
       <c r="J47" s="10" t="n">
-        <v>66.1343677654413</v>
+        <v>66.1317796471168</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>68.2864507739057</v>
+        <v>68.2904312356266</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>68.2864507739057</v>
+        <v>68.2904312356266</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>68.2864507739057</v>
+        <v>68.2904312356266</v>
       </c>
       <c r="N47" s="14" t="n">
-        <v>68.2864507739057</v>
+        <v>68.2904312356266</v>
       </c>
       <c r="O47" s="15" t="n">
-        <v>-0.0762608255400355</v>
+        <v>-0.076156094889133</v>
       </c>
       <c r="P47" s="16" t="n">
-        <v>-0.0358695928443216</v>
+        <v>-0.0358406449040939</v>
       </c>
       <c r="Q47" s="17" t="n">
-        <v>-0.0734254992553122</v>
+        <v>-0.0733284534229917</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>0.992963466049572</v>
+        <v>0.993016510892123</v>
       </c>
       <c r="S47" s="19" t="n">
-        <v>1.01478982374651</v>
+        <v>1.01403329698127</v>
       </c>
     </row>
     <row r="48">
@@ -4212,46 +4212,46 @@
         <v>65.884</v>
       </c>
       <c r="F48" s="6" t="n">
-        <v>2.49945320480183</v>
+        <v>2.50164309886692</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H48" s="8" t="n">
-        <v>63.6670962878137</v>
+        <v>63.6683328475565</v>
       </c>
       <c r="I48" s="9" t="n">
-        <v>67.2935832081259</v>
+        <v>67.3558924419452</v>
       </c>
       <c r="J48" s="10" t="n">
-        <v>65.5338051455169</v>
+        <v>65.5312951231734</v>
       </c>
       <c r="K48" s="11" t="n">
-        <v>63.3845467951982</v>
+        <v>63.3823569011331</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>63.3845467951982</v>
+        <v>63.3823569011331</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>63.3845467951982</v>
+        <v>63.3823569011331</v>
       </c>
       <c r="N48" s="14" t="n">
-        <v>63.3845467951982</v>
+        <v>63.3823569011331</v>
       </c>
       <c r="O48" s="15" t="n">
-        <v>-0.074491278437148</v>
+        <v>-0.0745841173238561</v>
       </c>
       <c r="P48" s="16" t="n">
-        <v>-0.142426925630147</v>
+        <v>-0.142510189327949</v>
       </c>
       <c r="Q48" s="17" t="n">
-        <v>-0.0717844304858894</v>
+        <v>-0.0718706009859398</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>0.995562079801186</v>
+        <v>0.995508348756231</v>
       </c>
       <c r="S48" s="19" t="n">
-        <v>0.941910710849831</v>
+        <v>0.94100686076965</v>
       </c>
     </row>
     <row r="49">
@@ -4271,46 +4271,46 @@
         <v>63.259</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>2.54314280657209</v>
+        <v>2.54108622384042</v>
       </c>
       <c r="G49" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>60.0926128193624</v>
+        <v>60.0904409986771</v>
       </c>
       <c r="I49" s="9" t="n">
-        <v>67.3758306042417</v>
+        <v>67.4466434106995</v>
       </c>
       <c r="J49" s="10" t="n">
-        <v>65.0538900643574</v>
+        <v>65.0517783486263</v>
       </c>
       <c r="K49" s="11" t="n">
-        <v>60.7158571934279</v>
+        <v>60.7179137761596</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>60.7158571934279</v>
+        <v>60.7179137761596</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>60.7158571934279</v>
+        <v>60.7179137761596</v>
       </c>
       <c r="N49" s="14" t="n">
-        <v>60.7158571934279</v>
+        <v>60.7179137761596</v>
       </c>
       <c r="O49" s="15" t="n">
-        <v>-0.0430151876127464</v>
+        <v>-0.0429467660019757</v>
       </c>
       <c r="P49" s="16" t="n">
-        <v>-0.167925861476507</v>
+        <v>-0.167904558960175</v>
       </c>
       <c r="Q49" s="17" t="n">
-        <v>-0.04210315820973</v>
+        <v>-0.0420376151226063</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>1.01037139749505</v>
+        <v>1.01044213966571</v>
       </c>
       <c r="S49" s="19" t="n">
-        <v>0.901151891545</v>
+        <v>0.900236256479556</v>
       </c>
     </row>
     <row r="50">
@@ -4330,46 +4330,46 @@
         <v>55.23</v>
       </c>
       <c r="F50" s="6" t="n">
-        <v>-2.9261516490117</v>
+        <v>-2.92019672255311</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>59.1570278649809</v>
+        <v>59.1574510187585</v>
       </c>
       <c r="I50" s="9" t="n">
-        <v>67.5518927338027</v>
+        <v>67.6313755462304</v>
       </c>
       <c r="J50" s="10" t="n">
-        <v>64.7712725004744</v>
+        <v>64.7699849616531</v>
       </c>
       <c r="K50" s="11" t="n">
-        <v>58.1561516490117</v>
+        <v>58.1501967225531</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>58.1561516490117</v>
+        <v>58.1501967225531</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>58.1561516490117</v>
+        <v>58.1501967225531</v>
       </c>
       <c r="N50" s="14" t="n">
-        <v>58.1561516490117</v>
+        <v>58.1501967225531</v>
       </c>
       <c r="O50" s="15" t="n">
-        <v>-0.0430732400297098</v>
+        <v>-0.0432095124190618</v>
       </c>
       <c r="P50" s="16" t="n">
-        <v>-0.210882882786949</v>
+        <v>-0.210927039767562</v>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>-0.0421587648225328</v>
+        <v>-0.0422892832430397</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>0.983081026006689</v>
+        <v>0.982973331696019</v>
       </c>
       <c r="S50" s="19" t="n">
-        <v>0.860910764975659</v>
+        <v>0.859810942079741</v>
       </c>
     </row>
     <row r="51">
@@ -4389,46 +4389,46 @@
         <v>60.865</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>-1.20419465106803</v>
+        <v>-1.21288223835042</v>
       </c>
       <c r="G51" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>61.7376322731934</v>
+        <v>61.7386604366682</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>67.8315322484837</v>
+        <v>67.9196521482238</v>
       </c>
       <c r="J51" s="10" t="n">
-        <v>64.7409122680251</v>
+        <v>64.7410012775691</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>62.069194651068</v>
+        <v>62.0778822383504</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>62.069194651068</v>
+        <v>62.0778822383504</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>62.069194651068</v>
+        <v>62.0778822383504</v>
       </c>
       <c r="N51" s="14" t="n">
-        <v>62.069194651068</v>
+        <v>62.0778822383504</v>
       </c>
       <c r="O51" s="15" t="n">
-        <v>0.0651181428012072</v>
+        <v>0.0653604998865324</v>
       </c>
       <c r="P51" s="16" t="n">
-        <v>-0.0910467018328837</v>
+        <v>-0.0909724669308444</v>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>0.0672851089885145</v>
+        <v>0.0675438044438119</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>1.00537050686375</v>
+        <v>1.00549447946041</v>
       </c>
       <c r="S51" s="19" t="n">
-        <v>0.915049278611211</v>
+        <v>0.913989990744879</v>
       </c>
     </row>
     <row r="52">
@@ -4448,46 +4448,46 @@
         <v>66.823</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>1.63523015734154</v>
+        <v>1.64119740292303</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>65.0294640210303</v>
+        <v>65.0270784798746</v>
       </c>
       <c r="I52" s="9" t="n">
-        <v>68.2186394617809</v>
+        <v>68.3151107796003</v>
       </c>
       <c r="J52" s="10" t="n">
-        <v>64.984693576909</v>
+        <v>64.9868146704941</v>
       </c>
       <c r="K52" s="11" t="n">
-        <v>65.1877698426585</v>
+        <v>65.181802597077</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>65.1877698426585</v>
+        <v>65.181802597077</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>65.1877698426585</v>
+        <v>65.181802597077</v>
       </c>
       <c r="N52" s="14" t="n">
-        <v>65.1877698426585</v>
+        <v>65.181802597077</v>
       </c>
       <c r="O52" s="15" t="n">
-        <v>0.0490220667456083</v>
+        <v>0.0487905668403197</v>
       </c>
       <c r="P52" s="16" t="n">
-        <v>0.0284489380871757</v>
+        <v>0.0283903247515827</v>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>0.0502435259410403</v>
+        <v>0.0500004228045172</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>1.0024343706966</v>
+        <v>1.0023793798033</v>
       </c>
       <c r="S52" s="19" t="n">
-        <v>0.955571239135889</v>
+        <v>0.954134478495804</v>
       </c>
     </row>
     <row r="53">
@@ -4507,46 +4507,46 @@
         <v>66.726</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>1.96577532019653</v>
+        <v>1.96333205721213</v>
       </c>
       <c r="G53" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H53" s="8" t="n">
-        <v>64.5934452343711</v>
+        <v>64.6031306104431</v>
       </c>
       <c r="I53" s="9" t="n">
-        <v>68.7135032261929</v>
+        <v>68.8177378970873</v>
       </c>
       <c r="J53" s="10" t="n">
-        <v>65.5111420489413</v>
+        <v>65.5160969193519</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>64.7602246798035</v>
+        <v>64.7626679427879</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>64.7602246798035</v>
+        <v>64.7626679427879</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>64.7602246798035</v>
+        <v>64.7626679427879</v>
       </c>
       <c r="N53" s="14" t="n">
-        <v>64.7602246798035</v>
+        <v>64.7626679427879</v>
       </c>
       <c r="O53" s="15" t="n">
-        <v>-0.00658027401116443</v>
+        <v>-0.00645100335683892</v>
       </c>
       <c r="P53" s="16" t="n">
-        <v>0.0666113874253815</v>
+        <v>0.06661549969486</v>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>-0.00655867141776645</v>
+        <v>-0.00643024030617856</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>1.00258198714788</v>
+        <v>1.00246949847225</v>
       </c>
       <c r="S53" s="19" t="n">
-        <v>0.942467224624309</v>
+        <v>0.941075221618537</v>
       </c>
     </row>
     <row r="54">
@@ -4566,46 +4566,46 @@
         <v>61.185</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>-2.9802906444212</v>
+        <v>-2.97531232927326</v>
       </c>
       <c r="G54" s="7" t="n">
-        <v>0.521424122701073</v>
+        <v>0.526140933006744</v>
       </c>
       <c r="H54" s="8" t="n">
-        <v>58.9265629239773</v>
+        <v>58.9491884126218</v>
       </c>
       <c r="I54" s="9" t="n">
-        <v>69.3145181007057</v>
+        <v>69.425561639798</v>
       </c>
       <c r="J54" s="10" t="n">
-        <v>66.3297986872655</v>
+        <v>66.338494742699</v>
       </c>
       <c r="K54" s="11" t="n">
-        <v>64.1652906444212</v>
+        <v>64.1603123292733</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>61.6581619296796</v>
+        <v>61.6909740121426</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>61.6581619296796</v>
+        <v>61.6909740121426</v>
       </c>
       <c r="N54" s="14" t="n">
-        <v>61.6581619296796</v>
+        <v>61.6909740121426</v>
       </c>
       <c r="O54" s="15" t="n">
-        <v>-0.0490859859806829</v>
+        <v>-0.0485916934336751</v>
       </c>
       <c r="P54" s="16" t="n">
-        <v>0.0602173662006291</v>
+        <v>0.060890203114587</v>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>-0.047900741009803</v>
+        <v>-0.0474300091120224</v>
       </c>
       <c r="R54" s="18" t="n">
-        <v>1.04635598735372</v>
+        <v>1.04651099825717</v>
       </c>
       <c r="S54" s="19" t="n">
-        <v>0.889541810564096</v>
+        <v>0.888591644849991</v>
       </c>
     </row>
     <row r="55">
@@ -4625,46 +4625,46 @@
         <v>33.184</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>0.454780375040798</v>
+        <v>0.441334922263408</v>
       </c>
       <c r="G55" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="8" t="n">
-        <v>55.6162506443746</v>
+        <v>55.6322183672127</v>
       </c>
       <c r="I55" s="9" t="n">
-        <v>70.0176078452138</v>
+        <v>70.134075728124</v>
       </c>
       <c r="J55" s="10" t="n">
-        <v>67.4464499081796</v>
+        <v>67.4598877142092</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>32.7292196249592</v>
+        <v>32.7426650777366</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>55.6162506443746</v>
+        <v>55.6322183672127</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>55.6162506443746</v>
+        <v>55.6322183672127</v>
       </c>
       <c r="N55" s="14" t="n">
-        <v>55.6162506443746</v>
+        <v>55.6322183672127</v>
       </c>
       <c r="O55" s="15" t="n">
-        <v>-0.10313017591704</v>
+        <v>-0.103375131447716</v>
       </c>
       <c r="P55" s="16" t="n">
-        <v>-0.103963714093113</v>
+        <v>-0.103831890501505</v>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>-0.0979904540812566</v>
+        <v>-0.0982113792487265</v>
       </c>
       <c r="R55" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S55" s="19" t="n">
-        <v>0.794318063069565</v>
+        <v>0.793226656081873</v>
       </c>
     </row>
     <row r="56">
@@ -4684,46 +4684,46 @@
         <v>75.79</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>0.707607099327488</v>
+        <v>0.722915323995523</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>62.15558365929</v>
+        <v>62.1599059406315</v>
       </c>
       <c r="I56" s="9" t="n">
-        <v>70.8139109970052</v>
+        <v>70.9339397651895</v>
       </c>
       <c r="J56" s="10" t="n">
-        <v>68.8435239441938</v>
+        <v>68.8629178039037</v>
       </c>
       <c r="K56" s="11" t="n">
-        <v>75.0823929006725</v>
+        <v>75.0670846760045</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>62.15558365929</v>
+        <v>62.1599059406315</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>62.15558365929</v>
+        <v>62.1599059406315</v>
       </c>
       <c r="N56" s="14" t="n">
-        <v>62.15558365929</v>
+        <v>62.1599059406315</v>
       </c>
       <c r="O56" s="15" t="n">
-        <v>0.111165219254917</v>
+        <v>0.1109476924101</v>
       </c>
       <c r="P56" s="16" t="n">
-        <v>-0.0465146482336662</v>
+        <v>-0.0463610476550549</v>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>0.117579537260246</v>
+        <v>0.11733646014853</v>
       </c>
       <c r="R56" s="18" t="n">
         <v>1</v>
       </c>
       <c r="S56" s="19" t="n">
-        <v>0.877731264721683</v>
+        <v>0.876306971618912</v>
       </c>
     </row>
     <row r="57">
@@ -4743,46 +4743,46 @@
         <v>74.809</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.05862670455717</v>
+        <v>1.05686412081018</v>
       </c>
       <c r="G57" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>72.4931676914316</v>
+        <v>72.4959943720126</v>
       </c>
       <c r="I57" s="9" t="n">
-        <v>71.685565245117</v>
+        <v>71.8067496932684</v>
       </c>
       <c r="J57" s="10" t="n">
-        <v>70.4442980314991</v>
+        <v>70.4710886350683</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>73.7503732954428</v>
+        <v>73.7521358791898</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>73.7503732954428</v>
+        <v>73.7521358791898</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>73.7503732954428</v>
+        <v>73.7521358791898</v>
       </c>
       <c r="N57" s="14" t="n">
-        <v>73.7503732954428</v>
+        <v>73.7521358791898</v>
       </c>
       <c r="O57" s="15" t="n">
-        <v>0.171045401257096</v>
+        <v>0.170999762997682</v>
       </c>
       <c r="P57" s="16" t="n">
-        <v>0.138822072654777</v>
+        <v>0.138806325031936</v>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.186544618416109</v>
+        <v>0.186490467820688</v>
       </c>
       <c r="R57" s="18" t="n">
-        <v>1.0173424012779</v>
+        <v>1.01732704707423</v>
       </c>
       <c r="S57" s="19" t="n">
-        <v>1.02880367955899</v>
+        <v>1.02709196829311</v>
       </c>
     </row>
     <row r="58">
@@ -4802,46 +4802,46 @@
         <v>74.937</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>-2.55479362292513</v>
+        <v>-2.5582132648688</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>78.6101144601967</v>
+        <v>78.6220995334314</v>
       </c>
       <c r="I58" s="9" t="n">
-        <v>72.6092968240007</v>
+        <v>72.7286176834943</v>
       </c>
       <c r="J58" s="10" t="n">
-        <v>72.138609704862</v>
+        <v>72.1743887716729</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>77.4917936229251</v>
+        <v>77.4952132648688</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>77.4917936229251</v>
+        <v>77.4952132648688</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>77.4917936229251</v>
+        <v>77.4952132648688</v>
       </c>
       <c r="N58" s="14" t="n">
-        <v>77.4917936229251</v>
+        <v>77.4952132648688</v>
       </c>
       <c r="O58" s="15" t="n">
-        <v>0.049485985176001</v>
+        <v>0.0495062142532076</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>0.256797011096498</v>
+        <v>0.25618398000355</v>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0507308663034725</v>
+        <v>0.0507521218342795</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>0.985773830187745</v>
+        <v>0.985667054489133</v>
       </c>
       <c r="S58" s="19" t="n">
-        <v>1.06724341114003</v>
+        <v>1.06553947721264</v>
       </c>
     </row>
     <row r="59">
@@ -4861,46 +4861,46 @@
         <v>83.357</v>
       </c>
       <c r="F59" s="6" t="n">
-        <v>1.73193788945066</v>
+        <v>1.70754441212578</v>
       </c>
       <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H59" s="8" t="n">
-        <v>80.8127307163717</v>
+        <v>80.8149281160344</v>
       </c>
       <c r="I59" s="9" t="n">
-        <v>73.5631224731387</v>
+        <v>73.6768717733669</v>
       </c>
       <c r="J59" s="10" t="n">
-        <v>73.8328268753688</v>
+        <v>73.8792120139076</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>81.6250621105493</v>
+        <v>81.6494555878742</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>81.6250621105493</v>
+        <v>81.6494555878742</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>81.6250621105493</v>
+        <v>81.6494555878742</v>
       </c>
       <c r="N59" s="14" t="n">
-        <v>81.6250621105493</v>
+        <v>81.6494555878742</v>
       </c>
       <c r="O59" s="15" t="n">
-        <v>0.0519643065056285</v>
+        <v>0.052218981635043</v>
       </c>
       <c r="P59" s="16" t="n">
-        <v>0.467647695859294</v>
+        <v>0.467664924826995</v>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>0.0533381445232342</v>
+        <v>0.0536064377138592</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>1.01005202258328</v>
+        <v>1.0103264024518</v>
       </c>
       <c r="S59" s="19" t="n">
-        <v>1.10959213484113</v>
+        <v>1.10821012921167</v>
       </c>
     </row>
     <row r="60">
@@ -4920,46 +4920,46 @@
         <v>78.522</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>-0.25010944521655</v>
+        <v>-0.207576531585893</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H60" s="8" t="n">
-        <v>77.8990034711661</v>
+        <v>77.878831588296</v>
       </c>
       <c r="I60" s="9" t="n">
-        <v>74.5281104925132</v>
+        <v>74.6318191226241</v>
       </c>
       <c r="J60" s="10" t="n">
-        <v>75.460083373696</v>
+        <v>75.5185562844288</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>78.7721094452166</v>
+        <v>78.7295765315859</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>78.7721094452166</v>
+        <v>78.7295765315859</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>78.7721094452166</v>
+        <v>78.7295765315859</v>
       </c>
       <c r="N60" s="14" t="n">
-        <v>78.7721094452166</v>
+        <v>78.7295765315859</v>
       </c>
       <c r="O60" s="15" t="n">
-        <v>-0.035577355360507</v>
+        <v>-0.0364162533233829</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>0.26733761969015</v>
+        <v>0.266565245558447</v>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>-0.0349519202995382</v>
+        <v>-0.0357611576864201</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>1.01120817899004</v>
+        <v>1.01092395617576</v>
       </c>
       <c r="S60" s="19" t="n">
-        <v>1.05694494231314</v>
+        <v>1.05490630480585</v>
       </c>
     </row>
     <row r="61">
@@ -4979,46 +4979,46 @@
         <v>73.12</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>0.501953746419341</v>
+        <v>0.504240842226624</v>
       </c>
       <c r="G61" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H61" s="8" t="n">
-        <v>74.3896881932484</v>
+        <v>74.3861372723834</v>
       </c>
       <c r="I61" s="9" t="n">
-        <v>75.4903678943794</v>
+        <v>75.578749755888</v>
       </c>
       <c r="J61" s="10" t="n">
-        <v>76.992474206696</v>
+        <v>77.0642707237626</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>72.6180462535807</v>
+        <v>72.6157591577734</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>72.6180462535807</v>
+        <v>72.6157591577734</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>72.6180462535807</v>
+        <v>72.6157591577734</v>
       </c>
       <c r="N61" s="14" t="n">
-        <v>72.6180462535807</v>
+        <v>72.6157591577734</v>
       </c>
       <c r="O61" s="15" t="n">
-        <v>-0.0813455312333038</v>
+        <v>-0.0808369318754656</v>
       </c>
       <c r="P61" s="16" t="n">
-        <v>-0.0153535092944694</v>
+        <v>-0.0154080516837898</v>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0781249002340841</v>
+        <v>-0.0776559158978796</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>0.976184307493461</v>
+        <v>0.976200160681454</v>
       </c>
       <c r="S61" s="19" t="n">
-        <v>0.961951150578343</v>
+        <v>0.960795982896187</v>
       </c>
     </row>
     <row r="62">
@@ -5038,46 +5038,46 @@
         <v>76.726</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>-2.01285499936331</v>
+        <v>-2.04852242253549</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>80.0404364531006</v>
+        <v>80.058464813932</v>
       </c>
       <c r="I62" s="9" t="n">
-        <v>76.4386541903382</v>
+        <v>76.5055147961615</v>
       </c>
       <c r="J62" s="10" t="n">
-        <v>78.4186545115791</v>
+        <v>78.5042595736707</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>78.7388549993633</v>
+        <v>78.7745224225355</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>78.7388549993633</v>
+        <v>78.7745224225355</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>78.7388549993633</v>
+        <v>78.7745224225355</v>
       </c>
       <c r="N62" s="14" t="n">
-        <v>78.7388549993633</v>
+        <v>78.7745224225355</v>
       </c>
       <c r="O62" s="15" t="n">
-        <v>0.0809232819446324</v>
+        <v>0.0814076585101127</v>
       </c>
       <c r="P62" s="16" t="n">
-        <v>0.0160928185829119</v>
+        <v>0.0165082345575871</v>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>0.0842877089313161</v>
+        <v>0.0848130397064479</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>0.983738451320166</v>
+        <v>0.983962440519181</v>
       </c>
       <c r="S62" s="19" t="n">
-        <v>1.03009211547992</v>
+        <v>1.02965809239268</v>
       </c>
     </row>
     <row r="63">
@@ -5097,46 +5097,46 @@
         <v>91.187</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>2.08498106143275</v>
+        <v>2.04954918686317</v>
       </c>
       <c r="G63" s="7" t="n">
-        <v>0.922037217446325</v>
+        <v>0.91432588394391</v>
       </c>
       <c r="H63" s="8" t="n">
-        <v>83.53986037445</v>
+        <v>83.5393979941284</v>
       </c>
       <c r="I63" s="9" t="n">
-        <v>77.3599336909649</v>
+        <v>77.3981134973233</v>
       </c>
       <c r="J63" s="10" t="n">
-        <v>79.7054072857895</v>
+        <v>79.8041845180852</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>89.1020189385672</v>
+        <v>89.1374508131368</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>88.6683775799039</v>
+        <v>88.657842586233</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>88.6683775799039</v>
+        <v>88.657842586233</v>
       </c>
       <c r="N63" s="14" t="n">
-        <v>88.6683775799039</v>
+        <v>88.657842586233</v>
       </c>
       <c r="O63" s="15" t="n">
-        <v>0.118766572068684</v>
+        <v>0.118194870383195</v>
       </c>
       <c r="P63" s="16" t="n">
-        <v>0.0862886384063686</v>
+        <v>0.0858350732151063</v>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>0.126107022773202</v>
+        <v>0.125463409485173</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>1.06139006197121</v>
+        <v>1.06126982854801</v>
       </c>
       <c r="S63" s="19" t="n">
-        <v>1.14617959645769</v>
+        <v>1.14547808183076</v>
       </c>
     </row>
     <row r="64">
@@ -5156,46 +5156,46 @@
         <v>75.475</v>
       </c>
       <c r="F64" s="6" t="n">
-        <v>-0.39541459860768</v>
+        <v>-0.331003223785546</v>
       </c>
       <c r="G64" s="7" t="n">
-        <v>1</v>
+        <v>0.993683656518232</v>
       </c>
       <c r="H64" s="8" t="n">
-        <v>80.9571281533998</v>
+        <v>80.8878345476836</v>
       </c>
       <c r="I64" s="9" t="n">
-        <v>78.2426083323405</v>
+        <v>78.2439632430188</v>
       </c>
       <c r="J64" s="10" t="n">
-        <v>80.8211165292109</v>
+        <v>80.9310585551823</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>75.8704145986077</v>
+        <v>75.8060032237855</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>75.8704145986077</v>
+        <v>75.8381018159437</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>75.8704145986077</v>
+        <v>75.8381018159437</v>
       </c>
       <c r="N64" s="14" t="n">
-        <v>75.8704145986077</v>
+        <v>75.8381018159437</v>
       </c>
       <c r="O64" s="15" t="n">
-        <v>-0.155876502014158</v>
+        <v>-0.156183666621706</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>-0.0368365766391836</v>
+        <v>-0.036726664146125</v>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>-0.144335143267545</v>
+        <v>-0.144597932865558</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>0.937167811274707</v>
+        <v>0.937571171734569</v>
       </c>
       <c r="S64" s="19" t="n">
-        <v>0.969681561181386</v>
+        <v>0.969251794932694</v>
       </c>
     </row>
     <row r="65">
@@ -5215,46 +5215,46 @@
         <v>82.884</v>
       </c>
       <c r="F65" s="6" t="n">
-        <v>-0.1155409895062</v>
+        <v>-0.0110951642500844</v>
       </c>
       <c r="G65" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H65" s="8" t="n">
-        <v>80.3983028914141</v>
+        <v>80.4018284316034</v>
       </c>
       <c r="I65" s="9" t="n">
-        <v>79.0821478279765</v>
+        <v>79.0375187475739</v>
       </c>
       <c r="J65" s="10" t="n">
-        <v>81.7789810931971</v>
+        <v>81.8961629734791</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>82.9995409895062</v>
+        <v>82.8950951642501</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>82.9995409895062</v>
+        <v>82.8950951642501</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>82.9995409895062</v>
+        <v>82.8950951642501</v>
       </c>
       <c r="N65" s="14" t="n">
-        <v>82.9995409895062</v>
+        <v>82.8950951642501</v>
       </c>
       <c r="O65" s="15" t="n">
-        <v>0.0898082636071736</v>
+        <v>0.0889750658649709</v>
       </c>
       <c r="P65" s="16" t="n">
-        <v>0.142960259488028</v>
+        <v>0.141557922490938</v>
       </c>
       <c r="Q65" s="17" t="n">
-        <v>0.0939645107861233</v>
+        <v>0.093053401645435</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>1.03235439063441</v>
+        <v>1.03101007503539</v>
       </c>
       <c r="S65" s="19" t="n">
-        <v>1.04953574566603</v>
+        <v>1.04880690180819</v>
       </c>
     </row>
     <row r="66">
@@ -5274,46 +5274,46 @@
         <v>81.745</v>
       </c>
       <c r="F66" s="6" t="n">
-        <v>-1.34539606404486</v>
+        <v>-1.56854003902848</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H66" s="8" t="n">
-        <v>83.7320024159884</v>
+        <v>83.8302515215122</v>
       </c>
       <c r="I66" s="9" t="n">
-        <v>79.8725392703009</v>
+        <v>79.7717310619228</v>
       </c>
       <c r="J66" s="10" t="n">
-        <v>82.5674463194491</v>
+        <v>82.6853142777963</v>
       </c>
       <c r="K66" s="11" t="n">
-        <v>83.0903960640449</v>
+        <v>83.3135400390285</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>83.0903960640449</v>
+        <v>83.3135400390285</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>83.0903960640449</v>
+        <v>83.3135400390285</v>
       </c>
       <c r="N66" s="14" t="n">
-        <v>83.0903960640449</v>
+        <v>83.3135400390285</v>
       </c>
       <c r="O66" s="15" t="n">
-        <v>0.00109404681840183</v>
+        <v>0.00503518674994657</v>
       </c>
       <c r="P66" s="16" t="n">
-        <v>0.0552654856959343</v>
+        <v>0.0576203761940484</v>
       </c>
       <c r="Q66" s="17" t="n">
-        <v>0.00109464550593308</v>
+        <v>0.00504788460582972</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>0.992337381963518</v>
+        <v>0.993836216960996</v>
       </c>
       <c r="S66" s="19" t="n">
-        <v>1.04028739818643</v>
+        <v>1.0443992994756</v>
       </c>
     </row>
     <row r="67">
@@ -5333,46 +5333,46 @@
         <v>86.53</v>
       </c>
       <c r="F67" s="6" t="n">
-        <v>1.84005996607998</v>
+        <v>1.86665895681897</v>
       </c>
       <c r="G67" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>85.3617320123648</v>
+        <v>85.3906809206671</v>
       </c>
       <c r="I67" s="9" t="n">
-        <v>80.6102181224675</v>
+        <v>80.4419622222599</v>
       </c>
       <c r="J67" s="10" t="n">
-        <v>83.1810603491494</v>
+        <v>83.2893236339085</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>84.68994003392</v>
+        <v>84.663341043181</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>84.68994003392</v>
+        <v>84.663341043181</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>84.68994003392</v>
+        <v>84.663341043181</v>
       </c>
       <c r="N67" s="14" t="n">
-        <v>84.68994003392</v>
+        <v>84.663341043181</v>
       </c>
       <c r="O67" s="15" t="n">
-        <v>0.0190676985148114</v>
+        <v>0.0160716171111921</v>
       </c>
       <c r="P67" s="16" t="n">
-        <v>-0.0448687305956251</v>
+        <v>-0.0450552531680058</v>
       </c>
       <c r="Q67" s="17" t="n">
-        <v>0.0192506480368952</v>
+        <v>0.0162014602130727</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>0.992130056846229</v>
+        <v>0.991482210123587</v>
       </c>
       <c r="S67" s="19" t="n">
-        <v>1.05061048098461</v>
+        <v>1.05247732283379</v>
       </c>
     </row>
     <row r="68">
@@ -5392,46 +5392,46 @@
         <v>87.103</v>
       </c>
       <c r="F68" s="6" t="n">
-        <v>-0.504065651025295</v>
+        <v>-0.366047573038055</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>85.5808361003216</v>
+        <v>85.4028006711968</v>
       </c>
       <c r="I68" s="9" t="n">
-        <v>81.2936310081266</v>
+        <v>81.0457878953902</v>
       </c>
       <c r="J68" s="10" t="n">
-        <v>83.6169860722035</v>
+        <v>83.7021433363967</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>87.6070656510253</v>
+        <v>87.4690475730381</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>87.6070656510253</v>
+        <v>87.4690475730381</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>87.6070656510253</v>
+        <v>87.4690475730381</v>
       </c>
       <c r="N68" s="14" t="n">
-        <v>87.6070656510253</v>
+        <v>87.4690475730381</v>
       </c>
       <c r="O68" s="15" t="n">
-        <v>0.0338648299387758</v>
+        <v>0.0326022901982391</v>
       </c>
       <c r="P68" s="16" t="n">
-        <v>0.154693382321823</v>
+        <v>0.153365465097244</v>
       </c>
       <c r="Q68" s="17" t="n">
-        <v>0.0344447713144784</v>
+        <v>0.0331395677903381</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>1.02367620653213</v>
+        <v>1.0241941351525</v>
       </c>
       <c r="S68" s="19" t="n">
-        <v>1.07766210666943</v>
+        <v>1.07925470088512</v>
       </c>
     </row>
     <row r="69">
@@ -5451,46 +5451,46 @@
         <v>82.518</v>
       </c>
       <c r="F69" s="6" t="n">
-        <v>0.0165012772788441</v>
+        <v>0.168467401785308</v>
       </c>
       <c r="G69" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>85.1091076031188</v>
+        <v>85.122400715333</v>
       </c>
       <c r="I69" s="9" t="n">
-        <v>81.9237743771225</v>
+        <v>81.583422109882</v>
       </c>
       <c r="J69" s="10" t="n">
-        <v>83.8799307769408</v>
+        <v>83.9245957668879</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>82.5014987227212</v>
+        <v>82.3495325982147</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>82.5014987227212</v>
+        <v>82.3495325982147</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>82.5014987227212</v>
+        <v>82.3495325982147</v>
       </c>
       <c r="N69" s="14" t="n">
-        <v>82.5014987227212</v>
+        <v>82.3495325982147</v>
       </c>
       <c r="O69" s="15" t="n">
-        <v>-0.0600451932947384</v>
+        <v>-0.0603122079479507</v>
       </c>
       <c r="P69" s="16" t="n">
-        <v>-0.0060005424228553</v>
+        <v>-0.00658136123680653</v>
       </c>
       <c r="Q69" s="17" t="n">
-        <v>-0.0582780268961604</v>
+        <v>-0.0585294468943255</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>0.969361576524131</v>
+        <v>0.967424930525734</v>
       </c>
       <c r="S69" s="19" t="n">
-        <v>1.00705197422837</v>
+        <v>1.00939051670695</v>
       </c>
     </row>
     <row r="70">
@@ -5510,46 +5510,46 @@
         <v>86.718</v>
       </c>
       <c r="F70" s="6" t="n">
-        <v>-0.910281794523327</v>
+        <v>-1.34598403721199</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H70" s="8" t="n">
-        <v>85.9232702493223</v>
+        <v>86.1121541287901</v>
       </c>
       <c r="I70" s="9" t="n">
-        <v>82.5055905759519</v>
+        <v>82.059093431602</v>
       </c>
       <c r="J70" s="10" t="n">
-        <v>83.9945521495847</v>
+        <v>83.9763378281926</v>
       </c>
       <c r="K70" s="11" t="n">
-        <v>87.6282817945233</v>
+        <v>88.063984037212</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>87.6282817945233</v>
+        <v>88.063984037212</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>87.6282817945233</v>
+        <v>88.063984037212</v>
       </c>
       <c r="N70" s="14" t="n">
-        <v>87.6282817945233</v>
+        <v>88.063984037212</v>
       </c>
       <c r="O70" s="15" t="n">
-        <v>0.0602873378610145</v>
+        <v>0.0670908607955894</v>
       </c>
       <c r="P70" s="16" t="n">
-        <v>0.0546138416163131</v>
+        <v>0.0570188710737554</v>
       </c>
       <c r="Q70" s="17" t="n">
-        <v>0.0621416962258197</v>
+        <v>0.0693926396264839</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>1.01984342006832</v>
+        <v>1.02266613729698</v>
       </c>
       <c r="S70" s="19" t="n">
-        <v>1.06208901945688</v>
+        <v>1.07317763765713</v>
       </c>
     </row>
     <row r="71">
@@ -5569,46 +5569,46 @@
         <v>86.566</v>
       </c>
       <c r="F71" s="6" t="n">
-        <v>0.836692102040065</v>
+        <v>0.958233119842036</v>
       </c>
       <c r="G71" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>85.89391562648</v>
+        <v>85.918767848927</v>
       </c>
       <c r="I71" s="9" t="n">
-        <v>83.0443830288272</v>
+        <v>82.4775092454721</v>
       </c>
       <c r="J71" s="10" t="n">
-        <v>83.9786157160875</v>
+        <v>83.8691511072778</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>85.7293078979599</v>
+        <v>85.607766880158</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>85.7293078979599</v>
+        <v>85.607766880158</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>85.7293078979599</v>
+        <v>85.607766880158</v>
       </c>
       <c r="N71" s="14" t="n">
-        <v>85.7293078979599</v>
+        <v>85.607766880158</v>
       </c>
       <c r="O71" s="15" t="n">
-        <v>-0.0219090477583231</v>
+        <v>-0.0282876279944692</v>
       </c>
       <c r="P71" s="16" t="n">
-        <v>0.0122726248669396</v>
+        <v>0.0111550740301549</v>
       </c>
       <c r="Q71" s="17" t="n">
-        <v>-0.0216707877602375</v>
+        <v>-0.0278912790956192</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>0.998083592681513</v>
+        <v>0.996380290633173</v>
       </c>
       <c r="S71" s="19" t="n">
-        <v>1.03233120376366</v>
+        <v>1.03795286331174</v>
       </c>
     </row>
     <row r="72">
@@ -5628,46 +5628,46 @@
         <v>82.84</v>
       </c>
       <c r="F72" s="6" t="n">
-        <v>0.0728965103216065</v>
+        <v>0.28168941574034</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H72" s="8" t="n">
-        <v>83.3853417810223</v>
+        <v>83.0919160546307</v>
       </c>
       <c r="I72" s="9" t="n">
-        <v>83.5486568419725</v>
+        <v>82.8471299930428</v>
       </c>
       <c r="J72" s="10" t="n">
-        <v>83.8680556506263</v>
+        <v>83.6352554221556</v>
       </c>
       <c r="K72" s="11" t="n">
-        <v>82.7671034896784</v>
+        <v>82.5583105842597</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>82.7671034896784</v>
+        <v>82.5583105842597</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>82.7671034896784</v>
+        <v>82.5583105842597</v>
       </c>
       <c r="N72" s="14" t="n">
-        <v>82.7671034896784</v>
+        <v>82.5583105842597</v>
       </c>
       <c r="O72" s="15" t="n">
-        <v>-0.0351640680173085</v>
+        <v>-0.0362711749734148</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>-0.0552462535456495</v>
+        <v>-0.0561425684288817</v>
       </c>
       <c r="Q72" s="17" t="n">
-        <v>-0.0345529957130569</v>
+        <v>-0.0356212573581931</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>0.992585767736403</v>
+        <v>0.993578130151431</v>
       </c>
       <c r="S72" s="19" t="n">
-        <v>0.990645530618495</v>
+        <v>0.996513827228447</v>
       </c>
     </row>
     <row r="73">
@@ -5687,46 +5687,46 @@
         <v>82.611</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>0.148605466851452</v>
+        <v>0.353492396511485</v>
       </c>
       <c r="G73" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>82.1582839301551</v>
+        <v>82.1768919765</v>
       </c>
       <c r="I73" s="9" t="n">
-        <v>84.028595199655</v>
+        <v>83.1783725268861</v>
       </c>
       <c r="J73" s="10" t="n">
-        <v>83.7075595882876</v>
+        <v>83.3155636697025</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>82.4623945331486</v>
+        <v>82.2575076034885</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>82.4623945331486</v>
+        <v>82.2575076034885</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>82.4623945331486</v>
+        <v>82.2575076034885</v>
       </c>
       <c r="N73" s="14" t="n">
-        <v>82.4623945331486</v>
+        <v>82.2575076034885</v>
       </c>
       <c r="O73" s="15" t="n">
-        <v>-0.00368831601628178</v>
+        <v>-0.00365017530555792</v>
       </c>
       <c r="P73" s="16" t="n">
-        <v>-0.0004739815661291</v>
+        <v>-0.00111749261741612</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>-0.00368152253350074</v>
+        <v>-0.00364352151397451</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>1.00370152087466</v>
+        <v>1.00098100116772</v>
       </c>
       <c r="S73" s="19" t="n">
-        <v>0.98136109900701</v>
+        <v>0.988929034129636</v>
       </c>
     </row>
     <row r="74">
@@ -5746,46 +5746,46 @@
         <v>79.522</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>-0.594090262109032</v>
+        <v>-1.25805208104809</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>78.7433302753282</v>
+        <v>79.1297956125132</v>
       </c>
       <c r="I74" s="9" t="n">
-        <v>84.4938928152969</v>
+        <v>83.4814731874438</v>
       </c>
       <c r="J74" s="10" t="n">
-        <v>83.536310403353</v>
+        <v>82.9456040226057</v>
       </c>
       <c r="K74" s="11" t="n">
-        <v>80.116090262109</v>
+        <v>80.7800520810481</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>80.116090262109</v>
+        <v>80.7800520810481</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>80.116090262109</v>
+        <v>80.7800520810481</v>
       </c>
       <c r="N74" s="14" t="n">
-        <v>80.116090262109</v>
+        <v>80.7800520810481</v>
       </c>
       <c r="O74" s="15" t="n">
-        <v>-0.028865654499662</v>
+        <v>-0.0181246084718034</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>-0.0857279337055744</v>
+        <v>-0.0827118150035777</v>
       </c>
       <c r="Q74" s="17" t="n">
-        <v>-0.0284530213356385</v>
+        <v>-0.0179613456021827</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>1.01743334936408</v>
+        <v>1.02085505789268</v>
       </c>
       <c r="S74" s="19" t="n">
-        <v>0.948187941076905</v>
+        <v>0.96764047155313</v>
       </c>
     </row>
     <row r="75">
@@ -5805,46 +5805,46 @@
         <v>74.938</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>-0.199404951921869</v>
+        <v>0.0363322338993265</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>0.991350654950947</v>
+        <v>0.90536033451555</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>78.4233421635909</v>
+        <v>78.6296549167427</v>
       </c>
       <c r="I75" s="9" t="n">
-        <v>84.9532655269037</v>
+        <v>83.7660927745803</v>
       </c>
       <c r="J75" s="10" t="n">
-        <v>83.3872651448285</v>
+        <v>82.555614373221</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>75.1374049519219</v>
+        <v>74.9016677661007</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>75.1658261566751</v>
+        <v>75.2544832229678</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>75.1658261566751</v>
+        <v>75.2544832229678</v>
       </c>
       <c r="N75" s="14" t="n">
-        <v>75.1658261566751</v>
+        <v>75.2544832229678</v>
       </c>
       <c r="O75" s="15" t="n">
-        <v>-0.0637800228200848</v>
+        <v>-0.0708545752939109</v>
       </c>
       <c r="P75" s="16" t="n">
-        <v>-0.12321902509534</v>
+        <v>-0.12093860212104</v>
       </c>
       <c r="Q75" s="17" t="n">
-        <v>-0.0617886380780511</v>
+        <v>-0.0684026404505957</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>0.958462417986208</v>
+        <v>0.957075079404218</v>
       </c>
       <c r="S75" s="19" t="n">
-        <v>0.884790310183792</v>
+        <v>0.89838836610754</v>
       </c>
     </row>
     <row r="76">
@@ -5864,46 +5864,46 @@
         <v>86.256</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.491196524550069</v>
+        <v>0.795486336221929</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="8" t="n">
-        <v>83.3443013832209</v>
+        <v>83.4174562637763</v>
       </c>
       <c r="I76" s="9" t="n">
-        <v>85.4126930458852</v>
+        <v>84.0402036999687</v>
       </c>
       <c r="J76" s="10" t="n">
-        <v>83.2762797610138</v>
+        <v>82.1650048541967</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>85.7648034754499</v>
+        <v>85.4605136637781</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>85.7648034754499</v>
+        <v>85.4605136637781</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>85.7648034754499</v>
+        <v>85.4605136637781</v>
       </c>
       <c r="N76" s="14" t="n">
-        <v>85.7648034754499</v>
+        <v>85.4605136637781</v>
       </c>
       <c r="O76" s="15" t="n">
-        <v>0.131912018167511</v>
+        <v>0.127178961205106</v>
       </c>
       <c r="P76" s="16" t="n">
-        <v>0.0362184957474727</v>
+        <v>0.0351533729188462</v>
       </c>
       <c r="Q76" s="17" t="n">
-        <v>0.141007926882655</v>
+        <v>0.135620231562436</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>1.02904220267082</v>
+        <v>1.02449196476984</v>
       </c>
       <c r="S76" s="19" t="n">
-        <v>1.00412246022234</v>
+        <v>1.01690036317475</v>
       </c>
     </row>
     <row r="77">
@@ -5923,80 +5923,106 @@
         <v>86.282</v>
       </c>
       <c r="F77" s="6" t="n">
-        <v>0.542171380966198</v>
+        <v>0.735049886956014</v>
       </c>
       <c r="G77" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>85.6934026255793</v>
+        <v>84.39548406602</v>
       </c>
       <c r="I77" s="9" t="n">
-        <v>85.8720379340448</v>
+        <v>84.3064586193123</v>
       </c>
       <c r="J77" s="10" t="n">
-        <v>83.1781030052679</v>
+        <v>81.7566799424297</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>85.7398286190338</v>
+        <v>85.546950113044</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>85.7398286190338</v>
+        <v>85.546950113044</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>85.7398286190338</v>
+        <v>85.546950113044</v>
       </c>
       <c r="N77" s="14" t="n">
-        <v>85.7398286190338</v>
+        <v>85.546950113044</v>
       </c>
       <c r="O77" s="15" t="n">
-        <v>-0.000291244105627546</v>
+        <v>0.00101090858513344</v>
       </c>
       <c r="P77" s="16" t="n">
-        <v>0.0397445903001006</v>
+        <v>0.0399895718383758</v>
       </c>
       <c r="Q77" s="17" t="n">
-        <v>-0.000291201698180088</v>
+        <v>0.00101141972544139</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1.00054176858465</v>
+        <v>1.01364369266634</v>
       </c>
       <c r="S77" s="19" t="n">
-        <v>0.998460391552457</v>
+        <v>1.01471407427197</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
         <v>130</v>
       </c>
-      <c r="B78" s="2"/>
+      <c r="B78" s="2" t="n">
+        <v>76.364</v>
+      </c>
       <c r="C78" s="3" t="n">
-        <v>81.4333459701193</v>
+        <v>76.364</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>97.0357288617872</v>
+        <v>76.364</v>
       </c>
       <c r="E78" s="5" t="n">
-        <v>65.8309630784515</v>
+        <v>76.364</v>
       </c>
       <c r="F78" s="6" t="n">
-        <v>-0.469177422976476</v>
-      </c>
-      <c r="G78" s="7"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="9"/>
-      <c r="J78" s="10"/>
-      <c r="K78" s="11"/>
-      <c r="L78" s="12"/>
-      <c r="M78" s="13"/>
+        <v>-1.2993472992852</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="8" t="n">
+        <v>80.0206772588438</v>
+      </c>
+      <c r="I78" s="9" t="n">
+        <v>84.5683978820416</v>
+      </c>
+      <c r="J78" s="10" t="n">
+        <v>81.3300216588647</v>
+      </c>
+      <c r="K78" s="11" t="n">
+        <v>77.6633472992852</v>
+      </c>
+      <c r="L78" s="12" t="n">
+        <v>77.6633472992852</v>
+      </c>
+      <c r="M78" s="13" t="n">
+        <v>77.6633472992852</v>
+      </c>
       <c r="N78" s="14" t="n">
-        <v>81.9025233930958</v>
-      </c>
-      <c r="O78" s="15"/>
-      <c r="P78" s="16"/>
-      <c r="Q78" s="17"/>
-      <c r="R78" s="18"/>
-      <c r="S78" s="19"/>
+        <v>77.6633472992852</v>
+      </c>
+      <c r="O78" s="15" t="n">
+        <v>-0.0966819240099437</v>
+      </c>
+      <c r="P78" s="16" t="n">
+        <v>-0.038582604262694</v>
+      </c>
+      <c r="Q78" s="17" t="n">
+        <v>-0.0921552761768967</v>
+      </c>
+      <c r="R78" s="18" t="n">
+        <v>0.970540989650296</v>
+      </c>
+      <c r="S78" s="19" t="n">
+        <v>0.918349516418796</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
@@ -6004,16 +6030,16 @@
       </c>
       <c r="B79" s="2"/>
       <c r="C79" s="3" t="n">
-        <v>80.6787070653612</v>
+        <v>78.8918146905253</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>97.0989642566814</v>
+        <v>94.4260980738131</v>
       </c>
       <c r="E79" s="5" t="n">
-        <v>64.2584498740409</v>
+        <v>63.3575313072374</v>
       </c>
       <c r="F79" s="6" t="n">
-        <v>-1.0131098163127</v>
+        <v>-0.705253186661475</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="8"/>
@@ -6023,7 +6049,7 @@
       <c r="L79" s="12"/>
       <c r="M79" s="13"/>
       <c r="N79" s="14" t="n">
-        <v>81.6918168816739</v>
+        <v>79.5970678771868</v>
       </c>
       <c r="O79" s="15"/>
       <c r="P79" s="16"/>
@@ -6037,16 +6063,16 @@
       </c>
       <c r="B80" s="2"/>
       <c r="C80" s="3" t="n">
-        <v>80.0021189833975</v>
+        <v>78.3331909899427</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>97.0726693231899</v>
+        <v>94.6591594318951</v>
       </c>
       <c r="E80" s="5" t="n">
-        <v>62.9315686436052</v>
+        <v>62.0072225479902</v>
       </c>
       <c r="F80" s="6" t="n">
-        <v>0.974327735275761</v>
+        <v>1.30230546154582</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="8"/>
@@ -6056,7 +6082,7 @@
       <c r="L80" s="12"/>
       <c r="M80" s="13"/>
       <c r="N80" s="14" t="n">
-        <v>79.0277912481217</v>
+        <v>77.0308855283969</v>
       </c>
       <c r="O80" s="15"/>
       <c r="P80" s="16"/>
@@ -6070,16 +6096,16 @@
       </c>
       <c r="B81" s="2"/>
       <c r="C81" s="3" t="n">
-        <v>79.3955090806097</v>
+        <v>77.8360973002782</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>96.9898602033172</v>
+        <v>94.7836120500271</v>
       </c>
       <c r="E81" s="5" t="n">
-        <v>61.8011579579022</v>
+        <v>60.8885825505293</v>
       </c>
       <c r="F81" s="6" t="n">
-        <v>0.666056319693859</v>
+        <v>0.854303369790119</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="8"/>
@@ -6089,7 +6115,7 @@
       <c r="L81" s="12"/>
       <c r="M81" s="13"/>
       <c r="N81" s="14" t="n">
-        <v>78.7294527609158</v>
+        <v>76.9817939304881</v>
       </c>
       <c r="O81" s="15"/>
       <c r="P81" s="16"/>
@@ -6102,10 +6128,18 @@
         <v>134</v>
       </c>
       <c r="B82" s="2"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="6"/>
+      <c r="C82" s="3" t="n">
+        <v>77.3937563540446</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>94.835789068413</v>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>59.9517236396761</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>-1.48576489342106</v>
+      </c>
       <c r="G82" s="7"/>
       <c r="H82" s="8"/>
       <c r="I82" s="9"/>
@@ -6113,7 +6147,9 @@
       <c r="K82" s="11"/>
       <c r="L82" s="12"/>
       <c r="M82" s="13"/>
-      <c r="N82" s="14"/>
+      <c r="N82" s="14" t="n">
+        <v>78.8795212474657</v>
+      </c>
       <c r="O82" s="15"/>
       <c r="P82" s="16"/>
       <c r="Q82" s="17"/>
@@ -6611,7 +6647,7 @@
         <v>171</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>0.0143909663492046</v>
+        <v>0.023921496262933</v>
       </c>
     </row>
     <row r="6">
@@ -6619,7 +6655,7 @@
         <v>172</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>-0.0549177632913489</v>
+        <v>-0.0553349541655469</v>
       </c>
     </row>
     <row r="7">
@@ -6627,7 +6663,7 @@
         <v>173</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>-0.00528574400128268</v>
+        <v>-0.0219857730555492</v>
       </c>
     </row>
     <row r="8">
@@ -6635,7 +6671,7 @@
         <v>174</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>0.137801449851668</v>
+        <v>0.134026332220822</v>
       </c>
     </row>
     <row r="9">
@@ -6643,7 +6679,7 @@
         <v>175</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>0.342637246779251</v>
+        <v>0.350515836346144</v>
       </c>
     </row>
     <row r="10">
@@ -6651,7 +6687,7 @@
         <v>176</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>0.133161196420219</v>
+        <v>0.126649476627443</v>
       </c>
     </row>
     <row r="11">
@@ -6659,7 +6695,7 @@
         <v>177</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>0.0283701131038142</v>
+        <v>0.0261420144716598</v>
       </c>
     </row>
     <row r="12">
@@ -6667,7 +6703,7 @@
         <v>178</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>-0.179612555020879</v>
+        <v>-0.151704345408151</v>
       </c>
     </row>
     <row r="13">
@@ -6675,7 +6711,7 @@
         <v>179</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>-0.238445213843736</v>
+        <v>-0.244803716257978</v>
       </c>
     </row>
     <row r="14">
